--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uscp9a\Distribución OBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="478" documentId="13_ncr:1_{661915EF-FB0A-4BAE-BE12-09ADC5EFB6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03B4D355-D7DB-46E1-A0F8-9B1AF84E55BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="100" r:id="rId2"/>
+    <pivotCache cacheId="268" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="23">
   <si>
     <t>SEM</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>TL</t>
@@ -583,7 +580,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Oriol Larrea Vivés" refreshedDate="45958.509275810182" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45960.681586921295" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -606,17 +603,17 @@
         <s v="B2"/>
         <s v="C1"/>
         <s v="C2"/>
-        <s v="C3"/>
+        <m/>
         <s v="TL"/>
-        <m/>
         <s v="S2"/>
         <s v="S3"/>
         <s v="S4"/>
         <s v="S5"/>
+        <s v="C3" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1872"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1662"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -662,21 +659,21 @@
   <r>
     <x v="0"/>
     <x v="6"/>
-    <n v="210"/>
+    <m/>
   </r>
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="1872"/>
+    <n v="1662"/>
   </r>
   <r>
     <x v="1"/>
+    <x v="6"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
     <x v="8"/>
-    <m/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="9"/>
     <s v="TL"/>
   </r>
   <r>
@@ -712,21 +709,21 @@
   <r>
     <x v="2"/>
     <x v="6"/>
-    <n v="214"/>
+    <m/>
   </r>
   <r>
     <x v="2"/>
     <x v="7"/>
-    <n v="1782"/>
+    <n v="1568"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="8"/>
+    <x v="6"/>
     <m/>
   </r>
   <r>
     <x v="3"/>
-    <x v="10"/>
+    <x v="9"/>
     <s v="TL"/>
   </r>
   <r>
@@ -762,21 +759,21 @@
   <r>
     <x v="3"/>
     <x v="6"/>
-    <n v="224"/>
+    <m/>
   </r>
   <r>
     <x v="3"/>
     <x v="7"/>
-    <n v="1720"/>
+    <n v="1496"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="8"/>
+    <x v="6"/>
     <m/>
   </r>
   <r>
     <x v="4"/>
-    <x v="11"/>
+    <x v="10"/>
     <s v="TL"/>
   </r>
   <r>
@@ -812,21 +809,21 @@
   <r>
     <x v="4"/>
     <x v="6"/>
-    <n v="54"/>
+    <m/>
   </r>
   <r>
     <x v="4"/>
     <x v="7"/>
-    <n v="383"/>
+    <n v="329"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="8"/>
+    <x v="6"/>
     <m/>
   </r>
   <r>
     <x v="5"/>
-    <x v="12"/>
+    <x v="11"/>
     <s v="TL"/>
   </r>
   <r>
@@ -862,7 +859,7 @@
   <r>
     <x v="5"/>
     <x v="6"/>
-    <n v="0"/>
+    <m/>
   </r>
   <r>
     <x v="5"/>
@@ -873,8 +870,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="100" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O9:W16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="268" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
@@ -895,13 +892,13 @@
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item x="6"/>
+        <item m="1" x="12"/>
+        <item h="1" x="8"/>
         <item h="1" x="9"/>
         <item h="1" x="10"/>
         <item h="1" x="11"/>
-        <item h="1" x="12"/>
         <item h="1" x="7"/>
-        <item h="1" x="8"/>
+        <item h="1" x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -933,7 +930,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="8">
+  <colItems count="7">
     <i>
       <x/>
     </i>
@@ -951,9 +948,6 @@
     </i>
     <i>
       <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -1300,20 +1294,20 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>21</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -1326,7 +1320,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1354,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1392,7 +1386,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -1400,7 +1394,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="11">
-        <f t="shared" ref="C4:C9" si="1">+SUM(D4:H4)</f>
+        <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
         <v>310</v>
       </c>
       <c r="D4">
@@ -1424,11 +1418,11 @@
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="31"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
@@ -1460,7 +1454,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
@@ -1492,7 +1486,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>1</v>
       </c>
@@ -1524,7 +1518,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
@@ -1556,109 +1550,59 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11">
-        <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>42</v>
-      </c>
-      <c r="F9">
-        <v>42</v>
-      </c>
-      <c r="G9">
-        <v>42</v>
-      </c>
-      <c r="H9">
-        <v>42</v>
-      </c>
-      <c r="I9" s="26">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="11"/>
+      <c r="I9" s="26"/>
       <c r="J9" s="3"/>
-      <c r="O9" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>1872</v>
+        <v>1662</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>394</v>
+        <v>352</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="F10" s="19">
         <f t="shared" si="3"/>
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="G10" s="19">
         <f t="shared" si="3"/>
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="3"/>
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>62.4</v>
+        <v>55.4</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" t="s">
-        <v>6</v>
-      </c>
-      <c r="S10" t="s">
-        <v>7</v>
-      </c>
-      <c r="T10" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" t="s">
-        <v>9</v>
-      </c>
-      <c r="V10" t="s">
-        <v>10</v>
-      </c>
-      <c r="W10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10" s="30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -1669,43 +1613,40 @@
       <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="O11" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="34">
-        <v>272</v>
-      </c>
-      <c r="Q11" s="34">
-        <v>310</v>
-      </c>
-      <c r="R11" s="34">
-        <v>305</v>
-      </c>
-      <c r="S11" s="34">
-        <v>273</v>
-      </c>
-      <c r="T11" s="34">
-        <v>232</v>
-      </c>
-      <c r="U11" s="34">
-        <v>270</v>
-      </c>
-      <c r="V11" s="34">
-        <v>210</v>
-      </c>
-      <c r="W11" s="34">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O11" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="P11" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" t="s">
+        <v>7</v>
+      </c>
+      <c r="T11" t="s">
+        <v>8</v>
+      </c>
+      <c r="U11" t="s">
+        <v>9</v>
+      </c>
+      <c r="V11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="8">
         <f>+H2+1</f>
@@ -1732,36 +1673,33 @@
       </c>
       <c r="J12" s="1"/>
       <c r="O12" s="29" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P12" s="34">
+        <v>272</v>
+      </c>
+      <c r="Q12" s="34">
+        <v>310</v>
+      </c>
+      <c r="R12" s="34">
+        <v>305</v>
+      </c>
+      <c r="S12" s="34">
+        <v>273</v>
+      </c>
+      <c r="T12" s="34">
+        <v>232</v>
+      </c>
+      <c r="U12" s="34">
         <v>270</v>
       </c>
-      <c r="Q12" s="34">
-        <v>312</v>
-      </c>
-      <c r="R12" s="34">
-        <v>245</v>
-      </c>
-      <c r="S12" s="34">
-        <v>228</v>
-      </c>
-      <c r="T12" s="34">
-        <v>231</v>
-      </c>
-      <c r="U12" s="34">
-        <v>282</v>
-      </c>
       <c r="V12" s="34">
-        <v>214</v>
-      </c>
-      <c r="W12" s="34">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>4</v>
@@ -1791,42 +1729,39 @@
       </c>
       <c r="J13" s="3"/>
       <c r="O13" s="29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P13" s="34">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q13" s="34">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="R13" s="34">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S13" s="34">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="T13" s="34">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="U13" s="34">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="V13" s="34">
-        <v>224</v>
-      </c>
-      <c r="W13" s="34">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="11">
-        <f t="shared" ref="C14:C19" si="5">+SUM(D14:H14)</f>
+        <f t="shared" ref="C14:C18" si="5">+SUM(D14:H14)</f>
         <v>312</v>
       </c>
       <c r="D14">
@@ -1850,36 +1785,33 @@
       </c>
       <c r="J14" s="3"/>
       <c r="O14" s="29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P14" s="34">
-        <v>54</v>
+        <v>267</v>
       </c>
       <c r="Q14" s="34">
-        <v>64</v>
+        <v>302</v>
       </c>
       <c r="R14" s="34">
-        <v>59</v>
+        <v>243</v>
       </c>
       <c r="S14" s="34">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="T14" s="34">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="U14" s="34">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="V14" s="34">
-        <v>54</v>
-      </c>
-      <c r="W14" s="34">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>6</v>
@@ -1909,36 +1841,33 @@
       </c>
       <c r="J15" s="3"/>
       <c r="O15" s="29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P15" s="34">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q15" s="34">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="R15" s="34">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="S15" s="34">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T15" s="34">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U15" s="34">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="V15" s="34">
-        <v>0</v>
-      </c>
-      <c r="W15" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>7</v>
@@ -1968,36 +1897,33 @@
       </c>
       <c r="J16" s="3"/>
       <c r="O16" s="29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P16" s="34">
-        <v>863</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="34">
-        <v>988</v>
+        <v>0</v>
       </c>
       <c r="R16" s="34">
-        <v>852</v>
+        <v>0</v>
       </c>
       <c r="S16" s="34">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="T16" s="34">
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="U16" s="34">
-        <v>878</v>
+        <v>0</v>
       </c>
       <c r="V16" s="34">
-        <v>702</v>
-      </c>
-      <c r="W16" s="34">
-        <v>5757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>8</v>
@@ -2026,10 +1952,34 @@
         <v>7.7</v>
       </c>
       <c r="J17" s="3"/>
+      <c r="O17" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" s="34">
+        <v>863</v>
+      </c>
+      <c r="Q17" s="34">
+        <v>988</v>
+      </c>
+      <c r="R17" s="34">
+        <v>852</v>
+      </c>
+      <c r="S17" s="34">
+        <v>781</v>
+      </c>
+      <c r="T17" s="34">
+        <v>693</v>
+      </c>
+      <c r="U17" s="34">
+        <v>878</v>
+      </c>
+      <c r="V17" s="34">
+        <v>5055</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>9</v>
@@ -2059,72 +2009,49 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11">
-        <f t="shared" si="5"/>
-        <v>214</v>
-      </c>
-      <c r="D19">
-        <v>42</v>
-      </c>
-      <c r="E19">
-        <v>42</v>
-      </c>
-      <c r="F19">
-        <v>42</v>
-      </c>
-      <c r="G19">
-        <v>42</v>
-      </c>
-      <c r="H19">
-        <v>46</v>
-      </c>
-      <c r="I19" s="26">
-        <f t="shared" si="6"/>
-        <v>7.1333333333333329</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="11"/>
+      <c r="I19" s="26"/>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="18">
         <f>SUM(C13:C19)</f>
-        <v>1782</v>
+        <v>1568</v>
       </c>
       <c r="D20" s="19">
         <f>SUM(D13:D19)</f>
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" ref="E20:H20" si="7">SUM(E13:E19)</f>
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="F20" s="19">
         <f t="shared" si="7"/>
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="G20" s="19">
         <f t="shared" si="7"/>
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="H20" s="19">
         <f t="shared" si="7"/>
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="I20" s="26">
         <f t="shared" si="6"/>
-        <v>59.4</v>
+        <v>52.266666666666666</v>
       </c>
       <c r="J20" s="20"/>
     </row>
@@ -2140,19 +2067,19 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="O21" s="31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P21" s="31"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="8">
         <f>+H12+1</f>
@@ -2184,7 +2111,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>4</v>
@@ -2216,13 +2143,13 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>5</v>
       </c>
       <c r="C24" s="11">
-        <f t="shared" ref="C24:C29" si="9">+SUM(D24:H24)</f>
+        <f t="shared" ref="C24:C28" si="9">+SUM(D24:H24)</f>
         <v>302</v>
       </c>
       <c r="D24">
@@ -2248,7 +2175,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>6</v>
@@ -2280,7 +2207,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>7</v>
@@ -2312,7 +2239,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>8</v>
@@ -2344,7 +2271,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>9</v>
@@ -2374,72 +2301,49 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="11">
-        <f t="shared" si="9"/>
-        <v>224</v>
-      </c>
-      <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29">
-        <v>46</v>
-      </c>
-      <c r="F29">
-        <v>46</v>
-      </c>
-      <c r="G29">
-        <v>46</v>
-      </c>
-      <c r="H29">
-        <v>46</v>
-      </c>
-      <c r="I29" s="26">
-        <f t="shared" si="10"/>
-        <v>7.4666666666666668</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="11"/>
+      <c r="I29" s="26"/>
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="18">
-        <f>SUM(C23:C29)</f>
-        <v>1720</v>
+        <f t="shared" ref="C30:H30" si="11">SUM(C23:C29)</f>
+        <v>1496</v>
       </c>
       <c r="D30" s="19">
-        <f>SUM(D23:D29)</f>
-        <v>341</v>
+        <f t="shared" si="11"/>
+        <v>301</v>
       </c>
       <c r="E30" s="19">
-        <f t="shared" ref="E30:H30" si="11">SUM(E23:E29)</f>
-        <v>347</v>
+        <f t="shared" si="11"/>
+        <v>301</v>
       </c>
       <c r="F30" s="19">
         <f t="shared" si="11"/>
-        <v>347</v>
+        <v>301</v>
       </c>
       <c r="G30" s="19">
         <f t="shared" si="11"/>
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="H30" s="19">
         <f t="shared" si="11"/>
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="I30" s="26">
         <f t="shared" si="10"/>
-        <v>57.333333333333336</v>
+        <v>49.866666666666667</v>
       </c>
       <c r="J30" s="20"/>
     </row>
@@ -2458,13 +2362,13 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="8">
         <f>+H22+1</f>
@@ -2494,7 +2398,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>4</v>
@@ -2519,13 +2423,13 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="11">
-        <f t="shared" ref="C34:C39" si="13">+SUM(D34:H34)</f>
+        <f t="shared" ref="C34:C38" si="13">+SUM(D34:H34)</f>
         <v>64</v>
       </c>
       <c r="D34" s="12">
@@ -2544,7 +2448,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>6</v>
@@ -2569,7 +2473,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>7</v>
@@ -2594,7 +2498,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>8</v>
@@ -2619,7 +2523,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>9</v>
@@ -2642,48 +2546,38 @@
       <c r="J38" s="3"/>
       <c r="AF38" s="27"/>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="11">
-        <f t="shared" si="13"/>
-        <v>54</v>
-      </c>
-      <c r="D39" s="16">
-        <v>54</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="16"/>
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
       <c r="H39" s="16"/>
-      <c r="I39" s="26">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
+      <c r="I39" s="26"/>
       <c r="J39" s="3"/>
       <c r="AF39" s="27"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40" s="18">
-        <f>SUM(C33:C39)</f>
-        <v>383</v>
+        <f t="shared" ref="C40:H40" si="15">SUM(C33:C39)</f>
+        <v>329</v>
       </c>
       <c r="D40" s="19">
-        <f>SUM(D33:D39)</f>
-        <v>383</v>
+        <f t="shared" si="15"/>
+        <v>329</v>
       </c>
       <c r="E40" s="19">
-        <f t="shared" ref="E40:H40" si="15">SUM(E33:E39)</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F40" s="19">
@@ -2700,7 +2594,7 @@
       </c>
       <c r="I40" s="26">
         <f t="shared" si="14"/>
-        <v>12.766666666666667</v>
+        <v>10.966666666666667</v>
       </c>
       <c r="J40" s="20"/>
       <c r="AF40" s="27"/>
@@ -2720,13 +2614,13 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" s="8">
         <f>+H32+1</f>
@@ -2756,7 +2650,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>4</v>
@@ -2779,13 +2673,13 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>5</v>
       </c>
       <c r="C44" s="11">
-        <f t="shared" ref="C44:C49" si="17">+SUM(D44:H44)</f>
+        <f t="shared" ref="C44:C48" si="17">+SUM(D44:H44)</f>
         <v>0</v>
       </c>
       <c r="D44" s="12"/>
@@ -2802,7 +2696,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>6</v>
@@ -2825,7 +2719,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>7</v>
@@ -2848,7 +2742,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>8</v>
@@ -2871,7 +2765,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>9</v>
@@ -2892,35 +2786,27 @@
       <c r="J48" s="3"/>
       <c r="AF48" s="27"/>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="11">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="11"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
       <c r="F49" s="16"/>
       <c r="G49" s="16"/>
       <c r="H49" s="16"/>
-      <c r="I49" s="26">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="I49" s="26"/>
       <c r="J49" s="3"/>
       <c r="AF49" s="27"/>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" s="22">
         <f>SUM(C43:C49)</f>
@@ -3016,6 +2902,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3024,7 +2921,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3259,18 +3156,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3278,7 +3175,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8039E8B4-6FF4-40F6-9FA1-E9DA9C439884}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3295,15 +3192,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uscp9a\Distribución OBS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52F4BA0-4433-4B1D-8803-6E440F3554BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="268" r:id="rId2"/>
+    <pivotCache cacheId="4731" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -580,7 +580,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45960.681586921295" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45966.741130555558" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -613,7 +613,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1662"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="709"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -629,32 +629,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="272"/>
+    <n v="112"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="310"/>
+    <n v="114"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="305"/>
+    <n v="126"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="273"/>
+    <n v="88"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="232"/>
+    <n v="145"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="270"/>
+    <n v="124"/>
   </r>
   <r>
     <x v="0"/>
@@ -664,7 +664,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="1662"/>
+    <n v="709"/>
   </r>
   <r>
     <x v="1"/>
@@ -679,32 +679,32 @@
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="270"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
-    <n v="312"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <n v="245"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="3"/>
-    <n v="228"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="4"/>
-    <n v="231"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="5"/>
-    <n v="282"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
@@ -714,7 +714,7 @@
   <r>
     <x v="2"/>
     <x v="7"/>
-    <n v="1568"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -729,32 +729,32 @@
   <r>
     <x v="3"/>
     <x v="0"/>
-    <n v="267"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="1"/>
-    <n v="302"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="2"/>
-    <n v="243"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="3"/>
-    <n v="230"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="4"/>
-    <n v="186"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
     <x v="5"/>
-    <n v="268"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="3"/>
@@ -764,7 +764,7 @@
   <r>
     <x v="3"/>
     <x v="7"/>
-    <n v="1496"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -779,32 +779,32 @@
   <r>
     <x v="4"/>
     <x v="0"/>
-    <n v="54"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="1"/>
-    <n v="64"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="2"/>
-    <n v="59"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="3"/>
-    <n v="50"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="4"/>
-    <n v="44"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="5"/>
-    <n v="58"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
@@ -814,7 +814,7 @@
   <r>
     <x v="4"/>
     <x v="7"/>
-    <n v="329"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -870,7 +870,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="268" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="4731" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1294,7 +1294,9 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -1331,23 +1333,23 @@
         <v>2</v>
       </c>
       <c r="D2" s="8">
-        <v>45937</v>
+        <v>45965</v>
       </c>
       <c r="E2" s="8">
         <f>+D2+1</f>
-        <v>45938</v>
+        <v>45966</v>
       </c>
       <c r="F2" s="8">
         <f t="shared" ref="F2:G2" si="0">+E2+1</f>
-        <v>45939</v>
+        <v>45967</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" si="0"/>
-        <v>45940</v>
+        <v>45968</v>
       </c>
       <c r="H2" s="8">
         <f>+G2+3</f>
-        <v>45943</v>
+        <v>45971</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>3</v>
@@ -1363,26 +1365,17 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>272</v>
+        <v>112</v>
       </c>
       <c r="D3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>53</v>
-      </c>
-      <c r="F3">
-        <v>53</v>
-      </c>
-      <c r="G3">
-        <v>53</v>
-      </c>
-      <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>9.0666666666666664</v>
+        <v>9.3333333333333339</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1395,26 +1388,17 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>310</v>
+        <v>114</v>
       </c>
       <c r="D4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4">
-        <v>62</v>
-      </c>
-      <c r="F4">
-        <v>62</v>
-      </c>
-      <c r="G4">
-        <v>62</v>
-      </c>
-      <c r="H4">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>10.333333333333332</v>
+        <v>9.5</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="31" t="s">
@@ -1431,26 +1415,17 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>305</v>
+        <v>126</v>
       </c>
       <c r="D5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E5">
-        <v>61</v>
-      </c>
-      <c r="F5">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>61</v>
-      </c>
-      <c r="H5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>10.166666666666668</v>
+        <v>10.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1463,26 +1438,17 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="D6">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E6">
-        <v>66</v>
-      </c>
-      <c r="F6">
-        <v>45</v>
-      </c>
-      <c r="G6">
-        <v>48</v>
-      </c>
-      <c r="H6">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>9.1</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1495,26 +1461,17 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7">
-        <v>44</v>
-      </c>
-      <c r="G7">
-        <v>44</v>
-      </c>
-      <c r="H7">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>7.7333333333333325</v>
+        <v>12.083333333333334</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1527,26 +1484,17 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>124</v>
       </c>
       <c r="D8">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>48</v>
-      </c>
-      <c r="H8">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1568,11 +1516,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>1662</v>
+        <v>709</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -1580,19 +1528,19 @@
       </c>
       <c r="F10" s="19">
         <f t="shared" si="3"/>
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19">
         <f t="shared" si="3"/>
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="3"/>
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>55.4</v>
+        <v>23.633333333333333</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -1650,23 +1598,23 @@
       </c>
       <c r="D12" s="8">
         <f>+H2+1</f>
-        <v>45944</v>
+        <v>45972</v>
       </c>
       <c r="E12" s="8">
         <f>+D12+1</f>
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" ref="F12:G12" si="4">+E12+1</f>
-        <v>45946</v>
+        <v>45974</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="4"/>
-        <v>45947</v>
+        <v>45975</v>
       </c>
       <c r="H12" s="8">
         <f>+G12+3</f>
-        <v>45950</v>
+        <v>45978</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>3</v>
@@ -1676,25 +1624,25 @@
         <v>1</v>
       </c>
       <c r="P12" s="34">
-        <v>272</v>
+        <v>112</v>
       </c>
       <c r="Q12" s="34">
-        <v>310</v>
+        <v>114</v>
       </c>
       <c r="R12" s="34">
-        <v>305</v>
+        <v>126</v>
       </c>
       <c r="S12" s="34">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="T12" s="34">
-        <v>232</v>
+        <v>145</v>
       </c>
       <c r="U12" s="34">
-        <v>270</v>
+        <v>124</v>
       </c>
       <c r="V12" s="34">
-        <v>1662</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1706,51 +1654,36 @@
       </c>
       <c r="C13" s="11">
         <f>+SUM(D13:H13)</f>
-        <v>270</v>
-      </c>
-      <c r="D13">
-        <v>60</v>
-      </c>
-      <c r="E13">
-        <v>59</v>
-      </c>
-      <c r="F13">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>41</v>
-      </c>
-      <c r="H13">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I13" s="26">
         <f>IFERROR(C13/6/COUNT(D13:H13),0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3"/>
       <c r="O13" s="29" t="s">
         <v>11</v>
       </c>
       <c r="P13" s="34">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="34">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="R13" s="34">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="S13" s="34">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="T13" s="34">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="U13" s="34">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="V13" s="34">
-        <v>1568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1762,51 +1695,36 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" ref="C14:C18" si="5">+SUM(D14:H14)</f>
-        <v>312</v>
-      </c>
-      <c r="D14">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>64</v>
-      </c>
-      <c r="F14">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>58</v>
-      </c>
-      <c r="H14">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" ref="I14:I20" si="6">IFERROR(C14/6/COUNT(D14:H14),0)</f>
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3"/>
       <c r="O14" s="29" t="s">
         <v>12</v>
       </c>
       <c r="P14" s="34">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="34">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="R14" s="34">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="S14" s="34">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="T14" s="34">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="U14" s="34">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="V14" s="34">
-        <v>1496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1818,51 +1736,36 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="5"/>
-        <v>245</v>
-      </c>
-      <c r="D15">
-        <v>49</v>
-      </c>
-      <c r="E15">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>49</v>
-      </c>
-      <c r="H15">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="6"/>
-        <v>8.1666666666666679</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3"/>
       <c r="O15" s="29" t="s">
         <v>13</v>
       </c>
       <c r="P15" s="34">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="34">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R15" s="34">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="S15" s="34">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T15" s="34">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="U15" s="34">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="V15" s="34">
-        <v>329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1874,26 +1777,11 @@
       </c>
       <c r="C16" s="11">
         <f t="shared" si="5"/>
-        <v>228</v>
-      </c>
-      <c r="D16">
-        <v>48</v>
-      </c>
-      <c r="E16">
-        <v>48</v>
-      </c>
-      <c r="F16">
-        <v>42</v>
-      </c>
-      <c r="G16">
-        <v>36</v>
-      </c>
-      <c r="H16">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I16" s="26">
         <f t="shared" si="6"/>
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3"/>
       <c r="O16" s="29" t="s">
@@ -1930,51 +1818,36 @@
       </c>
       <c r="C17" s="11">
         <f t="shared" si="5"/>
-        <v>231</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
-      </c>
-      <c r="E17">
-        <v>50</v>
-      </c>
-      <c r="F17">
-        <v>50</v>
-      </c>
-      <c r="G17">
-        <v>44</v>
-      </c>
-      <c r="H17">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I17" s="26">
         <f t="shared" si="6"/>
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3"/>
       <c r="O17" s="29" t="s">
         <v>16</v>
       </c>
       <c r="P17" s="34">
-        <v>863</v>
+        <v>112</v>
       </c>
       <c r="Q17" s="34">
-        <v>988</v>
+        <v>114</v>
       </c>
       <c r="R17" s="34">
-        <v>852</v>
+        <v>126</v>
       </c>
       <c r="S17" s="34">
-        <v>781</v>
+        <v>88</v>
       </c>
       <c r="T17" s="34">
-        <v>693</v>
+        <v>145</v>
       </c>
       <c r="U17" s="34">
-        <v>878</v>
+        <v>124</v>
       </c>
       <c r="V17" s="34">
-        <v>5055</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -1986,26 +1859,11 @@
       </c>
       <c r="C18" s="11">
         <f t="shared" si="5"/>
-        <v>282</v>
-      </c>
-      <c r="D18">
-        <v>60</v>
-      </c>
-      <c r="E18">
-        <v>60</v>
-      </c>
-      <c r="F18">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>48</v>
-      </c>
-      <c r="H18">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I18" s="26">
         <f t="shared" si="6"/>
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -2027,31 +1885,31 @@
       </c>
       <c r="C20" s="18">
         <f>SUM(C13:C19)</f>
-        <v>1568</v>
+        <v>0</v>
       </c>
       <c r="D20" s="19">
         <f>SUM(D13:D19)</f>
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" ref="E20:H20" si="7">SUM(E13:E19)</f>
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="F20" s="19">
         <f t="shared" si="7"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G20" s="19">
         <f t="shared" si="7"/>
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="H20" s="19">
         <f t="shared" si="7"/>
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="I20" s="26">
         <f t="shared" si="6"/>
-        <v>52.266666666666666</v>
+        <v>0</v>
       </c>
       <c r="J20" s="20"/>
     </row>
@@ -2083,30 +1941,30 @@
       </c>
       <c r="D22" s="8">
         <f>+H12+1</f>
-        <v>45951</v>
+        <v>45979</v>
       </c>
       <c r="E22" s="8">
         <f>+D22+1</f>
-        <v>45952</v>
+        <v>45980</v>
       </c>
       <c r="F22" s="8">
         <f t="shared" ref="F22:G22" si="8">+E22+1</f>
-        <v>45953</v>
+        <v>45981</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="8"/>
-        <v>45954</v>
+        <v>45982</v>
       </c>
       <c r="H22" s="8">
         <f>+G22+3</f>
-        <v>45957</v>
+        <v>45985</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>45957.73333333333</v>
+        <v>45966.51666666667</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -2118,26 +1976,11 @@
       </c>
       <c r="C23" s="11">
         <f>+SUM(D23:H23)</f>
-        <v>267</v>
-      </c>
-      <c r="D23">
-        <v>55</v>
-      </c>
-      <c r="E23">
-        <v>55</v>
-      </c>
-      <c r="F23">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>48</v>
-      </c>
-      <c r="H23">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I23" s="26">
         <f>IFERROR(C23/6/COUNT(D23:H23),0)</f>
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3"/>
     </row>
@@ -2150,26 +1993,11 @@
       </c>
       <c r="C24" s="11">
         <f t="shared" ref="C24:C28" si="9">+SUM(D24:H24)</f>
-        <v>302</v>
-      </c>
-      <c r="D24">
-        <v>58</v>
-      </c>
-      <c r="E24">
-        <v>58</v>
-      </c>
-      <c r="F24">
-        <v>58</v>
-      </c>
-      <c r="G24">
-        <v>64</v>
-      </c>
-      <c r="H24">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I24" s="26">
         <f t="shared" ref="I24:I30" si="10">IFERROR(C24/6/COUNT(D24:H24),0)</f>
-        <v>10.066666666666666</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3"/>
     </row>
@@ -2182,26 +2010,11 @@
       </c>
       <c r="C25" s="11">
         <f t="shared" si="9"/>
-        <v>243</v>
-      </c>
-      <c r="D25">
-        <v>49</v>
-      </c>
-      <c r="E25">
-        <v>49</v>
-      </c>
-      <c r="F25">
-        <v>49</v>
-      </c>
-      <c r="G25">
-        <v>49</v>
-      </c>
-      <c r="H25">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I25" s="26">
         <f t="shared" si="10"/>
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3"/>
     </row>
@@ -2214,26 +2027,11 @@
       </c>
       <c r="C26" s="11">
         <f t="shared" si="9"/>
-        <v>230</v>
-      </c>
-      <c r="D26">
-        <v>46</v>
-      </c>
-      <c r="E26">
-        <v>46</v>
-      </c>
-      <c r="F26">
-        <v>46</v>
-      </c>
-      <c r="G26">
-        <v>46</v>
-      </c>
-      <c r="H26">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I26" s="26">
         <f t="shared" si="10"/>
-        <v>7.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3"/>
     </row>
@@ -2246,26 +2044,11 @@
       </c>
       <c r="C27" s="11">
         <f t="shared" si="9"/>
-        <v>186</v>
-      </c>
-      <c r="D27">
-        <v>37</v>
-      </c>
-      <c r="E27">
-        <v>37</v>
-      </c>
-      <c r="F27">
-        <v>37</v>
-      </c>
-      <c r="G27">
-        <v>31</v>
-      </c>
-      <c r="H27">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I27" s="26">
         <f t="shared" si="10"/>
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3"/>
     </row>
@@ -2278,26 +2061,11 @@
       </c>
       <c r="C28" s="11">
         <f t="shared" si="9"/>
-        <v>268</v>
-      </c>
-      <c r="D28">
-        <v>56</v>
-      </c>
-      <c r="E28">
-        <v>56</v>
-      </c>
-      <c r="F28">
-        <v>56</v>
-      </c>
-      <c r="G28">
-        <v>44</v>
-      </c>
-      <c r="H28">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I28" s="26">
         <f t="shared" si="10"/>
-        <v>8.9333333333333336</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3"/>
     </row>
@@ -2319,31 +2087,31 @@
       </c>
       <c r="C30" s="18">
         <f t="shared" ref="C30:H30" si="11">SUM(C23:C29)</f>
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="D30" s="19">
         <f t="shared" si="11"/>
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="E30" s="19">
         <f t="shared" si="11"/>
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="F30" s="19">
         <f t="shared" si="11"/>
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="G30" s="19">
         <f t="shared" si="11"/>
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="H30" s="19">
         <f t="shared" si="11"/>
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="I30" s="26">
         <f t="shared" si="10"/>
-        <v>49.866666666666667</v>
+        <v>0</v>
       </c>
       <c r="J30" s="20"/>
     </row>
@@ -2372,23 +2140,23 @@
       </c>
       <c r="D32" s="8">
         <f>+H22+1</f>
-        <v>45958</v>
+        <v>45986</v>
       </c>
       <c r="E32" s="8">
         <f>+D32+1</f>
-        <v>45959</v>
+        <v>45987</v>
       </c>
       <c r="F32" s="8">
         <f t="shared" ref="F32:G32" si="12">+E32+1</f>
-        <v>45960</v>
+        <v>45988</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="12"/>
-        <v>45961</v>
+        <v>45989</v>
       </c>
       <c r="H32" s="8">
         <f>+G32+3</f>
-        <v>45964</v>
+        <v>45992</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>3</v>
@@ -2405,18 +2173,16 @@
       </c>
       <c r="C33" s="11">
         <f>+SUM(D33:H33)</f>
-        <v>54</v>
-      </c>
-      <c r="D33" s="12">
-        <v>54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
       <c r="I33" s="26">
         <f>IFERROR(C33/6/COUNT(D33:H33),0)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3"/>
       <c r="AF33" s="27"/>
@@ -2430,18 +2196,16 @@
       </c>
       <c r="C34" s="11">
         <f t="shared" ref="C34:C38" si="13">+SUM(D34:H34)</f>
-        <v>64</v>
-      </c>
-      <c r="D34" s="12">
-        <v>64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
       <c r="I34" s="26">
         <f t="shared" ref="I34:I40" si="14">IFERROR(C34/6/COUNT(D34:H34),0)</f>
-        <v>10.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3"/>
       <c r="AF34" s="27"/>
@@ -2455,18 +2219,16 @@
       </c>
       <c r="C35" s="11">
         <f t="shared" si="13"/>
-        <v>59</v>
-      </c>
-      <c r="D35" s="12">
-        <v>59</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
       <c r="I35" s="26">
         <f t="shared" si="14"/>
-        <v>9.8333333333333339</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3"/>
       <c r="AF35" s="27"/>
@@ -2480,18 +2242,16 @@
       </c>
       <c r="C36" s="11">
         <f t="shared" si="13"/>
-        <v>50</v>
-      </c>
-      <c r="D36" s="12">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="26">
         <f t="shared" si="14"/>
-        <v>8.3333333333333339</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3"/>
       <c r="AF36" s="27"/>
@@ -2505,18 +2265,16 @@
       </c>
       <c r="C37" s="11">
         <f t="shared" si="13"/>
-        <v>44</v>
-      </c>
-      <c r="D37" s="12">
-        <v>44</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
       <c r="I37" s="26">
         <f t="shared" si="14"/>
-        <v>7.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3"/>
       <c r="AF37" s="27"/>
@@ -2530,18 +2288,16 @@
       </c>
       <c r="C38" s="11">
         <f t="shared" si="13"/>
-        <v>58</v>
-      </c>
-      <c r="D38" s="12">
-        <v>58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
       <c r="I38" s="26">
         <f t="shared" si="14"/>
-        <v>9.6666666666666661</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3"/>
       <c r="AF38" s="27"/>
@@ -2570,11 +2326,11 @@
       </c>
       <c r="C40" s="18">
         <f t="shared" ref="C40:H40" si="15">SUM(C33:C39)</f>
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="D40" s="19">
         <f t="shared" si="15"/>
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="E40" s="19">
         <f t="shared" si="15"/>
@@ -2594,7 +2350,7 @@
       </c>
       <c r="I40" s="26">
         <f t="shared" si="14"/>
-        <v>10.966666666666667</v>
+        <v>0</v>
       </c>
       <c r="J40" s="20"/>
       <c r="AF40" s="27"/>
@@ -2624,23 +2380,23 @@
       </c>
       <c r="D42" s="8">
         <f>+H32+1</f>
-        <v>45965</v>
+        <v>45993</v>
       </c>
       <c r="E42" s="8">
         <f>+D42+1</f>
-        <v>45966</v>
+        <v>45994</v>
       </c>
       <c r="F42" s="8">
         <f t="shared" ref="F42:G42" si="16">+E42+1</f>
-        <v>45967</v>
+        <v>45995</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="16"/>
-        <v>45968</v>
+        <v>45996</v>
       </c>
       <c r="H42" s="8">
         <f>+G42+3</f>
-        <v>45971</v>
+        <v>45999</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>3</v>
@@ -2902,26 +2658,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3156,26 +2892,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8039E8B4-6FF4-40F6-9FA1-E9DA9C439884}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3192,4 +2929,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D52F4BA0-4433-4B1D-8803-6E440F3554BA}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5180EEA4-8255-40E7-B53F-1ACFD26231B6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
+    <workbookView xWindow="28680" yWindow="4440" windowWidth="20730" windowHeight="11040" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
   <sheets>
     <sheet name="Estatus diario" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4731" r:id="rId2"/>
+    <pivotCache cacheId="3447" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -361,7 +361,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="58">
+  <cellStyleXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -398,6 +398,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -495,10 +496,10 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -506,7 +507,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="58">
+  <cellStyles count="59">
     <cellStyle name="Hyperlink" xfId="18" xr:uid="{B2018405-1245-4847-A253-ACF8F5BE6E28}"/>
     <cellStyle name="Moneda 2" xfId="19" xr:uid="{CEBF53AA-8B6B-4E2D-9FCD-940A0C0397D1}"/>
     <cellStyle name="Moneda 2 2" xfId="21" xr:uid="{EBFDC036-FF0B-49ED-AC3A-709715F7B82A}"/>
@@ -533,6 +534,7 @@
     <cellStyle name="Moneda 3 3" xfId="56" xr:uid="{34925A72-50E9-4BB6-AB5E-29A42278EC06}"/>
     <cellStyle name="Moneda 4" xfId="52" xr:uid="{37C3E87F-62D1-4247-9FCD-BF46D4177B38}"/>
     <cellStyle name="Moneda 4 2" xfId="57" xr:uid="{0D33716A-1B52-49C5-B03E-298B115A6242}"/>
+    <cellStyle name="Moneda 5" xfId="58" xr:uid="{3670C6D2-7DDC-4274-A607-0FB14349F8E2}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="10" xr:uid="{0B95864E-03D8-4F67-B990-2AF43328EB3C}"/>
     <cellStyle name="Normal 10 2" xfId="30" xr:uid="{7FA630B3-0C0F-4FC1-B9AD-58284DA35EB1}"/>
@@ -580,7 +582,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45966.741130555558" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45971.562244097222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -613,7 +615,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="709"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1740"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -629,32 +631,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="112"/>
+    <n v="288"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="114"/>
+    <n v="292"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="126"/>
+    <n v="311"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="88"/>
+    <n v="226"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="145"/>
+    <n v="337"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="124"/>
+    <n v="286"/>
   </r>
   <r>
     <x v="0"/>
@@ -664,7 +666,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="709"/>
+    <n v="1740"/>
   </r>
   <r>
     <x v="1"/>
@@ -870,7 +872,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="4731" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="3447" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1294,9 +1296,7 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="D3">
         <v>56</v>
@@ -1373,9 +1373,18 @@
       <c r="E3">
         <v>56</v>
       </c>
+      <c r="F3">
+        <v>56</v>
+      </c>
+      <c r="G3">
+        <v>62</v>
+      </c>
+      <c r="H3">
+        <v>58</v>
+      </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>9.3333333333333339</v>
+        <v>9.6</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -1388,17 +1397,26 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="D4">
         <v>63</v>
       </c>
       <c r="E4">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="F4">
+        <v>59</v>
+      </c>
+      <c r="G4">
+        <v>59</v>
+      </c>
+      <c r="H4">
+        <v>59</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>9.5</v>
+        <v>9.7333333333333325</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="31" t="s">
@@ -1415,7 +1433,7 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="D5">
         <v>63</v>
@@ -1423,9 +1441,18 @@
       <c r="E5">
         <v>63</v>
       </c>
+      <c r="F5">
+        <v>63</v>
+      </c>
+      <c r="G5">
+        <v>57</v>
+      </c>
+      <c r="H5">
+        <v>65</v>
+      </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>10.5</v>
+        <v>10.366666666666667</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1438,7 +1465,7 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="D6">
         <v>46</v>
@@ -1446,9 +1473,18 @@
       <c r="E6">
         <v>42</v>
       </c>
+      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>54</v>
+      </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>7.333333333333333</v>
+        <v>7.5333333333333332</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1461,7 +1497,7 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>145</v>
+        <v>337</v>
       </c>
       <c r="D7">
         <v>73</v>
@@ -1469,9 +1505,18 @@
       <c r="E7">
         <v>72</v>
       </c>
+      <c r="F7">
+        <v>72</v>
+      </c>
+      <c r="G7">
+        <v>48</v>
+      </c>
+      <c r="H7">
+        <v>72</v>
+      </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>12.083333333333334</v>
+        <v>11.233333333333333</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1484,7 +1529,7 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>124</v>
+        <v>286</v>
       </c>
       <c r="D8">
         <v>62</v>
@@ -1492,9 +1537,18 @@
       <c r="E8">
         <v>62</v>
       </c>
+      <c r="F8">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>44</v>
+      </c>
+      <c r="H8">
+        <v>62</v>
+      </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>10.333333333333334</v>
+        <v>9.5333333333333332</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1516,7 +1570,7 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>709</v>
+        <v>1740</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
@@ -1524,29 +1578,29 @@
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F10" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="G10" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>23.633333333333333</v>
+        <v>58</v>
       </c>
       <c r="J10" s="20"/>
-      <c r="O10" s="30" t="s">
+      <c r="O10" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="30" t="s">
+      <c r="P10" s="29" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1561,7 +1615,7 @@
       <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="O11" s="30" t="s">
+      <c r="O11" s="29" t="s">
         <v>15</v>
       </c>
       <c r="P11" t="s">
@@ -1620,29 +1674,29 @@
         <v>3</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="O12" s="29" t="s">
+      <c r="O12" s="30" t="s">
         <v>1</v>
       </c>
       <c r="P12" s="34">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="Q12" s="34">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="R12" s="34">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="S12" s="34">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="T12" s="34">
-        <v>145</v>
+        <v>337</v>
       </c>
       <c r="U12" s="34">
-        <v>124</v>
+        <v>286</v>
       </c>
       <c r="V12" s="34">
-        <v>709</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1661,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="O13" s="29" t="s">
+      <c r="O13" s="30" t="s">
         <v>11</v>
       </c>
       <c r="P13" s="34">
@@ -1702,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="O14" s="29" t="s">
+      <c r="O14" s="30" t="s">
         <v>12</v>
       </c>
       <c r="P14" s="34">
@@ -1743,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="O15" s="29" t="s">
+      <c r="O15" s="30" t="s">
         <v>13</v>
       </c>
       <c r="P15" s="34">
@@ -1784,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="O16" s="29" t="s">
+      <c r="O16" s="30" t="s">
         <v>14</v>
       </c>
       <c r="P16" s="34">
@@ -1825,29 +1879,29 @@
         <v>0</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="O17" s="29" t="s">
+      <c r="O17" s="30" t="s">
         <v>16</v>
       </c>
       <c r="P17" s="34">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="Q17" s="34">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="R17" s="34">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="S17" s="34">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="T17" s="34">
-        <v>145</v>
+        <v>337</v>
       </c>
       <c r="U17" s="34">
-        <v>124</v>
+        <v>286</v>
       </c>
       <c r="V17" s="34">
-        <v>709</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -1964,7 +2018,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>45966.51666666667</v>
+        <v>45968.718055555553</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -2893,15 +2947,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -2910,6 +2955,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2932,14 +2986,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2948,4 +2994,12 @@
     <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5180EEA4-8255-40E7-B53F-1ACFD26231B6}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7DD2CE-27A9-4B53-8730-FA9BD08B419F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="4440" windowWidth="20730" windowHeight="11040" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
   <sheets>
     <sheet name="Estatus diario" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3447" r:id="rId2"/>
+    <pivotCache cacheId="5" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -114,9 +114,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -361,7 +362,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="59">
+  <cellStyleXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -421,8 +422,13 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -493,23 +499,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="59">
+  <cellStyles count="64">
     <cellStyle name="Hyperlink" xfId="18" xr:uid="{B2018405-1245-4847-A253-ACF8F5BE6E28}"/>
     <cellStyle name="Moneda 2" xfId="19" xr:uid="{CEBF53AA-8B6B-4E2D-9FCD-940A0C0397D1}"/>
+    <cellStyle name="Moneda 2 10" xfId="59" xr:uid="{FDF75B95-A597-4585-8A7D-1645B69538BC}"/>
     <cellStyle name="Moneda 2 2" xfId="21" xr:uid="{EBFDC036-FF0B-49ED-AC3A-709715F7B82A}"/>
     <cellStyle name="Moneda 2 2 2" xfId="37" xr:uid="{CC7FC404-D3BE-4275-A513-2A476E6F003A}"/>
     <cellStyle name="Moneda 2 2 3" xfId="40" xr:uid="{F05178DD-0970-4BBD-B557-6633C9B3DA72}"/>
@@ -517,12 +526,14 @@
     <cellStyle name="Moneda 2 2 5" xfId="46" xr:uid="{E0C5F919-636E-4F9D-8793-F35F305CE8A8}"/>
     <cellStyle name="Moneda 2 2 6" xfId="50" xr:uid="{060513CE-1E51-4AF2-BED2-3308E7A5528F}"/>
     <cellStyle name="Moneda 2 2 7" xfId="55" xr:uid="{94A23887-FE88-4793-9FDA-92C9211068DD}"/>
+    <cellStyle name="Moneda 2 2 8" xfId="61" xr:uid="{49063416-6398-4A1E-BD9F-012E3656CEF7}"/>
     <cellStyle name="Moneda 2 3" xfId="36" xr:uid="{1215ABD4-5220-487B-89B5-AA885EAB04A5}"/>
     <cellStyle name="Moneda 2 3 2" xfId="39" xr:uid="{3420C6FC-40C3-4347-8915-5E37D4F27C66}"/>
     <cellStyle name="Moneda 2 3 3" xfId="42" xr:uid="{7BE246B1-3564-4109-A03A-9C159034B353}"/>
     <cellStyle name="Moneda 2 3 4" xfId="45" xr:uid="{C537BDE2-9AB6-4E9B-9408-C3A95636E5DD}"/>
     <cellStyle name="Moneda 2 3 5" xfId="49" xr:uid="{A5551541-CFD7-4A26-9869-71C8BCD7753D}"/>
     <cellStyle name="Moneda 2 3 6" xfId="54" xr:uid="{D8E5DCCD-1ADF-400D-B378-83D66EE3168E}"/>
+    <cellStyle name="Moneda 2 3 7" xfId="60" xr:uid="{F5F4C5BE-7CED-4B09-A44C-DC609CCE0C51}"/>
     <cellStyle name="Moneda 2 4" xfId="22" xr:uid="{C856720B-E8A6-4AC5-AB83-CF98E3EF83EE}"/>
     <cellStyle name="Moneda 2 5" xfId="38" xr:uid="{543CB192-C6A7-4F18-96D2-D078B55A61CB}"/>
     <cellStyle name="Moneda 2 6" xfId="41" xr:uid="{14D1D7A7-6BF3-4644-A820-240992FDB63E}"/>
@@ -532,8 +543,10 @@
     <cellStyle name="Moneda 3" xfId="47" xr:uid="{85CAFDD7-BC80-42AB-AB19-AD3F8539702F}"/>
     <cellStyle name="Moneda 3 2" xfId="51" xr:uid="{96C4286F-DBE0-4288-BB74-90F8B138EA6D}"/>
     <cellStyle name="Moneda 3 3" xfId="56" xr:uid="{34925A72-50E9-4BB6-AB5E-29A42278EC06}"/>
+    <cellStyle name="Moneda 3 4" xfId="62" xr:uid="{2CBB34AE-A901-454F-8B45-5C34D3D6C141}"/>
     <cellStyle name="Moneda 4" xfId="52" xr:uid="{37C3E87F-62D1-4247-9FCD-BF46D4177B38}"/>
     <cellStyle name="Moneda 4 2" xfId="57" xr:uid="{0D33716A-1B52-49C5-B03E-298B115A6242}"/>
+    <cellStyle name="Moneda 4 3" xfId="63" xr:uid="{ED1C5CE2-B4BC-4A3D-AB59-9C0356444D01}"/>
     <cellStyle name="Moneda 5" xfId="58" xr:uid="{3670C6D2-7DDC-4274-A607-0FB14349F8E2}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="10" xr:uid="{0B95864E-03D8-4F67-B990-2AF43328EB3C}"/>
@@ -582,7 +595,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45971.562244097222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45972.522349074075" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -681,32 +694,32 @@
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="0"/>
+    <n v="58"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
-    <n v="0"/>
+    <n v="62"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <n v="0"/>
+    <n v="65"/>
   </r>
   <r>
     <x v="2"/>
     <x v="3"/>
-    <n v="0"/>
+    <n v="54"/>
   </r>
   <r>
     <x v="2"/>
     <x v="4"/>
-    <n v="0"/>
+    <n v="72"/>
   </r>
   <r>
     <x v="2"/>
     <x v="5"/>
-    <n v="0"/>
+    <n v="66"/>
   </r>
   <r>
     <x v="2"/>
@@ -716,7 +729,7 @@
   <r>
     <x v="2"/>
     <x v="7"/>
-    <n v="0"/>
+    <n v="377"/>
   </r>
   <r>
     <x v="1"/>
@@ -872,7 +885,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="3447" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1419,10 +1432,10 @@
         <v>9.7333333333333325</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="31"/>
+      <c r="P4" s="28"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
@@ -1597,10 +1610,10 @@
         <v>58</v>
       </c>
       <c r="J10" s="20"/>
-      <c r="O10" s="29" t="s">
+      <c r="O10" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="29" t="s">
+      <c r="P10" s="35" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1615,28 +1628,28 @@
       <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="O11" s="29" t="s">
+      <c r="O11" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="S11" t="s">
+      <c r="S11" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="U11" t="s">
+      <c r="U11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="V11" t="s">
+      <c r="V11" s="32" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1674,28 +1687,28 @@
         <v>3</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="36">
         <v>288</v>
       </c>
-      <c r="Q12" s="34">
+      <c r="Q12" s="36">
         <v>292</v>
       </c>
-      <c r="R12" s="34">
+      <c r="R12" s="36">
         <v>311</v>
       </c>
-      <c r="S12" s="34">
+      <c r="S12" s="36">
         <v>226</v>
       </c>
-      <c r="T12" s="34">
+      <c r="T12" s="36">
         <v>337</v>
       </c>
-      <c r="U12" s="34">
+      <c r="U12" s="36">
         <v>286</v>
       </c>
-      <c r="V12" s="34">
+      <c r="V12" s="36">
         <v>1740</v>
       </c>
     </row>
@@ -1708,36 +1721,39 @@
       </c>
       <c r="C13" s="11">
         <f>+SUM(D13:H13)</f>
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="D13" s="31">
+        <v>58</v>
       </c>
       <c r="I13" s="26">
         <f>IFERROR(C13/6/COUNT(D13:H13),0)</f>
-        <v>0</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="O13" s="30" t="s">
+      <c r="O13" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="34">
-        <v>0</v>
-      </c>
-      <c r="R13" s="34">
-        <v>0</v>
-      </c>
-      <c r="S13" s="34">
-        <v>0</v>
-      </c>
-      <c r="T13" s="34">
-        <v>0</v>
-      </c>
-      <c r="U13" s="34">
-        <v>0</v>
-      </c>
-      <c r="V13" s="34">
-        <v>0</v>
+      <c r="P13" s="36">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="36">
+        <v>62</v>
+      </c>
+      <c r="R13" s="36">
+        <v>65</v>
+      </c>
+      <c r="S13" s="36">
+        <v>54</v>
+      </c>
+      <c r="T13" s="36">
+        <v>72</v>
+      </c>
+      <c r="U13" s="36">
+        <v>66</v>
+      </c>
+      <c r="V13" s="36">
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1749,35 +1765,38 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" ref="C14:C18" si="5">+SUM(D14:H14)</f>
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="D14" s="31">
+        <v>62</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" ref="I14:I20" si="6">IFERROR(C14/6/COUNT(D14:H14),0)</f>
-        <v>0</v>
+        <v>10.333333333333334</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="O14" s="30" t="s">
+      <c r="O14" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="34">
-        <v>0</v>
-      </c>
-      <c r="R14" s="34">
-        <v>0</v>
-      </c>
-      <c r="S14" s="34">
-        <v>0</v>
-      </c>
-      <c r="T14" s="34">
-        <v>0</v>
-      </c>
-      <c r="U14" s="34">
-        <v>0</v>
-      </c>
-      <c r="V14" s="34">
+      <c r="P14" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="36">
+        <v>0</v>
+      </c>
+      <c r="R14" s="36">
+        <v>0</v>
+      </c>
+      <c r="S14" s="36">
+        <v>0</v>
+      </c>
+      <c r="T14" s="36">
+        <v>0</v>
+      </c>
+      <c r="U14" s="36">
+        <v>0</v>
+      </c>
+      <c r="V14" s="36">
         <v>0</v>
       </c>
     </row>
@@ -1790,35 +1809,38 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="D15" s="31">
+        <v>65</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10.833333333333334</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="O15" s="30" t="s">
+      <c r="O15" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="P15" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="34">
-        <v>0</v>
-      </c>
-      <c r="R15" s="34">
-        <v>0</v>
-      </c>
-      <c r="S15" s="34">
-        <v>0</v>
-      </c>
-      <c r="T15" s="34">
-        <v>0</v>
-      </c>
-      <c r="U15" s="34">
-        <v>0</v>
-      </c>
-      <c r="V15" s="34">
+      <c r="P15" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="36">
+        <v>0</v>
+      </c>
+      <c r="R15" s="36">
+        <v>0</v>
+      </c>
+      <c r="S15" s="36">
+        <v>0</v>
+      </c>
+      <c r="T15" s="36">
+        <v>0</v>
+      </c>
+      <c r="U15" s="36">
+        <v>0</v>
+      </c>
+      <c r="V15" s="36">
         <v>0</v>
       </c>
     </row>
@@ -1831,35 +1853,38 @@
       </c>
       <c r="C16" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>54</v>
+      </c>
+      <c r="D16" s="31">
+        <v>54</v>
       </c>
       <c r="I16" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="O16" s="30" t="s">
+      <c r="O16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="34">
-        <v>0</v>
-      </c>
-      <c r="R16" s="34">
-        <v>0</v>
-      </c>
-      <c r="S16" s="34">
-        <v>0</v>
-      </c>
-      <c r="T16" s="34">
-        <v>0</v>
-      </c>
-      <c r="U16" s="34">
-        <v>0</v>
-      </c>
-      <c r="V16" s="34">
+      <c r="P16" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="36">
+        <v>0</v>
+      </c>
+      <c r="R16" s="36">
+        <v>0</v>
+      </c>
+      <c r="S16" s="36">
+        <v>0</v>
+      </c>
+      <c r="T16" s="36">
+        <v>0</v>
+      </c>
+      <c r="U16" s="36">
+        <v>0</v>
+      </c>
+      <c r="V16" s="36">
         <v>0</v>
       </c>
     </row>
@@ -1872,36 +1897,39 @@
       </c>
       <c r="C17" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="D17" s="31">
+        <v>72</v>
       </c>
       <c r="I17" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="O17" s="30" t="s">
+      <c r="O17" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="34">
-        <v>288</v>
-      </c>
-      <c r="Q17" s="34">
-        <v>292</v>
-      </c>
-      <c r="R17" s="34">
-        <v>311</v>
-      </c>
-      <c r="S17" s="34">
-        <v>226</v>
-      </c>
-      <c r="T17" s="34">
-        <v>337</v>
-      </c>
-      <c r="U17" s="34">
-        <v>286</v>
-      </c>
-      <c r="V17" s="34">
-        <v>1740</v>
+      <c r="P17" s="36">
+        <v>346</v>
+      </c>
+      <c r="Q17" s="36">
+        <v>354</v>
+      </c>
+      <c r="R17" s="36">
+        <v>376</v>
+      </c>
+      <c r="S17" s="36">
+        <v>280</v>
+      </c>
+      <c r="T17" s="36">
+        <v>409</v>
+      </c>
+      <c r="U17" s="36">
+        <v>352</v>
+      </c>
+      <c r="V17" s="36">
+        <v>2117</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
@@ -1913,11 +1941,14 @@
       </c>
       <c r="C18" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="D18" s="31">
+        <v>66</v>
       </c>
       <c r="I18" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -1939,11 +1970,11 @@
       </c>
       <c r="C20" s="18">
         <f>SUM(C13:C19)</f>
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="D20" s="19">
         <f>SUM(D13:D19)</f>
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" ref="E20:H20" si="7">SUM(E13:E19)</f>
@@ -1963,13 +1994,13 @@
       </c>
       <c r="I20" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12.566666666666666</v>
       </c>
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -1978,10 +2009,10 @@
       <c r="H21" s="21"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="31"/>
+      <c r="P21" s="28"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
@@ -2017,8 +2048,8 @@
         <v>3</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="O22" s="28">
-        <v>45968.718055555553</v>
+      <c r="O22" s="34">
+        <v>45971.515277777777</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -2170,8 +2201,8 @@
       <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2410,8 +2441,8 @@
       <c r="AF40" s="27"/>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2650,8 +2681,8 @@
       <c r="AF50" s="27"/>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
       <c r="C51" s="2"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
@@ -2663,8 +2694,8 @@
       <c r="AF51" s="27"/>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21">
         <v>0</v>
@@ -2685,8 +2716,8 @@
       <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2712,6 +2743,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -2946,17 +2988,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2967,6 +2998,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8039E8B4-6FF4-40F6-9FA1-E9DA9C439884}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2985,17 +3027,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A7DD2CE-27A9-4B53-8730-FA9BD08B419F}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0158A4-8174-497B-AFE3-255F1DB4E23A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -362,7 +362,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="64">
+  <cellStyleXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -422,13 +422,18 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -504,7 +509,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -513,12 +518,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="64">
+  <cellStyles count="69">
     <cellStyle name="Hyperlink" xfId="18" xr:uid="{B2018405-1245-4847-A253-ACF8F5BE6E28}"/>
     <cellStyle name="Moneda 2" xfId="19" xr:uid="{CEBF53AA-8B6B-4E2D-9FCD-940A0C0397D1}"/>
     <cellStyle name="Moneda 2 10" xfId="59" xr:uid="{FDF75B95-A597-4585-8A7D-1645B69538BC}"/>
+    <cellStyle name="Moneda 2 11" xfId="64" xr:uid="{733FA569-27EB-4B97-8F71-9F2702548B08}"/>
     <cellStyle name="Moneda 2 2" xfId="21" xr:uid="{EBFDC036-FF0B-49ED-AC3A-709715F7B82A}"/>
     <cellStyle name="Moneda 2 2 2" xfId="37" xr:uid="{CC7FC404-D3BE-4275-A513-2A476E6F003A}"/>
     <cellStyle name="Moneda 2 2 3" xfId="40" xr:uid="{F05178DD-0970-4BBD-B557-6633C9B3DA72}"/>
@@ -527,6 +532,7 @@
     <cellStyle name="Moneda 2 2 6" xfId="50" xr:uid="{060513CE-1E51-4AF2-BED2-3308E7A5528F}"/>
     <cellStyle name="Moneda 2 2 7" xfId="55" xr:uid="{94A23887-FE88-4793-9FDA-92C9211068DD}"/>
     <cellStyle name="Moneda 2 2 8" xfId="61" xr:uid="{49063416-6398-4A1E-BD9F-012E3656CEF7}"/>
+    <cellStyle name="Moneda 2 2 9" xfId="66" xr:uid="{A08EDAF3-8B31-4980-9755-F9731E0076E3}"/>
     <cellStyle name="Moneda 2 3" xfId="36" xr:uid="{1215ABD4-5220-487B-89B5-AA885EAB04A5}"/>
     <cellStyle name="Moneda 2 3 2" xfId="39" xr:uid="{3420C6FC-40C3-4347-8915-5E37D4F27C66}"/>
     <cellStyle name="Moneda 2 3 3" xfId="42" xr:uid="{7BE246B1-3564-4109-A03A-9C159034B353}"/>
@@ -534,6 +540,7 @@
     <cellStyle name="Moneda 2 3 5" xfId="49" xr:uid="{A5551541-CFD7-4A26-9869-71C8BCD7753D}"/>
     <cellStyle name="Moneda 2 3 6" xfId="54" xr:uid="{D8E5DCCD-1ADF-400D-B378-83D66EE3168E}"/>
     <cellStyle name="Moneda 2 3 7" xfId="60" xr:uid="{F5F4C5BE-7CED-4B09-A44C-DC609CCE0C51}"/>
+    <cellStyle name="Moneda 2 3 8" xfId="65" xr:uid="{29D3C733-4371-485E-8502-AA4779581B3E}"/>
     <cellStyle name="Moneda 2 4" xfId="22" xr:uid="{C856720B-E8A6-4AC5-AB83-CF98E3EF83EE}"/>
     <cellStyle name="Moneda 2 5" xfId="38" xr:uid="{543CB192-C6A7-4F18-96D2-D078B55A61CB}"/>
     <cellStyle name="Moneda 2 6" xfId="41" xr:uid="{14D1D7A7-6BF3-4644-A820-240992FDB63E}"/>
@@ -544,9 +551,11 @@
     <cellStyle name="Moneda 3 2" xfId="51" xr:uid="{96C4286F-DBE0-4288-BB74-90F8B138EA6D}"/>
     <cellStyle name="Moneda 3 3" xfId="56" xr:uid="{34925A72-50E9-4BB6-AB5E-29A42278EC06}"/>
     <cellStyle name="Moneda 3 4" xfId="62" xr:uid="{2CBB34AE-A901-454F-8B45-5C34D3D6C141}"/>
+    <cellStyle name="Moneda 3 5" xfId="67" xr:uid="{3FFD3DD0-5204-47D9-B534-A50AAA72ACB7}"/>
     <cellStyle name="Moneda 4" xfId="52" xr:uid="{37C3E87F-62D1-4247-9FCD-BF46D4177B38}"/>
     <cellStyle name="Moneda 4 2" xfId="57" xr:uid="{0D33716A-1B52-49C5-B03E-298B115A6242}"/>
     <cellStyle name="Moneda 4 3" xfId="63" xr:uid="{ED1C5CE2-B4BC-4A3D-AB59-9C0356444D01}"/>
+    <cellStyle name="Moneda 4 4" xfId="68" xr:uid="{A8A598A9-970D-47DC-B1E1-29E7D47DD090}"/>
     <cellStyle name="Moneda 5" xfId="58" xr:uid="{3670C6D2-7DDC-4274-A607-0FB14349F8E2}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="10" xr:uid="{0B95864E-03D8-4F67-B990-2AF43328EB3C}"/>
@@ -595,7 +604,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45972.522349074075" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45972.748491435188" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1690,25 +1699,25 @@
       <c r="O12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="P12" s="36">
+      <c r="P12" s="31">
         <v>288</v>
       </c>
-      <c r="Q12" s="36">
+      <c r="Q12" s="31">
         <v>292</v>
       </c>
-      <c r="R12" s="36">
+      <c r="R12" s="31">
         <v>311</v>
       </c>
-      <c r="S12" s="36">
+      <c r="S12" s="31">
         <v>226</v>
       </c>
-      <c r="T12" s="36">
+      <c r="T12" s="31">
         <v>337</v>
       </c>
-      <c r="U12" s="36">
+      <c r="U12" s="31">
         <v>286</v>
       </c>
-      <c r="V12" s="36">
+      <c r="V12" s="31">
         <v>1740</v>
       </c>
     </row>
@@ -1723,7 +1732,7 @@
         <f>+SUM(D13:H13)</f>
         <v>58</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13">
         <v>58</v>
       </c>
       <c r="I13" s="26">
@@ -1734,25 +1743,25 @@
       <c r="O13" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="36">
+      <c r="P13" s="31">
         <v>58</v>
       </c>
-      <c r="Q13" s="36">
+      <c r="Q13" s="31">
         <v>62</v>
       </c>
-      <c r="R13" s="36">
+      <c r="R13" s="31">
         <v>65</v>
       </c>
-      <c r="S13" s="36">
+      <c r="S13" s="31">
         <v>54</v>
       </c>
-      <c r="T13" s="36">
+      <c r="T13" s="31">
         <v>72</v>
       </c>
-      <c r="U13" s="36">
+      <c r="U13" s="31">
         <v>66</v>
       </c>
-      <c r="V13" s="36">
+      <c r="V13" s="31">
         <v>377</v>
       </c>
     </row>
@@ -1767,7 +1776,7 @@
         <f t="shared" ref="C14:C18" si="5">+SUM(D14:H14)</f>
         <v>62</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14">
         <v>62</v>
       </c>
       <c r="I14" s="26">
@@ -1778,25 +1787,25 @@
       <c r="O14" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="36">
-        <v>0</v>
-      </c>
-      <c r="R14" s="36">
-        <v>0</v>
-      </c>
-      <c r="S14" s="36">
-        <v>0</v>
-      </c>
-      <c r="T14" s="36">
-        <v>0</v>
-      </c>
-      <c r="U14" s="36">
-        <v>0</v>
-      </c>
-      <c r="V14" s="36">
+      <c r="P14" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="31">
+        <v>0</v>
+      </c>
+      <c r="R14" s="31">
+        <v>0</v>
+      </c>
+      <c r="S14" s="31">
+        <v>0</v>
+      </c>
+      <c r="T14" s="31">
+        <v>0</v>
+      </c>
+      <c r="U14" s="31">
+        <v>0</v>
+      </c>
+      <c r="V14" s="31">
         <v>0</v>
       </c>
     </row>
@@ -1811,7 +1820,7 @@
         <f t="shared" si="5"/>
         <v>65</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15">
         <v>65</v>
       </c>
       <c r="I15" s="26">
@@ -1822,25 +1831,25 @@
       <c r="O15" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="P15" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36">
-        <v>0</v>
-      </c>
-      <c r="R15" s="36">
-        <v>0</v>
-      </c>
-      <c r="S15" s="36">
-        <v>0</v>
-      </c>
-      <c r="T15" s="36">
-        <v>0</v>
-      </c>
-      <c r="U15" s="36">
-        <v>0</v>
-      </c>
-      <c r="V15" s="36">
+      <c r="P15" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="31">
+        <v>0</v>
+      </c>
+      <c r="R15" s="31">
+        <v>0</v>
+      </c>
+      <c r="S15" s="31">
+        <v>0</v>
+      </c>
+      <c r="T15" s="31">
+        <v>0</v>
+      </c>
+      <c r="U15" s="31">
+        <v>0</v>
+      </c>
+      <c r="V15" s="31">
         <v>0</v>
       </c>
     </row>
@@ -1855,7 +1864,7 @@
         <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16">
         <v>54</v>
       </c>
       <c r="I16" s="26">
@@ -1866,25 +1875,25 @@
       <c r="O16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <v>0</v>
-      </c>
-      <c r="R16" s="36">
-        <v>0</v>
-      </c>
-      <c r="S16" s="36">
-        <v>0</v>
-      </c>
-      <c r="T16" s="36">
-        <v>0</v>
-      </c>
-      <c r="U16" s="36">
-        <v>0</v>
-      </c>
-      <c r="V16" s="36">
+      <c r="P16" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="31">
+        <v>0</v>
+      </c>
+      <c r="R16" s="31">
+        <v>0</v>
+      </c>
+      <c r="S16" s="31">
+        <v>0</v>
+      </c>
+      <c r="T16" s="31">
+        <v>0</v>
+      </c>
+      <c r="U16" s="31">
+        <v>0</v>
+      </c>
+      <c r="V16" s="31">
         <v>0</v>
       </c>
     </row>
@@ -1899,7 +1908,7 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17">
         <v>72</v>
       </c>
       <c r="I17" s="26">
@@ -1910,25 +1919,25 @@
       <c r="O17" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="36">
+      <c r="P17" s="31">
         <v>346</v>
       </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="31">
         <v>354</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="31">
         <v>376</v>
       </c>
-      <c r="S17" s="36">
+      <c r="S17" s="31">
         <v>280</v>
       </c>
-      <c r="T17" s="36">
+      <c r="T17" s="31">
         <v>409</v>
       </c>
-      <c r="U17" s="36">
+      <c r="U17" s="31">
         <v>352</v>
       </c>
-      <c r="V17" s="36">
+      <c r="V17" s="31">
         <v>2117</v>
       </c>
     </row>
@@ -1943,7 +1952,7 @@
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18">
         <v>66</v>
       </c>
       <c r="I18" s="26">
@@ -2049,7 +2058,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="34">
-        <v>45971.515277777777</v>
+        <v>45972.513194444444</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
@@ -2743,17 +2752,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -2988,6 +2986,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2998,17 +3007,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8039E8B4-6FF4-40F6-9FA1-E9DA9C439884}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3027,6 +3025,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0158A4-8174-497B-AFE3-255F1DB4E23A}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417CE98F-DC79-4302-A893-B76A9B1BB777}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId2"/>
+    <pivotCache cacheId="274" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -114,12 +114,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,8 +232,138 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,8 +406,181 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -361,8 +663,115 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="69">
+  <cellStyleXfs count="255">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -427,13 +836,199 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -504,59 +1099,237 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
-  <cellStyles count="69">
+  <cellStyles count="255">
+    <cellStyle name="20% - Énfasis1" xfId="184" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="188" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="192" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="196" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="200" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="204" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="185" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="189" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="193" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="197" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="201" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="205" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="186" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="190" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="194" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="198" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="202" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="206" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="171" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="176" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="178" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="177" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="167" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="170" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="183" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="187" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="191" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="195" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="199" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="203" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="174" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="18" xr:uid="{B2018405-1245-4847-A253-ACF8F5BE6E28}"/>
+    <cellStyle name="Incorrecto" xfId="172" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Moneda 2" xfId="19" xr:uid="{CEBF53AA-8B6B-4E2D-9FCD-940A0C0397D1}"/>
     <cellStyle name="Moneda 2 10" xfId="59" xr:uid="{FDF75B95-A597-4585-8A7D-1645B69538BC}"/>
+    <cellStyle name="Moneda 2 10 2" xfId="105" xr:uid="{EC109079-E88F-4EBC-BA51-0F55F0012AAA}"/>
+    <cellStyle name="Moneda 2 10 3" xfId="151" xr:uid="{CC924310-31DA-4300-90F2-D39F2C529DF4}"/>
+    <cellStyle name="Moneda 2 10 4" xfId="238" xr:uid="{830C5F1F-837E-476B-AC4B-2430F822591A}"/>
     <cellStyle name="Moneda 2 11" xfId="64" xr:uid="{733FA569-27EB-4B97-8F71-9F2702548B08}"/>
+    <cellStyle name="Moneda 2 11 2" xfId="110" xr:uid="{25D37EC2-C0F0-439A-84B1-9F07511977A9}"/>
+    <cellStyle name="Moneda 2 11 3" xfId="156" xr:uid="{85446705-B7C3-4FC5-AC58-950A1162D64D}"/>
+    <cellStyle name="Moneda 2 11 4" xfId="243" xr:uid="{1DF776D6-58E9-4FD7-B167-54CF363D54C0}"/>
+    <cellStyle name="Moneda 2 12" xfId="69" xr:uid="{033D24C2-CEBB-4FC5-A4C0-7404A5F207C3}"/>
+    <cellStyle name="Moneda 2 12 2" xfId="115" xr:uid="{B70301D3-5E35-4972-AF54-A43466A75284}"/>
+    <cellStyle name="Moneda 2 12 3" xfId="161" xr:uid="{4F1ACD12-6748-4AEF-905D-79FE42340EB0}"/>
+    <cellStyle name="Moneda 2 12 4" xfId="248" xr:uid="{FE725EAA-25C6-4977-AC7D-92B74FFE9366}"/>
+    <cellStyle name="Moneda 2 13" xfId="79" xr:uid="{E7B2FE90-A322-4407-AF6E-3C797FE973CA}"/>
+    <cellStyle name="Moneda 2 13 2" xfId="125" xr:uid="{B4C13C6D-C18C-482A-BA72-CB6AF979BBC8}"/>
+    <cellStyle name="Moneda 2 13 3" xfId="212" xr:uid="{49EEF507-F7FF-4F6A-B172-C1724AB4FC29}"/>
+    <cellStyle name="Moneda 2 14" xfId="74" xr:uid="{45BE0D07-B9A8-4064-94DB-D20AF1E0C4D0}"/>
+    <cellStyle name="Moneda 2 15" xfId="120" xr:uid="{48B5C7BB-EAA1-4983-80A6-6DB1BDEB2305}"/>
+    <cellStyle name="Moneda 2 16" xfId="207" xr:uid="{C7E238F2-6DB0-47E6-9D6A-2FD41B2C8E92}"/>
     <cellStyle name="Moneda 2 2" xfId="21" xr:uid="{EBFDC036-FF0B-49ED-AC3A-709715F7B82A}"/>
+    <cellStyle name="Moneda 2 2 10" xfId="71" xr:uid="{5DDC46D0-842C-4A2E-92E8-ABD6AD2AAA1B}"/>
+    <cellStyle name="Moneda 2 2 10 2" xfId="117" xr:uid="{960E80FF-4C72-481C-B563-7016118359F3}"/>
+    <cellStyle name="Moneda 2 2 10 3" xfId="163" xr:uid="{64FD41C9-235A-40AC-A4D8-171C7342486B}"/>
+    <cellStyle name="Moneda 2 2 10 4" xfId="250" xr:uid="{11947B10-CB33-4D7F-A33F-052322AE9486}"/>
+    <cellStyle name="Moneda 2 2 11" xfId="80" xr:uid="{1AFA96EE-ADFB-46F6-AFF7-84204B421FA8}"/>
+    <cellStyle name="Moneda 2 2 11 2" xfId="126" xr:uid="{02884BCA-0787-40C1-ABD4-B7905AA874CC}"/>
+    <cellStyle name="Moneda 2 2 11 3" xfId="213" xr:uid="{86C7BD59-388B-482F-B3C1-9811B734512C}"/>
+    <cellStyle name="Moneda 2 2 12" xfId="76" xr:uid="{E3478D81-419E-4796-9D51-DA114F8D2C71}"/>
+    <cellStyle name="Moneda 2 2 13" xfId="122" xr:uid="{731D2916-217E-4669-AFED-472E473A1648}"/>
+    <cellStyle name="Moneda 2 2 14" xfId="209" xr:uid="{3A471E74-A74D-4314-A42E-9CD3371195ED}"/>
     <cellStyle name="Moneda 2 2 2" xfId="37" xr:uid="{CC7FC404-D3BE-4275-A513-2A476E6F003A}"/>
+    <cellStyle name="Moneda 2 2 2 2" xfId="83" xr:uid="{2B5DCB4A-E3BC-4992-B73E-D561B5F63554}"/>
+    <cellStyle name="Moneda 2 2 2 3" xfId="129" xr:uid="{9450676A-C05C-4D12-BED3-C60386F06150}"/>
+    <cellStyle name="Moneda 2 2 2 4" xfId="216" xr:uid="{9C268655-4231-4B29-9ED4-6A0B600F606C}"/>
     <cellStyle name="Moneda 2 2 3" xfId="40" xr:uid="{F05178DD-0970-4BBD-B557-6633C9B3DA72}"/>
+    <cellStyle name="Moneda 2 2 3 2" xfId="86" xr:uid="{C9137B14-5840-498A-AE7C-D82E04F564B4}"/>
+    <cellStyle name="Moneda 2 2 3 3" xfId="132" xr:uid="{9F23760D-D4E5-4CA6-8A1D-5E62D0E84756}"/>
+    <cellStyle name="Moneda 2 2 3 4" xfId="219" xr:uid="{96B37EBD-0D01-4617-9047-A58FD45F8724}"/>
     <cellStyle name="Moneda 2 2 4" xfId="43" xr:uid="{B1D1D8B7-FFC4-44C3-A297-D56D6135BA6B}"/>
+    <cellStyle name="Moneda 2 2 4 2" xfId="89" xr:uid="{87C20372-0BCB-4D10-BF74-8578B62A332F}"/>
+    <cellStyle name="Moneda 2 2 4 3" xfId="135" xr:uid="{1C58CE7E-BB98-4DE5-B62D-5AFFAD89DEDF}"/>
+    <cellStyle name="Moneda 2 2 4 4" xfId="222" xr:uid="{0B684038-DB80-4159-BB65-A9C33CB85C6D}"/>
     <cellStyle name="Moneda 2 2 5" xfId="46" xr:uid="{E0C5F919-636E-4F9D-8793-F35F305CE8A8}"/>
+    <cellStyle name="Moneda 2 2 5 2" xfId="92" xr:uid="{2295E829-7422-40C0-936A-2498C625B8CA}"/>
+    <cellStyle name="Moneda 2 2 5 3" xfId="138" xr:uid="{00DE2E34-0A4F-4477-8712-2AA8148E7B07}"/>
+    <cellStyle name="Moneda 2 2 5 4" xfId="225" xr:uid="{020629BF-CD7E-4F39-9DDB-FA6B6597B973}"/>
     <cellStyle name="Moneda 2 2 6" xfId="50" xr:uid="{060513CE-1E51-4AF2-BED2-3308E7A5528F}"/>
+    <cellStyle name="Moneda 2 2 6 2" xfId="96" xr:uid="{8980EDDE-FAB1-4D17-A547-1E4AC662111E}"/>
+    <cellStyle name="Moneda 2 2 6 3" xfId="142" xr:uid="{B10B84A8-1070-4A7A-888C-663EE2298782}"/>
+    <cellStyle name="Moneda 2 2 6 4" xfId="229" xr:uid="{5D7B8547-C1F5-467D-B96A-6CC67AB320F6}"/>
     <cellStyle name="Moneda 2 2 7" xfId="55" xr:uid="{94A23887-FE88-4793-9FDA-92C9211068DD}"/>
+    <cellStyle name="Moneda 2 2 7 2" xfId="101" xr:uid="{2171A9C0-9E4E-4E9D-BEFF-4EDAF9750199}"/>
+    <cellStyle name="Moneda 2 2 7 3" xfId="147" xr:uid="{0AE522F1-FB55-43FD-A794-C5E3F3059E69}"/>
+    <cellStyle name="Moneda 2 2 7 4" xfId="234" xr:uid="{15F7D30F-479D-46A3-A95C-E57FC7127380}"/>
     <cellStyle name="Moneda 2 2 8" xfId="61" xr:uid="{49063416-6398-4A1E-BD9F-012E3656CEF7}"/>
+    <cellStyle name="Moneda 2 2 8 2" xfId="107" xr:uid="{8F3774A5-B9F6-4398-94C1-5484F962B184}"/>
+    <cellStyle name="Moneda 2 2 8 3" xfId="153" xr:uid="{D5E74BFB-237B-4194-9841-8A55B2E00591}"/>
+    <cellStyle name="Moneda 2 2 8 4" xfId="240" xr:uid="{464980FD-9027-4E44-9377-F10F03930B67}"/>
     <cellStyle name="Moneda 2 2 9" xfId="66" xr:uid="{A08EDAF3-8B31-4980-9755-F9731E0076E3}"/>
+    <cellStyle name="Moneda 2 2 9 2" xfId="112" xr:uid="{CC9101B4-3453-4D5F-B5BA-41D03BF78857}"/>
+    <cellStyle name="Moneda 2 2 9 3" xfId="158" xr:uid="{781489DB-F7B2-4A1B-AC30-394C49DEE35D}"/>
+    <cellStyle name="Moneda 2 2 9 4" xfId="245" xr:uid="{010D2155-13CE-4575-9531-9B68CBFE68CD}"/>
     <cellStyle name="Moneda 2 3" xfId="36" xr:uid="{1215ABD4-5220-487B-89B5-AA885EAB04A5}"/>
+    <cellStyle name="Moneda 2 3 10" xfId="82" xr:uid="{B5049156-F7B5-4D82-A28C-72F77FAC3FDE}"/>
+    <cellStyle name="Moneda 2 3 10 2" xfId="128" xr:uid="{E577115C-2C28-4FD5-BD08-F2EC8B795D84}"/>
+    <cellStyle name="Moneda 2 3 10 3" xfId="215" xr:uid="{635DFC0C-397D-4DE7-855D-BD5CAB2D8395}"/>
+    <cellStyle name="Moneda 2 3 11" xfId="75" xr:uid="{AFAAB54B-D457-4581-9388-C2AF44BDBE66}"/>
+    <cellStyle name="Moneda 2 3 12" xfId="121" xr:uid="{A21B8778-7457-4CB2-9FF8-B162FF534DB8}"/>
+    <cellStyle name="Moneda 2 3 13" xfId="208" xr:uid="{5E956D6D-9857-4FCA-894B-DB3819E49033}"/>
     <cellStyle name="Moneda 2 3 2" xfId="39" xr:uid="{3420C6FC-40C3-4347-8915-5E37D4F27C66}"/>
+    <cellStyle name="Moneda 2 3 2 2" xfId="85" xr:uid="{8DB36012-E571-4B42-A3E0-8B4BD7C0751C}"/>
+    <cellStyle name="Moneda 2 3 2 3" xfId="131" xr:uid="{586EC2D4-BA22-4AEA-B984-BEA6F26151B3}"/>
+    <cellStyle name="Moneda 2 3 2 4" xfId="218" xr:uid="{7544BB2C-5BD6-4D28-B4E0-954BC9201C88}"/>
     <cellStyle name="Moneda 2 3 3" xfId="42" xr:uid="{7BE246B1-3564-4109-A03A-9C159034B353}"/>
+    <cellStyle name="Moneda 2 3 3 2" xfId="88" xr:uid="{F87279E2-F415-4C64-9C05-C74C17FFB004}"/>
+    <cellStyle name="Moneda 2 3 3 3" xfId="134" xr:uid="{0DD1AEAC-9B83-4DB8-9D36-0748DFCD1D1C}"/>
+    <cellStyle name="Moneda 2 3 3 4" xfId="221" xr:uid="{5F0DEDC8-9C07-4D61-BE51-BE12390B8597}"/>
     <cellStyle name="Moneda 2 3 4" xfId="45" xr:uid="{C537BDE2-9AB6-4E9B-9408-C3A95636E5DD}"/>
+    <cellStyle name="Moneda 2 3 4 2" xfId="91" xr:uid="{B8A9AD54-5724-4B5F-98E9-362585CA22A8}"/>
+    <cellStyle name="Moneda 2 3 4 3" xfId="137" xr:uid="{C3075DD4-4BBF-4B1F-AB23-8AA30141E209}"/>
+    <cellStyle name="Moneda 2 3 4 4" xfId="224" xr:uid="{378D5109-26D3-41DC-A183-5470D924BD48}"/>
     <cellStyle name="Moneda 2 3 5" xfId="49" xr:uid="{A5551541-CFD7-4A26-9869-71C8BCD7753D}"/>
+    <cellStyle name="Moneda 2 3 5 2" xfId="95" xr:uid="{0E94BD71-E69C-4C3C-9356-0D9A2AF72228}"/>
+    <cellStyle name="Moneda 2 3 5 3" xfId="141" xr:uid="{E77E3A4A-58E9-4EBC-9E89-0C55C7B37DCE}"/>
+    <cellStyle name="Moneda 2 3 5 4" xfId="228" xr:uid="{8E37ACAA-DF68-4FEB-9BC8-90E08DD53A34}"/>
     <cellStyle name="Moneda 2 3 6" xfId="54" xr:uid="{D8E5DCCD-1ADF-400D-B378-83D66EE3168E}"/>
+    <cellStyle name="Moneda 2 3 6 2" xfId="100" xr:uid="{6B4B5ACC-3EC5-4FF5-ACF9-93C7E1B75047}"/>
+    <cellStyle name="Moneda 2 3 6 3" xfId="146" xr:uid="{EA4637C3-3F4A-44E1-A2FF-1CEACC6462EE}"/>
+    <cellStyle name="Moneda 2 3 6 4" xfId="233" xr:uid="{E41B9DD5-347A-4B9B-BCE8-2D15516F8747}"/>
     <cellStyle name="Moneda 2 3 7" xfId="60" xr:uid="{F5F4C5BE-7CED-4B09-A44C-DC609CCE0C51}"/>
+    <cellStyle name="Moneda 2 3 7 2" xfId="106" xr:uid="{F42142CF-8DA9-4703-8B04-7BEA3108A6BA}"/>
+    <cellStyle name="Moneda 2 3 7 3" xfId="152" xr:uid="{8E124B33-8F74-4780-A4B4-5A74BC351914}"/>
+    <cellStyle name="Moneda 2 3 7 4" xfId="239" xr:uid="{33686559-6105-430C-A5BE-2181DB44B51E}"/>
     <cellStyle name="Moneda 2 3 8" xfId="65" xr:uid="{29D3C733-4371-485E-8502-AA4779581B3E}"/>
+    <cellStyle name="Moneda 2 3 8 2" xfId="111" xr:uid="{4C7F8DB4-C43D-4B0A-AE79-6C154945E15D}"/>
+    <cellStyle name="Moneda 2 3 8 3" xfId="157" xr:uid="{DF36EBD3-143A-47F4-AF6A-1A495DF8EA4F}"/>
+    <cellStyle name="Moneda 2 3 8 4" xfId="244" xr:uid="{47C80C7F-8816-4600-84C8-B83AAFEDD791}"/>
+    <cellStyle name="Moneda 2 3 9" xfId="70" xr:uid="{5FC70BAA-7994-49FF-B8A1-13765913B757}"/>
+    <cellStyle name="Moneda 2 3 9 2" xfId="116" xr:uid="{74FD84EE-B106-4AC4-BEC4-2E83620C2F8A}"/>
+    <cellStyle name="Moneda 2 3 9 3" xfId="162" xr:uid="{B56FB880-E67F-4704-860D-5D040EA47BD3}"/>
+    <cellStyle name="Moneda 2 3 9 4" xfId="249" xr:uid="{18456A30-E58F-4715-97B7-C049517476AD}"/>
     <cellStyle name="Moneda 2 4" xfId="22" xr:uid="{C856720B-E8A6-4AC5-AB83-CF98E3EF83EE}"/>
+    <cellStyle name="Moneda 2 4 2" xfId="81" xr:uid="{B905E27A-E356-4F29-AEE3-13771753F9DA}"/>
+    <cellStyle name="Moneda 2 4 3" xfId="127" xr:uid="{DACFF950-40D1-41D6-8EB6-B447D99CED5A}"/>
+    <cellStyle name="Moneda 2 4 4" xfId="214" xr:uid="{9E337CD0-9A13-4633-90FE-83FCB36E59E5}"/>
     <cellStyle name="Moneda 2 5" xfId="38" xr:uid="{543CB192-C6A7-4F18-96D2-D078B55A61CB}"/>
+    <cellStyle name="Moneda 2 5 2" xfId="84" xr:uid="{486A89DC-ECBC-402C-A58A-FBAC4FFCF01C}"/>
+    <cellStyle name="Moneda 2 5 3" xfId="130" xr:uid="{A43C2057-7CF1-475D-A586-BC553198FEBE}"/>
+    <cellStyle name="Moneda 2 5 4" xfId="217" xr:uid="{9CCC8394-F96F-47AF-A39A-120DF642B610}"/>
     <cellStyle name="Moneda 2 6" xfId="41" xr:uid="{14D1D7A7-6BF3-4644-A820-240992FDB63E}"/>
+    <cellStyle name="Moneda 2 6 2" xfId="87" xr:uid="{93DBA7D8-4A16-4297-AED1-7E763BB07D3B}"/>
+    <cellStyle name="Moneda 2 6 3" xfId="133" xr:uid="{AC18E7A7-AD52-4063-9EC4-5B12B12AC1E2}"/>
+    <cellStyle name="Moneda 2 6 4" xfId="220" xr:uid="{7BB2960D-19E2-4607-A815-E350CD4D4E2E}"/>
     <cellStyle name="Moneda 2 7" xfId="44" xr:uid="{FFF1D48E-6176-4CF7-81EF-EE5AC9546ED6}"/>
+    <cellStyle name="Moneda 2 7 2" xfId="90" xr:uid="{662C375C-70C8-4901-893E-E33A91557316}"/>
+    <cellStyle name="Moneda 2 7 3" xfId="136" xr:uid="{03CD9128-CD3A-4ACF-83FD-DD49DD62D230}"/>
+    <cellStyle name="Moneda 2 7 4" xfId="223" xr:uid="{0982ADCE-1E5F-44E3-AFFF-9514712C3B4C}"/>
     <cellStyle name="Moneda 2 8" xfId="48" xr:uid="{505EEDDC-CA34-4C8E-894B-E00A33C56132}"/>
+    <cellStyle name="Moneda 2 8 2" xfId="94" xr:uid="{0C48F0DF-9A9B-47F2-B5B5-8C5A4F507DB2}"/>
+    <cellStyle name="Moneda 2 8 3" xfId="140" xr:uid="{2DDA0C3B-B4D2-4D0E-91AE-8417131A2ED7}"/>
+    <cellStyle name="Moneda 2 8 4" xfId="227" xr:uid="{DB10AF3D-5235-4D42-B947-427251072FEA}"/>
     <cellStyle name="Moneda 2 9" xfId="53" xr:uid="{9DEFD098-5F68-4A9D-A770-6123E150DD6E}"/>
+    <cellStyle name="Moneda 2 9 2" xfId="99" xr:uid="{4C4F8FDC-C495-441C-A948-3A3941756072}"/>
+    <cellStyle name="Moneda 2 9 3" xfId="145" xr:uid="{A15D5E0D-4857-485B-B899-5C79ED2126D5}"/>
+    <cellStyle name="Moneda 2 9 4" xfId="232" xr:uid="{2FB3D762-2DBC-41C3-8A4B-F42EAB96A89D}"/>
     <cellStyle name="Moneda 3" xfId="47" xr:uid="{85CAFDD7-BC80-42AB-AB19-AD3F8539702F}"/>
+    <cellStyle name="Moneda 3 10" xfId="210" xr:uid="{47A1FA21-1B88-42B7-9293-A37799E2DB5B}"/>
     <cellStyle name="Moneda 3 2" xfId="51" xr:uid="{96C4286F-DBE0-4288-BB74-90F8B138EA6D}"/>
+    <cellStyle name="Moneda 3 2 2" xfId="97" xr:uid="{20E23E69-96B9-4897-A347-54D52E8BA6FB}"/>
+    <cellStyle name="Moneda 3 2 3" xfId="143" xr:uid="{71BD2A54-4155-4016-BAFD-7CA7F2237F57}"/>
+    <cellStyle name="Moneda 3 2 4" xfId="230" xr:uid="{E79D693B-91F0-4C13-87C9-AE6C3239D037}"/>
     <cellStyle name="Moneda 3 3" xfId="56" xr:uid="{34925A72-50E9-4BB6-AB5E-29A42278EC06}"/>
+    <cellStyle name="Moneda 3 3 2" xfId="102" xr:uid="{6A49C2AA-C587-4F11-A173-65C84D02B8F7}"/>
+    <cellStyle name="Moneda 3 3 3" xfId="148" xr:uid="{302BEA78-715F-4324-ACD0-913C3FAB3E5F}"/>
+    <cellStyle name="Moneda 3 3 4" xfId="235" xr:uid="{EA31B6D8-5FA9-41AC-B355-44EEF417FEB9}"/>
     <cellStyle name="Moneda 3 4" xfId="62" xr:uid="{2CBB34AE-A901-454F-8B45-5C34D3D6C141}"/>
+    <cellStyle name="Moneda 3 4 2" xfId="108" xr:uid="{B89AE0FB-3978-48B9-BB55-8875ECCD656E}"/>
+    <cellStyle name="Moneda 3 4 3" xfId="154" xr:uid="{63E6F307-7839-490B-A5B9-66ED924F46EC}"/>
+    <cellStyle name="Moneda 3 4 4" xfId="241" xr:uid="{B185CB40-E726-4791-8F3F-DAC9A0F48648}"/>
     <cellStyle name="Moneda 3 5" xfId="67" xr:uid="{3FFD3DD0-5204-47D9-B534-A50AAA72ACB7}"/>
+    <cellStyle name="Moneda 3 5 2" xfId="113" xr:uid="{20EED5AE-EC9D-4E21-859D-241A45CFABB1}"/>
+    <cellStyle name="Moneda 3 5 3" xfId="159" xr:uid="{C2B9F339-D756-4C5D-8C08-99A8D24897C3}"/>
+    <cellStyle name="Moneda 3 5 4" xfId="246" xr:uid="{6C021489-637C-4A39-99E4-5D3E6B3DD5E7}"/>
+    <cellStyle name="Moneda 3 6" xfId="72" xr:uid="{1123ABF6-735C-4B1A-9A9D-13E29730795D}"/>
+    <cellStyle name="Moneda 3 6 2" xfId="118" xr:uid="{FC7BC7D2-0411-41D8-AA8D-F1A5D239DB53}"/>
+    <cellStyle name="Moneda 3 6 3" xfId="164" xr:uid="{981CB1AA-33DA-4075-8E2C-8C3DF7FB9680}"/>
+    <cellStyle name="Moneda 3 6 4" xfId="251" xr:uid="{D054D014-DA1F-4C61-9ADB-EE6129C7176A}"/>
+    <cellStyle name="Moneda 3 7" xfId="93" xr:uid="{143FA41C-45A1-4D0D-BCEB-2A6CD584F1A4}"/>
+    <cellStyle name="Moneda 3 7 2" xfId="139" xr:uid="{9666F50D-330E-4835-BC7E-5A08B5870F28}"/>
+    <cellStyle name="Moneda 3 7 3" xfId="226" xr:uid="{AEE6FEBA-FC88-460F-A1E4-CFC753A2AD21}"/>
+    <cellStyle name="Moneda 3 8" xfId="77" xr:uid="{9D38D546-6677-4929-8E55-423271F0B76D}"/>
+    <cellStyle name="Moneda 3 9" xfId="123" xr:uid="{71D30BF2-29FB-4DB6-B941-317AF9935F77}"/>
     <cellStyle name="Moneda 4" xfId="52" xr:uid="{37C3E87F-62D1-4247-9FCD-BF46D4177B38}"/>
     <cellStyle name="Moneda 4 2" xfId="57" xr:uid="{0D33716A-1B52-49C5-B03E-298B115A6242}"/>
+    <cellStyle name="Moneda 4 2 2" xfId="103" xr:uid="{AACBA8BA-7D9F-4375-8223-C5DC3A39545A}"/>
+    <cellStyle name="Moneda 4 2 3" xfId="149" xr:uid="{001258B4-E819-4E14-A4BC-69EC9A476FE6}"/>
+    <cellStyle name="Moneda 4 2 4" xfId="236" xr:uid="{D36259C9-FD7D-400D-BCD1-26EC9D76B543}"/>
     <cellStyle name="Moneda 4 3" xfId="63" xr:uid="{ED1C5CE2-B4BC-4A3D-AB59-9C0356444D01}"/>
+    <cellStyle name="Moneda 4 3 2" xfId="109" xr:uid="{1CD0CC82-5263-4DEE-B94E-D77A2438921E}"/>
+    <cellStyle name="Moneda 4 3 3" xfId="155" xr:uid="{5DD14E02-C160-4EEF-8CB5-E2E7D2B0945B}"/>
+    <cellStyle name="Moneda 4 3 4" xfId="242" xr:uid="{D4B83A40-21EC-497B-9D2A-C8198487483A}"/>
     <cellStyle name="Moneda 4 4" xfId="68" xr:uid="{A8A598A9-970D-47DC-B1E1-29E7D47DD090}"/>
+    <cellStyle name="Moneda 4 4 2" xfId="114" xr:uid="{59279AA4-CD79-48BE-BA6F-A548E9E73AA7}"/>
+    <cellStyle name="Moneda 4 4 3" xfId="160" xr:uid="{809D950E-8DD7-4C72-A60E-6AEC953EFB87}"/>
+    <cellStyle name="Moneda 4 4 4" xfId="247" xr:uid="{7E083487-A7F5-4EDF-9737-4F0A76B48A43}"/>
+    <cellStyle name="Moneda 4 5" xfId="73" xr:uid="{69AE1A5E-3A9B-4A7C-B962-B3043E993D8D}"/>
+    <cellStyle name="Moneda 4 5 2" xfId="119" xr:uid="{41931F4B-6B43-4774-8F41-F8AACDBD14B2}"/>
+    <cellStyle name="Moneda 4 5 3" xfId="165" xr:uid="{50D6C0B2-B998-4C77-AEDD-420AE00EDE82}"/>
+    <cellStyle name="Moneda 4 5 4" xfId="252" xr:uid="{F2BF692C-6CE4-47D1-847C-7C8D4010FB28}"/>
+    <cellStyle name="Moneda 4 6" xfId="98" xr:uid="{4F9D7CCE-4CC0-4C6C-9305-EA75C4F3875B}"/>
+    <cellStyle name="Moneda 4 6 2" xfId="144" xr:uid="{39DE7B02-8CEB-402C-9AA1-EABC50DB2540}"/>
+    <cellStyle name="Moneda 4 6 3" xfId="231" xr:uid="{AF02880C-F531-4C7D-AD09-5D7917357588}"/>
+    <cellStyle name="Moneda 4 7" xfId="78" xr:uid="{35E27D55-94D0-4DEB-AA9D-FDA546D20F9E}"/>
+    <cellStyle name="Moneda 4 8" xfId="124" xr:uid="{D4251BD3-7034-44C2-AADD-AB8F76DC2AB0}"/>
+    <cellStyle name="Moneda 4 9" xfId="211" xr:uid="{56745075-97AD-4F75-A521-4FC3CA6F3143}"/>
     <cellStyle name="Moneda 5" xfId="58" xr:uid="{3670C6D2-7DDC-4274-A607-0FB14349F8E2}"/>
+    <cellStyle name="Moneda 5 2" xfId="104" xr:uid="{AAA1E068-29D5-4C3E-BCED-A365C80CD4D7}"/>
+    <cellStyle name="Moneda 5 3" xfId="150" xr:uid="{E7798976-6AE6-4957-B10E-F095B839ADD4}"/>
+    <cellStyle name="Moneda 5 4" xfId="237" xr:uid="{BB71DFD8-A349-4772-BDC8-941CB4398B27}"/>
+    <cellStyle name="Moneda 6" xfId="253" xr:uid="{A995F97A-4D71-43DC-9949-BFE8D21A8A32}"/>
+    <cellStyle name="Neutral" xfId="173" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="10" xr:uid="{0B95864E-03D8-4F67-B990-2AF43328EB3C}"/>
     <cellStyle name="Normal 10 2" xfId="30" xr:uid="{7FA630B3-0C0F-4FC1-B9AD-58284DA35EB1}"/>
@@ -571,6 +1344,7 @@
     <cellStyle name="Normal 15" xfId="15" xr:uid="{DAAA0BE8-7004-4376-A042-6A9A168A9A21}"/>
     <cellStyle name="Normal 15 2" xfId="20" xr:uid="{55332A69-B081-4BAD-8A20-77725DD92B5C}"/>
     <cellStyle name="Normal 15 3" xfId="35" xr:uid="{CCD54986-C90C-4098-A1A6-8D44F35D6691}"/>
+    <cellStyle name="Normal 16" xfId="254" xr:uid="{25D55C6B-2597-45A4-85E5-AD68CDB53B3A}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{0C12119C-D43E-49BD-BFF9-9B05911E5BF0}"/>
     <cellStyle name="Normal 2 2" xfId="2" xr:uid="{A7FB9C6F-E634-4B2E-86BE-BBD572D5AFB7}"/>
     <cellStyle name="Normal 2 3" xfId="16" xr:uid="{76702E4E-6488-468F-BE6C-98D1A76F4C63}"/>
@@ -588,7 +1362,15 @@
     <cellStyle name="Normal 8 2" xfId="28" xr:uid="{E1572630-C991-475A-B9DB-D7C6C95041D9}"/>
     <cellStyle name="Normal 9" xfId="9" xr:uid="{71DD3493-6787-4E9A-9884-29FA502B524E}"/>
     <cellStyle name="Normal 9 2" xfId="29" xr:uid="{C7D337D3-C3B7-4827-905C-EA6DC470000D}"/>
+    <cellStyle name="Notas" xfId="180" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Porcentaje 2" xfId="17" xr:uid="{B4DC4AB0-E63A-4080-AE1F-316E36CABFFB}"/>
+    <cellStyle name="Salida" xfId="175" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="179" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="181" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="166" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="168" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="169" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="182" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -604,7 +1386,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="45972.748491435188" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46092.44579247685" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -637,7 +1419,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1740"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7538"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -653,32 +1435,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="288"/>
+    <n v="1160"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="292"/>
+    <n v="1098"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="311"/>
+    <n v="1286"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="226"/>
+    <n v="1392"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="337"/>
+    <n v="1380"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="286"/>
+    <n v="1222"/>
   </r>
   <r>
     <x v="0"/>
@@ -688,7 +1470,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="1740"/>
+    <n v="7538"/>
   </r>
   <r>
     <x v="1"/>
@@ -703,32 +1485,32 @@
   <r>
     <x v="2"/>
     <x v="0"/>
-    <n v="58"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="1"/>
-    <n v="62"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <n v="65"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="3"/>
-    <n v="54"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="4"/>
-    <n v="72"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
     <x v="5"/>
-    <n v="66"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="2"/>
@@ -738,7 +1520,7 @@
   <r>
     <x v="2"/>
     <x v="7"/>
-    <n v="377"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -894,7 +1676,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="274" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -1310,7 +2092,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC90F7AF-2A69-4C5E-9FF5-F9DB01805A13}">
   <dimension ref="A1:AF53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="7.85546875" customWidth="1"/>
@@ -1318,7 +2100,7 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -1326,7 +2108,7 @@
     <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22">
       <c r="A1" s="25" t="s">
         <v>19</v>
       </c>
@@ -1344,7 +2126,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1355,30 +2137,30 @@
         <v>2</v>
       </c>
       <c r="D2" s="8">
-        <v>45965</v>
+        <v>46084</v>
       </c>
       <c r="E2" s="8">
         <f>+D2+1</f>
-        <v>45966</v>
+        <v>46085</v>
       </c>
       <c r="F2" s="8">
         <f t="shared" ref="F2:G2" si="0">+E2+1</f>
-        <v>45967</v>
+        <v>46086</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" si="0"/>
-        <v>45968</v>
+        <v>46087</v>
       </c>
       <c r="H2" s="8">
         <f>+G2+3</f>
-        <v>45971</v>
+        <v>46090</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1387,30 +2169,18 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>288</v>
-      </c>
-      <c r="D3">
-        <v>56</v>
-      </c>
-      <c r="E3">
-        <v>56</v>
-      </c>
-      <c r="F3">
-        <v>56</v>
-      </c>
-      <c r="G3">
-        <v>62</v>
-      </c>
-      <c r="H3">
-        <v>58</v>
+        <v>1160</v>
+      </c>
+      <c r="D3" s="31">
+        <v>1160</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>9.6</v>
+        <v>193.33333333333334</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -1419,34 +2189,22 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>292</v>
-      </c>
-      <c r="D4">
-        <v>63</v>
-      </c>
-      <c r="E4">
-        <v>52</v>
-      </c>
-      <c r="F4">
-        <v>59</v>
-      </c>
-      <c r="G4">
-        <v>59</v>
-      </c>
-      <c r="H4">
-        <v>59</v>
+        <v>1098</v>
+      </c>
+      <c r="D4" s="31">
+        <v>1098</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>9.7333333333333325</v>
+        <v>183</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="28"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P4" s="32"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
@@ -1455,30 +2213,18 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>311</v>
-      </c>
-      <c r="D5">
-        <v>63</v>
-      </c>
-      <c r="E5">
-        <v>63</v>
-      </c>
-      <c r="F5">
-        <v>63</v>
-      </c>
-      <c r="G5">
-        <v>57</v>
-      </c>
-      <c r="H5">
-        <v>65</v>
+        <v>1286</v>
+      </c>
+      <c r="D5" s="31">
+        <v>1286</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>10.366666666666667</v>
+        <v>214.33333333333334</v>
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22">
       <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
@@ -1487,30 +2233,18 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>226</v>
-      </c>
-      <c r="D6">
-        <v>46</v>
-      </c>
-      <c r="E6">
-        <v>42</v>
-      </c>
-      <c r="F6">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>48</v>
-      </c>
-      <c r="H6">
-        <v>54</v>
+        <v>1392</v>
+      </c>
+      <c r="D6" s="31">
+        <v>1392</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>7.5333333333333332</v>
+        <v>232</v>
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22">
       <c r="A7" s="13" t="s">
         <v>1</v>
       </c>
@@ -1519,30 +2253,18 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>337</v>
-      </c>
-      <c r="D7">
-        <v>73</v>
-      </c>
-      <c r="E7">
-        <v>72</v>
-      </c>
-      <c r="F7">
-        <v>72</v>
-      </c>
-      <c r="G7">
-        <v>48</v>
-      </c>
-      <c r="H7">
-        <v>72</v>
+        <v>1380</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1380</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>11.233333333333333</v>
+        <v>230</v>
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
@@ -1551,30 +2273,18 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>286</v>
-      </c>
-      <c r="D8">
-        <v>62</v>
-      </c>
-      <c r="E8">
-        <v>62</v>
-      </c>
-      <c r="F8">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>44</v>
-      </c>
-      <c r="H8">
-        <v>62</v>
+        <v>1222</v>
+      </c>
+      <c r="D8" s="31">
+        <v>1222</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>9.5333333333333332</v>
+        <v>203.66666666666666</v>
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" hidden="1">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +2293,7 @@
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22">
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
@@ -1592,41 +2302,41 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>1740</v>
+        <v>7538</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>363</v>
+        <v>7538</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="F10" s="19">
         <f t="shared" si="3"/>
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="G10" s="19">
         <f t="shared" si="3"/>
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>251.26666666666665</v>
       </c>
       <c r="J10" s="20"/>
-      <c r="O10" s="35" t="s">
+      <c r="O10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="35" t="s">
+      <c r="P10" s="30" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -1637,32 +2347,32 @@
       <c r="H11" s="21"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="O11" s="35" t="s">
+      <c r="O11" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="P11" s="32" t="s">
+      <c r="P11" t="s">
         <v>4</v>
       </c>
-      <c r="Q11" s="32" t="s">
+      <c r="Q11" t="s">
         <v>5</v>
       </c>
-      <c r="R11" s="32" t="s">
+      <c r="R11" t="s">
         <v>6</v>
       </c>
-      <c r="S11" s="32" t="s">
+      <c r="S11" t="s">
         <v>7</v>
       </c>
-      <c r="T11" s="32" t="s">
+      <c r="T11" t="s">
         <v>8</v>
       </c>
-      <c r="U11" s="32" t="s">
+      <c r="U11" t="s">
         <v>9</v>
       </c>
-      <c r="V11" s="32" t="s">
+      <c r="V11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1674,54 +2384,54 @@
       </c>
       <c r="D12" s="8">
         <f>+H2+1</f>
-        <v>45972</v>
+        <v>46091</v>
       </c>
       <c r="E12" s="8">
         <f>+D12+1</f>
-        <v>45973</v>
+        <v>46092</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" ref="F12:G12" si="4">+E12+1</f>
-        <v>45974</v>
+        <v>46093</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="4"/>
-        <v>45975</v>
+        <v>46094</v>
       </c>
       <c r="H12" s="8">
         <f>+G12+3</f>
-        <v>45978</v>
+        <v>46097</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="O12" s="33" t="s">
+      <c r="O12" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="P12" s="31">
-        <v>288</v>
-      </c>
-      <c r="Q12" s="31">
-        <v>292</v>
-      </c>
-      <c r="R12" s="31">
-        <v>311</v>
-      </c>
-      <c r="S12" s="31">
-        <v>226</v>
-      </c>
-      <c r="T12" s="31">
-        <v>337</v>
-      </c>
-      <c r="U12" s="31">
-        <v>286</v>
-      </c>
-      <c r="V12" s="31">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P12">
+        <v>1160</v>
+      </c>
+      <c r="Q12">
+        <v>1098</v>
+      </c>
+      <c r="R12">
+        <v>1286</v>
+      </c>
+      <c r="S12">
+        <v>1392</v>
+      </c>
+      <c r="T12">
+        <v>1380</v>
+      </c>
+      <c r="U12">
+        <v>1222</v>
+      </c>
+      <c r="V12">
+        <v>7538</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1730,42 +2440,39 @@
       </c>
       <c r="C13" s="11">
         <f>+SUM(D13:H13)</f>
-        <v>58</v>
-      </c>
-      <c r="D13">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I13" s="26">
         <f>IFERROR(C13/6/COUNT(D13:H13),0)</f>
-        <v>9.6666666666666661</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="O13" s="33" t="s">
+      <c r="O13" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="31">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="31">
-        <v>62</v>
-      </c>
-      <c r="R13" s="31">
-        <v>65</v>
-      </c>
-      <c r="S13" s="31">
-        <v>54</v>
-      </c>
-      <c r="T13" s="31">
-        <v>72</v>
-      </c>
-      <c r="U13" s="31">
-        <v>66</v>
-      </c>
-      <c r="V13" s="31">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
@@ -1774,42 +2481,39 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" ref="C14:C18" si="5">+SUM(D14:H14)</f>
-        <v>62</v>
-      </c>
-      <c r="D14">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I14" s="26">
         <f t="shared" ref="I14:I20" si="6">IFERROR(C14/6/COUNT(D14:H14),0)</f>
-        <v>10.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="O14" s="33" t="s">
+      <c r="O14" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="31">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="31">
-        <v>0</v>
-      </c>
-      <c r="R14" s="31">
-        <v>0</v>
-      </c>
-      <c r="S14" s="31">
-        <v>0</v>
-      </c>
-      <c r="T14" s="31">
-        <v>0</v>
-      </c>
-      <c r="U14" s="31">
-        <v>0</v>
-      </c>
-      <c r="V14" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -1818,42 +2522,39 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="5"/>
-        <v>65</v>
-      </c>
-      <c r="D15">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I15" s="26">
         <f t="shared" si="6"/>
-        <v>10.833333333333334</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="O15" s="33" t="s">
+      <c r="O15" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="P15" s="31">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="31">
-        <v>0</v>
-      </c>
-      <c r="R15" s="31">
-        <v>0</v>
-      </c>
-      <c r="S15" s="31">
-        <v>0</v>
-      </c>
-      <c r="T15" s="31">
-        <v>0</v>
-      </c>
-      <c r="U15" s="31">
-        <v>0</v>
-      </c>
-      <c r="V15" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -1862,42 +2563,39 @@
       </c>
       <c r="C16" s="11">
         <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-      <c r="D16">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I16" s="26">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="O16" s="33" t="s">
+      <c r="O16" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P16" s="31">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="31">
-        <v>0</v>
-      </c>
-      <c r="R16" s="31">
-        <v>0</v>
-      </c>
-      <c r="S16" s="31">
-        <v>0</v>
-      </c>
-      <c r="T16" s="31">
-        <v>0</v>
-      </c>
-      <c r="U16" s="31">
-        <v>0</v>
-      </c>
-      <c r="V16" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -1906,42 +2604,39 @@
       </c>
       <c r="C17" s="11">
         <f t="shared" si="5"/>
-        <v>72</v>
-      </c>
-      <c r="D17">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I17" s="26">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="O17" s="33" t="s">
+      <c r="O17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="31">
-        <v>346</v>
-      </c>
-      <c r="Q17" s="31">
-        <v>354</v>
-      </c>
-      <c r="R17" s="31">
-        <v>376</v>
-      </c>
-      <c r="S17" s="31">
-        <v>280</v>
-      </c>
-      <c r="T17" s="31">
-        <v>409</v>
-      </c>
-      <c r="U17" s="31">
-        <v>352</v>
-      </c>
-      <c r="V17" s="31">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="P17">
+        <v>1160</v>
+      </c>
+      <c r="Q17">
+        <v>1098</v>
+      </c>
+      <c r="R17">
+        <v>1286</v>
+      </c>
+      <c r="S17">
+        <v>1392</v>
+      </c>
+      <c r="T17">
+        <v>1380</v>
+      </c>
+      <c r="U17">
+        <v>1222</v>
+      </c>
+      <c r="V17">
+        <v>7538</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
@@ -1950,18 +2645,15 @@
       </c>
       <c r="C18" s="11">
         <f t="shared" si="5"/>
-        <v>66</v>
-      </c>
-      <c r="D18">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I18" s="26">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" hidden="1">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -1970,7 +2662,7 @@
       <c r="I19" s="26"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -1979,11 +2671,11 @@
       </c>
       <c r="C20" s="18">
         <f>SUM(C13:C19)</f>
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="D20" s="19">
         <f>SUM(D13:D19)</f>
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="E20" s="19">
         <f t="shared" ref="E20:H20" si="7">SUM(E13:E19)</f>
@@ -2003,13 +2695,13 @@
       </c>
       <c r="I20" s="26">
         <f t="shared" si="6"/>
-        <v>12.566666666666666</v>
+        <v>0</v>
       </c>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
+    <row r="21" spans="1:32">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -2018,12 +2710,12 @@
       <c r="H21" s="21"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="O21" s="28" t="s">
+      <c r="O21" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="28"/>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="P21" s="32"/>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -2035,33 +2727,33 @@
       </c>
       <c r="D22" s="8">
         <f>+H12+1</f>
-        <v>45979</v>
+        <v>46098</v>
       </c>
       <c r="E22" s="8">
         <f>+D22+1</f>
-        <v>45980</v>
+        <v>46099</v>
       </c>
       <c r="F22" s="8">
         <f t="shared" ref="F22:G22" si="8">+E22+1</f>
-        <v>45981</v>
+        <v>46100</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="8"/>
-        <v>45982</v>
+        <v>46101</v>
       </c>
       <c r="H22" s="8">
         <f>+G22+3</f>
-        <v>45985</v>
+        <v>46104</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="O22" s="34">
-        <v>45972.513194444444</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="O22" s="28">
+        <v>46092.463194444441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="13" t="s">
         <v>12</v>
       </c>
@@ -2078,7 +2770,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32">
       <c r="A24" s="13" t="s">
         <v>12</v>
       </c>
@@ -2095,7 +2787,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32">
       <c r="A25" s="13" t="s">
         <v>12</v>
       </c>
@@ -2112,7 +2804,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32">
       <c r="A26" s="13" t="s">
         <v>12</v>
       </c>
@@ -2129,7 +2821,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32">
       <c r="A27" s="13" t="s">
         <v>12</v>
       </c>
@@ -2146,7 +2838,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32">
       <c r="A28" s="13" t="s">
         <v>12</v>
       </c>
@@ -2163,7 +2855,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" hidden="1">
       <c r="A29" s="13" t="s">
         <v>12</v>
       </c>
@@ -2172,7 +2864,7 @@
       <c r="I29" s="26"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32">
       <c r="A30" s="13" t="s">
         <v>12</v>
       </c>
@@ -2209,9 +2901,9 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
+    <row r="31" spans="1:32">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2222,7 +2914,7 @@
       <c r="J31" s="3"/>
       <c r="AF31" s="27"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32">
       <c r="A32" s="5" t="s">
         <v>13</v>
       </c>
@@ -2234,23 +2926,23 @@
       </c>
       <c r="D32" s="8">
         <f>+H22+1</f>
-        <v>45986</v>
+        <v>46105</v>
       </c>
       <c r="E32" s="8">
         <f>+D32+1</f>
-        <v>45987</v>
+        <v>46106</v>
       </c>
       <c r="F32" s="8">
         <f t="shared" ref="F32:G32" si="12">+E32+1</f>
-        <v>45988</v>
+        <v>46107</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="12"/>
-        <v>45989</v>
+        <v>46108</v>
       </c>
       <c r="H32" s="8">
         <f>+G32+3</f>
-        <v>45992</v>
+        <v>46111</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>3</v>
@@ -2258,7 +2950,7 @@
       <c r="J32" s="1"/>
       <c r="AF32" s="27"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32">
       <c r="A33" s="13" t="s">
         <v>13</v>
       </c>
@@ -2269,7 +2961,6 @@
         <f>+SUM(D33:H33)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
@@ -2281,7 +2972,7 @@
       <c r="J33" s="3"/>
       <c r="AF33" s="27"/>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32">
       <c r="A34" s="13" t="s">
         <v>13</v>
       </c>
@@ -2292,7 +2983,6 @@
         <f t="shared" ref="C34:C38" si="13">+SUM(D34:H34)</f>
         <v>0</v>
       </c>
-      <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -2304,7 +2994,7 @@
       <c r="J34" s="3"/>
       <c r="AF34" s="27"/>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32">
       <c r="A35" s="13" t="s">
         <v>13</v>
       </c>
@@ -2315,7 +3005,6 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -2327,7 +3016,7 @@
       <c r="J35" s="3"/>
       <c r="AF35" s="27"/>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32">
       <c r="A36" s="13" t="s">
         <v>13</v>
       </c>
@@ -2338,7 +3027,6 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
@@ -2350,7 +3038,7 @@
       <c r="J36" s="3"/>
       <c r="AF36" s="27"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32">
       <c r="A37" s="13" t="s">
         <v>13</v>
       </c>
@@ -2361,7 +3049,6 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
@@ -2373,7 +3060,7 @@
       <c r="J37" s="3"/>
       <c r="AF37" s="27"/>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32">
       <c r="A38" s="13" t="s">
         <v>13</v>
       </c>
@@ -2384,7 +3071,6 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
@@ -2396,7 +3082,7 @@
       <c r="J38" s="3"/>
       <c r="AF38" s="27"/>
     </row>
-    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" hidden="1">
       <c r="A39" s="13" t="s">
         <v>13</v>
       </c>
@@ -2411,7 +3097,7 @@
       <c r="J39" s="3"/>
       <c r="AF39" s="27"/>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32">
       <c r="A40" s="13" t="s">
         <v>13</v>
       </c>
@@ -2449,9 +3135,9 @@
       <c r="J40" s="20"/>
       <c r="AF40" s="27"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
+    <row r="41" spans="1:32">
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2462,7 +3148,7 @@
       <c r="J41" s="3"/>
       <c r="AF41" s="27"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32">
       <c r="A42" s="5" t="s">
         <v>14</v>
       </c>
@@ -2474,23 +3160,23 @@
       </c>
       <c r="D42" s="8">
         <f>+H32+1</f>
-        <v>45993</v>
+        <v>46112</v>
       </c>
       <c r="E42" s="8">
         <f>+D42+1</f>
-        <v>45994</v>
+        <v>46113</v>
       </c>
       <c r="F42" s="8">
         <f t="shared" ref="F42:G42" si="16">+E42+1</f>
-        <v>45995</v>
+        <v>46114</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="16"/>
-        <v>45996</v>
+        <v>46115</v>
       </c>
       <c r="H42" s="8">
         <f>+G42+3</f>
-        <v>45999</v>
+        <v>46118</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>3</v>
@@ -2498,7 +3184,7 @@
       <c r="J42" s="1"/>
       <c r="AF42" s="27"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32">
       <c r="A43" s="13" t="s">
         <v>14</v>
       </c>
@@ -2521,7 +3207,7 @@
       <c r="J43" s="3"/>
       <c r="AF43" s="27"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32">
       <c r="A44" s="13" t="s">
         <v>14</v>
       </c>
@@ -2544,7 +3230,7 @@
       <c r="J44" s="3"/>
       <c r="AF44" s="27"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32">
       <c r="A45" s="13" t="s">
         <v>14</v>
       </c>
@@ -2567,7 +3253,7 @@
       <c r="J45" s="3"/>
       <c r="AF45" s="27"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32">
       <c r="A46" s="13" t="s">
         <v>14</v>
       </c>
@@ -2590,7 +3276,7 @@
       <c r="J46" s="3"/>
       <c r="AF46" s="27"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32">
       <c r="A47" s="13" t="s">
         <v>14</v>
       </c>
@@ -2613,7 +3299,7 @@
       <c r="J47" s="3"/>
       <c r="AF47" s="27"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32">
       <c r="A48" s="13" t="s">
         <v>14</v>
       </c>
@@ -2636,7 +3322,7 @@
       <c r="J48" s="3"/>
       <c r="AF48" s="27"/>
     </row>
-    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" hidden="1">
       <c r="A49" s="13" t="s">
         <v>14</v>
       </c>
@@ -2651,7 +3337,7 @@
       <c r="J49" s="3"/>
       <c r="AF49" s="27"/>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32">
       <c r="A50" s="13" t="s">
         <v>14</v>
       </c>
@@ -2689,9 +3375,9 @@
       <c r="J50" s="20"/>
       <c r="AF50" s="27"/>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
+    <row r="51" spans="1:32">
+      <c r="A51" s="33"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="2"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
@@ -2702,9 +3388,9 @@
       <c r="J51" s="3"/>
       <c r="AF51" s="27"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
+    <row r="52" spans="1:32">
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21">
         <v>0</v>
@@ -2724,9 +3410,9 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
+    <row r="53" spans="1:32">
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2752,8 +3438,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
     <xsd:import namespace="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <xsd:element name="properties">
@@ -2986,41 +3692,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8039E8B4-6FF4-40F6-9FA1-E9DA9C439884}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3037,9 +3712,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{417CE98F-DC79-4302-A893-B76A9B1BB777}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E5DBE-A9BE-4103-BB1F-35FCC29679BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="274" r:id="rId2"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1676,7 +1676,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="274" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46092.463194444441</v>
+        <v>46093.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3438,15 +3438,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -3455,6 +3446,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3693,20 +3693,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7E5DBE-A9BE-4103-BB1F-35FCC29679BB}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012DE619-6E75-4B10-A7D4-424A6ADB7323}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="990" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1028,7 +1028,7 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1114,6 +1114,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="255">
     <cellStyle name="20% - Énfasis1" xfId="184" builtinId="30" customBuiltin="1"/>
@@ -1386,7 +1387,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46092.44579247685" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46106.545731828701" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1676,7 +1677,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="990" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2409,25 +2410,25 @@
       <c r="O12" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="35">
         <v>1160</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="35">
         <v>1098</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="35">
         <v>1286</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="35">
         <v>1392</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="35">
         <v>1380</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="35">
         <v>1222</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="35">
         <v>7538</v>
       </c>
     </row>
@@ -2450,25 +2451,25 @@
       <c r="O13" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
+      <c r="P13" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="35">
+        <v>0</v>
+      </c>
+      <c r="R13" s="35">
+        <v>0</v>
+      </c>
+      <c r="S13" s="35">
+        <v>0</v>
+      </c>
+      <c r="T13" s="35">
+        <v>0</v>
+      </c>
+      <c r="U13" s="35">
+        <v>0</v>
+      </c>
+      <c r="V13" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2491,25 +2492,25 @@
       <c r="O14" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
+      <c r="P14" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="35">
+        <v>0</v>
+      </c>
+      <c r="R14" s="35">
+        <v>0</v>
+      </c>
+      <c r="S14" s="35">
+        <v>0</v>
+      </c>
+      <c r="T14" s="35">
+        <v>0</v>
+      </c>
+      <c r="U14" s="35">
+        <v>0</v>
+      </c>
+      <c r="V14" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2532,25 +2533,25 @@
       <c r="O15" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
+      <c r="P15" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="35">
+        <v>0</v>
+      </c>
+      <c r="R15" s="35">
+        <v>0</v>
+      </c>
+      <c r="S15" s="35">
+        <v>0</v>
+      </c>
+      <c r="T15" s="35">
+        <v>0</v>
+      </c>
+      <c r="U15" s="35">
+        <v>0</v>
+      </c>
+      <c r="V15" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2573,25 +2574,25 @@
       <c r="O16" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
+      <c r="P16" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="35">
+        <v>0</v>
+      </c>
+      <c r="R16" s="35">
+        <v>0</v>
+      </c>
+      <c r="S16" s="35">
+        <v>0</v>
+      </c>
+      <c r="T16" s="35">
+        <v>0</v>
+      </c>
+      <c r="U16" s="35">
+        <v>0</v>
+      </c>
+      <c r="V16" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2614,25 +2615,25 @@
       <c r="O17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="35">
         <v>1160</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="35">
         <v>1098</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="35">
         <v>1286</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="35">
         <v>1392</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="35">
         <v>1380</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="35">
         <v>1222</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="35">
         <v>7538</v>
       </c>
     </row>
@@ -2750,7 +2751,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46093.854166666664</v>
+        <v>46105.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3438,26 +3439,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3692,26 +3673,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3728,4 +3710,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012DE619-6E75-4B10-A7D4-424A6ADB7323}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F2E453A-A053-43DD-989D-FEBFFC27E551}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="990" r:id="rId2"/>
+    <pivotCache cacheId="149" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -771,7 +771,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="255">
+  <cellStyleXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -1026,6 +1026,55 @@
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
@@ -1116,7 +1165,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="255">
+  <cellStyles count="304">
     <cellStyle name="20% - Énfasis1" xfId="184" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis2" xfId="188" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis3" xfId="192" builtinId="38" customBuiltin="1"/>
@@ -1155,173 +1204,218 @@
     <cellStyle name="Moneda 2 10 2" xfId="105" xr:uid="{EC109079-E88F-4EBC-BA51-0F55F0012AAA}"/>
     <cellStyle name="Moneda 2 10 3" xfId="151" xr:uid="{CC924310-31DA-4300-90F2-D39F2C529DF4}"/>
     <cellStyle name="Moneda 2 10 4" xfId="238" xr:uid="{830C5F1F-837E-476B-AC4B-2430F822591A}"/>
+    <cellStyle name="Moneda 2 10 5" xfId="286" xr:uid="{721499DF-B54D-40BB-AB3A-DA07F1785B62}"/>
     <cellStyle name="Moneda 2 11" xfId="64" xr:uid="{733FA569-27EB-4B97-8F71-9F2702548B08}"/>
     <cellStyle name="Moneda 2 11 2" xfId="110" xr:uid="{25D37EC2-C0F0-439A-84B1-9F07511977A9}"/>
     <cellStyle name="Moneda 2 11 3" xfId="156" xr:uid="{85446705-B7C3-4FC5-AC58-950A1162D64D}"/>
     <cellStyle name="Moneda 2 11 4" xfId="243" xr:uid="{1DF776D6-58E9-4FD7-B167-54CF363D54C0}"/>
+    <cellStyle name="Moneda 2 11 5" xfId="291" xr:uid="{554D3D0F-FFE2-4863-8939-9FD4DADA551D}"/>
     <cellStyle name="Moneda 2 12" xfId="69" xr:uid="{033D24C2-CEBB-4FC5-A4C0-7404A5F207C3}"/>
     <cellStyle name="Moneda 2 12 2" xfId="115" xr:uid="{B70301D3-5E35-4972-AF54-A43466A75284}"/>
     <cellStyle name="Moneda 2 12 3" xfId="161" xr:uid="{4F1ACD12-6748-4AEF-905D-79FE42340EB0}"/>
     <cellStyle name="Moneda 2 12 4" xfId="248" xr:uid="{FE725EAA-25C6-4977-AC7D-92B74FFE9366}"/>
+    <cellStyle name="Moneda 2 12 5" xfId="296" xr:uid="{84CD5094-55DB-4263-8857-64D1F384208D}"/>
     <cellStyle name="Moneda 2 13" xfId="79" xr:uid="{E7B2FE90-A322-4407-AF6E-3C797FE973CA}"/>
     <cellStyle name="Moneda 2 13 2" xfId="125" xr:uid="{B4C13C6D-C18C-482A-BA72-CB6AF979BBC8}"/>
     <cellStyle name="Moneda 2 13 3" xfId="212" xr:uid="{49EEF507-F7FF-4F6A-B172-C1724AB4FC29}"/>
+    <cellStyle name="Moneda 2 13 4" xfId="260" xr:uid="{F13A5BF8-9AC4-49E3-856F-084736FC9AD3}"/>
     <cellStyle name="Moneda 2 14" xfId="74" xr:uid="{45BE0D07-B9A8-4064-94DB-D20AF1E0C4D0}"/>
     <cellStyle name="Moneda 2 15" xfId="120" xr:uid="{48B5C7BB-EAA1-4983-80A6-6DB1BDEB2305}"/>
     <cellStyle name="Moneda 2 16" xfId="207" xr:uid="{C7E238F2-6DB0-47E6-9D6A-2FD41B2C8E92}"/>
+    <cellStyle name="Moneda 2 17" xfId="255" xr:uid="{47C87C91-D05B-4365-AB7C-5B116842909C}"/>
     <cellStyle name="Moneda 2 2" xfId="21" xr:uid="{EBFDC036-FF0B-49ED-AC3A-709715F7B82A}"/>
     <cellStyle name="Moneda 2 2 10" xfId="71" xr:uid="{5DDC46D0-842C-4A2E-92E8-ABD6AD2AAA1B}"/>
     <cellStyle name="Moneda 2 2 10 2" xfId="117" xr:uid="{960E80FF-4C72-481C-B563-7016118359F3}"/>
     <cellStyle name="Moneda 2 2 10 3" xfId="163" xr:uid="{64FD41C9-235A-40AC-A4D8-171C7342486B}"/>
     <cellStyle name="Moneda 2 2 10 4" xfId="250" xr:uid="{11947B10-CB33-4D7F-A33F-052322AE9486}"/>
+    <cellStyle name="Moneda 2 2 10 5" xfId="298" xr:uid="{7AD1CE47-E173-4456-8881-4870FEF752C5}"/>
     <cellStyle name="Moneda 2 2 11" xfId="80" xr:uid="{1AFA96EE-ADFB-46F6-AFF7-84204B421FA8}"/>
     <cellStyle name="Moneda 2 2 11 2" xfId="126" xr:uid="{02884BCA-0787-40C1-ABD4-B7905AA874CC}"/>
     <cellStyle name="Moneda 2 2 11 3" xfId="213" xr:uid="{86C7BD59-388B-482F-B3C1-9811B734512C}"/>
+    <cellStyle name="Moneda 2 2 11 4" xfId="261" xr:uid="{479DED99-FD38-4EDB-8A6A-3E2AE96CA395}"/>
     <cellStyle name="Moneda 2 2 12" xfId="76" xr:uid="{E3478D81-419E-4796-9D51-DA114F8D2C71}"/>
     <cellStyle name="Moneda 2 2 13" xfId="122" xr:uid="{731D2916-217E-4669-AFED-472E473A1648}"/>
     <cellStyle name="Moneda 2 2 14" xfId="209" xr:uid="{3A471E74-A74D-4314-A42E-9CD3371195ED}"/>
+    <cellStyle name="Moneda 2 2 15" xfId="257" xr:uid="{20055C74-8600-4B4E-B66C-008AF1A968A4}"/>
     <cellStyle name="Moneda 2 2 2" xfId="37" xr:uid="{CC7FC404-D3BE-4275-A513-2A476E6F003A}"/>
     <cellStyle name="Moneda 2 2 2 2" xfId="83" xr:uid="{2B5DCB4A-E3BC-4992-B73E-D561B5F63554}"/>
     <cellStyle name="Moneda 2 2 2 3" xfId="129" xr:uid="{9450676A-C05C-4D12-BED3-C60386F06150}"/>
     <cellStyle name="Moneda 2 2 2 4" xfId="216" xr:uid="{9C268655-4231-4B29-9ED4-6A0B600F606C}"/>
+    <cellStyle name="Moneda 2 2 2 5" xfId="264" xr:uid="{ECAF40C8-5546-4E7C-B118-47021AC53B0C}"/>
     <cellStyle name="Moneda 2 2 3" xfId="40" xr:uid="{F05178DD-0970-4BBD-B557-6633C9B3DA72}"/>
     <cellStyle name="Moneda 2 2 3 2" xfId="86" xr:uid="{C9137B14-5840-498A-AE7C-D82E04F564B4}"/>
     <cellStyle name="Moneda 2 2 3 3" xfId="132" xr:uid="{9F23760D-D4E5-4CA6-8A1D-5E62D0E84756}"/>
     <cellStyle name="Moneda 2 2 3 4" xfId="219" xr:uid="{96B37EBD-0D01-4617-9047-A58FD45F8724}"/>
+    <cellStyle name="Moneda 2 2 3 5" xfId="267" xr:uid="{2AB8E6A5-2ADF-4C53-9448-9BE6D8AD85EE}"/>
     <cellStyle name="Moneda 2 2 4" xfId="43" xr:uid="{B1D1D8B7-FFC4-44C3-A297-D56D6135BA6B}"/>
     <cellStyle name="Moneda 2 2 4 2" xfId="89" xr:uid="{87C20372-0BCB-4D10-BF74-8578B62A332F}"/>
     <cellStyle name="Moneda 2 2 4 3" xfId="135" xr:uid="{1C58CE7E-BB98-4DE5-B62D-5AFFAD89DEDF}"/>
     <cellStyle name="Moneda 2 2 4 4" xfId="222" xr:uid="{0B684038-DB80-4159-BB65-A9C33CB85C6D}"/>
+    <cellStyle name="Moneda 2 2 4 5" xfId="270" xr:uid="{97AFE70E-6E26-4A5B-9A69-C5EEF837C853}"/>
     <cellStyle name="Moneda 2 2 5" xfId="46" xr:uid="{E0C5F919-636E-4F9D-8793-F35F305CE8A8}"/>
     <cellStyle name="Moneda 2 2 5 2" xfId="92" xr:uid="{2295E829-7422-40C0-936A-2498C625B8CA}"/>
     <cellStyle name="Moneda 2 2 5 3" xfId="138" xr:uid="{00DE2E34-0A4F-4477-8712-2AA8148E7B07}"/>
     <cellStyle name="Moneda 2 2 5 4" xfId="225" xr:uid="{020629BF-CD7E-4F39-9DDB-FA6B6597B973}"/>
+    <cellStyle name="Moneda 2 2 5 5" xfId="273" xr:uid="{D0BB08B7-6D35-4405-849D-5C20E2DA1C0E}"/>
     <cellStyle name="Moneda 2 2 6" xfId="50" xr:uid="{060513CE-1E51-4AF2-BED2-3308E7A5528F}"/>
     <cellStyle name="Moneda 2 2 6 2" xfId="96" xr:uid="{8980EDDE-FAB1-4D17-A547-1E4AC662111E}"/>
     <cellStyle name="Moneda 2 2 6 3" xfId="142" xr:uid="{B10B84A8-1070-4A7A-888C-663EE2298782}"/>
     <cellStyle name="Moneda 2 2 6 4" xfId="229" xr:uid="{5D7B8547-C1F5-467D-B96A-6CC67AB320F6}"/>
+    <cellStyle name="Moneda 2 2 6 5" xfId="277" xr:uid="{D6668A9C-0735-4921-8C1F-C2C30A7639AC}"/>
     <cellStyle name="Moneda 2 2 7" xfId="55" xr:uid="{94A23887-FE88-4793-9FDA-92C9211068DD}"/>
     <cellStyle name="Moneda 2 2 7 2" xfId="101" xr:uid="{2171A9C0-9E4E-4E9D-BEFF-4EDAF9750199}"/>
     <cellStyle name="Moneda 2 2 7 3" xfId="147" xr:uid="{0AE522F1-FB55-43FD-A794-C5E3F3059E69}"/>
     <cellStyle name="Moneda 2 2 7 4" xfId="234" xr:uid="{15F7D30F-479D-46A3-A95C-E57FC7127380}"/>
+    <cellStyle name="Moneda 2 2 7 5" xfId="282" xr:uid="{E4D1B045-D26E-4A36-B412-84FCADD1E3DE}"/>
     <cellStyle name="Moneda 2 2 8" xfId="61" xr:uid="{49063416-6398-4A1E-BD9F-012E3656CEF7}"/>
     <cellStyle name="Moneda 2 2 8 2" xfId="107" xr:uid="{8F3774A5-B9F6-4398-94C1-5484F962B184}"/>
     <cellStyle name="Moneda 2 2 8 3" xfId="153" xr:uid="{D5E74BFB-237B-4194-9841-8A55B2E00591}"/>
     <cellStyle name="Moneda 2 2 8 4" xfId="240" xr:uid="{464980FD-9027-4E44-9377-F10F03930B67}"/>
+    <cellStyle name="Moneda 2 2 8 5" xfId="288" xr:uid="{F23AE6E4-AAEF-46E3-A20D-EEBEB6A4308D}"/>
     <cellStyle name="Moneda 2 2 9" xfId="66" xr:uid="{A08EDAF3-8B31-4980-9755-F9731E0076E3}"/>
     <cellStyle name="Moneda 2 2 9 2" xfId="112" xr:uid="{CC9101B4-3453-4D5F-B5BA-41D03BF78857}"/>
     <cellStyle name="Moneda 2 2 9 3" xfId="158" xr:uid="{781489DB-F7B2-4A1B-AC30-394C49DEE35D}"/>
     <cellStyle name="Moneda 2 2 9 4" xfId="245" xr:uid="{010D2155-13CE-4575-9531-9B68CBFE68CD}"/>
+    <cellStyle name="Moneda 2 2 9 5" xfId="293" xr:uid="{CB7CC49D-EF63-4C72-8529-03AE18049B06}"/>
     <cellStyle name="Moneda 2 3" xfId="36" xr:uid="{1215ABD4-5220-487B-89B5-AA885EAB04A5}"/>
     <cellStyle name="Moneda 2 3 10" xfId="82" xr:uid="{B5049156-F7B5-4D82-A28C-72F77FAC3FDE}"/>
     <cellStyle name="Moneda 2 3 10 2" xfId="128" xr:uid="{E577115C-2C28-4FD5-BD08-F2EC8B795D84}"/>
     <cellStyle name="Moneda 2 3 10 3" xfId="215" xr:uid="{635DFC0C-397D-4DE7-855D-BD5CAB2D8395}"/>
+    <cellStyle name="Moneda 2 3 10 4" xfId="263" xr:uid="{2EDFE188-C919-438C-BED7-34478823B1F0}"/>
     <cellStyle name="Moneda 2 3 11" xfId="75" xr:uid="{AFAAB54B-D457-4581-9388-C2AF44BDBE66}"/>
     <cellStyle name="Moneda 2 3 12" xfId="121" xr:uid="{A21B8778-7457-4CB2-9FF8-B162FF534DB8}"/>
     <cellStyle name="Moneda 2 3 13" xfId="208" xr:uid="{5E956D6D-9857-4FCA-894B-DB3819E49033}"/>
+    <cellStyle name="Moneda 2 3 14" xfId="256" xr:uid="{047DDC5F-042F-4F06-B45B-97750A590BD9}"/>
     <cellStyle name="Moneda 2 3 2" xfId="39" xr:uid="{3420C6FC-40C3-4347-8915-5E37D4F27C66}"/>
     <cellStyle name="Moneda 2 3 2 2" xfId="85" xr:uid="{8DB36012-E571-4B42-A3E0-8B4BD7C0751C}"/>
     <cellStyle name="Moneda 2 3 2 3" xfId="131" xr:uid="{586EC2D4-BA22-4AEA-B984-BEA6F26151B3}"/>
     <cellStyle name="Moneda 2 3 2 4" xfId="218" xr:uid="{7544BB2C-5BD6-4D28-B4E0-954BC9201C88}"/>
+    <cellStyle name="Moneda 2 3 2 5" xfId="266" xr:uid="{577D9394-14B6-4DB1-B166-B719AF0E087B}"/>
     <cellStyle name="Moneda 2 3 3" xfId="42" xr:uid="{7BE246B1-3564-4109-A03A-9C159034B353}"/>
     <cellStyle name="Moneda 2 3 3 2" xfId="88" xr:uid="{F87279E2-F415-4C64-9C05-C74C17FFB004}"/>
     <cellStyle name="Moneda 2 3 3 3" xfId="134" xr:uid="{0DD1AEAC-9B83-4DB8-9D36-0748DFCD1D1C}"/>
     <cellStyle name="Moneda 2 3 3 4" xfId="221" xr:uid="{5F0DEDC8-9C07-4D61-BE51-BE12390B8597}"/>
+    <cellStyle name="Moneda 2 3 3 5" xfId="269" xr:uid="{A8040A55-45EA-4CDD-AD08-954B2A1D01F5}"/>
     <cellStyle name="Moneda 2 3 4" xfId="45" xr:uid="{C537BDE2-9AB6-4E9B-9408-C3A95636E5DD}"/>
     <cellStyle name="Moneda 2 3 4 2" xfId="91" xr:uid="{B8A9AD54-5724-4B5F-98E9-362585CA22A8}"/>
     <cellStyle name="Moneda 2 3 4 3" xfId="137" xr:uid="{C3075DD4-4BBF-4B1F-AB23-8AA30141E209}"/>
     <cellStyle name="Moneda 2 3 4 4" xfId="224" xr:uid="{378D5109-26D3-41DC-A183-5470D924BD48}"/>
+    <cellStyle name="Moneda 2 3 4 5" xfId="272" xr:uid="{3B176A68-AD1A-48AE-A7DF-87346DC97141}"/>
     <cellStyle name="Moneda 2 3 5" xfId="49" xr:uid="{A5551541-CFD7-4A26-9869-71C8BCD7753D}"/>
     <cellStyle name="Moneda 2 3 5 2" xfId="95" xr:uid="{0E94BD71-E69C-4C3C-9356-0D9A2AF72228}"/>
     <cellStyle name="Moneda 2 3 5 3" xfId="141" xr:uid="{E77E3A4A-58E9-4EBC-9E89-0C55C7B37DCE}"/>
     <cellStyle name="Moneda 2 3 5 4" xfId="228" xr:uid="{8E37ACAA-DF68-4FEB-9BC8-90E08DD53A34}"/>
+    <cellStyle name="Moneda 2 3 5 5" xfId="276" xr:uid="{95AB7E0D-8C17-4588-90FD-AD693CC2181A}"/>
     <cellStyle name="Moneda 2 3 6" xfId="54" xr:uid="{D8E5DCCD-1ADF-400D-B378-83D66EE3168E}"/>
     <cellStyle name="Moneda 2 3 6 2" xfId="100" xr:uid="{6B4B5ACC-3EC5-4FF5-ACF9-93C7E1B75047}"/>
     <cellStyle name="Moneda 2 3 6 3" xfId="146" xr:uid="{EA4637C3-3F4A-44E1-A2FF-1CEACC6462EE}"/>
     <cellStyle name="Moneda 2 3 6 4" xfId="233" xr:uid="{E41B9DD5-347A-4B9B-BCE8-2D15516F8747}"/>
+    <cellStyle name="Moneda 2 3 6 5" xfId="281" xr:uid="{4BE63423-B5F8-47A9-8377-B1DAA3803F09}"/>
     <cellStyle name="Moneda 2 3 7" xfId="60" xr:uid="{F5F4C5BE-7CED-4B09-A44C-DC609CCE0C51}"/>
     <cellStyle name="Moneda 2 3 7 2" xfId="106" xr:uid="{F42142CF-8DA9-4703-8B04-7BEA3108A6BA}"/>
     <cellStyle name="Moneda 2 3 7 3" xfId="152" xr:uid="{8E124B33-8F74-4780-A4B4-5A74BC351914}"/>
     <cellStyle name="Moneda 2 3 7 4" xfId="239" xr:uid="{33686559-6105-430C-A5BE-2181DB44B51E}"/>
+    <cellStyle name="Moneda 2 3 7 5" xfId="287" xr:uid="{A1AD85FA-0F29-41E9-83F6-F8DF0CCE3936}"/>
     <cellStyle name="Moneda 2 3 8" xfId="65" xr:uid="{29D3C733-4371-485E-8502-AA4779581B3E}"/>
     <cellStyle name="Moneda 2 3 8 2" xfId="111" xr:uid="{4C7F8DB4-C43D-4B0A-AE79-6C154945E15D}"/>
     <cellStyle name="Moneda 2 3 8 3" xfId="157" xr:uid="{DF36EBD3-143A-47F4-AF6A-1A495DF8EA4F}"/>
     <cellStyle name="Moneda 2 3 8 4" xfId="244" xr:uid="{47C80C7F-8816-4600-84C8-B83AAFEDD791}"/>
+    <cellStyle name="Moneda 2 3 8 5" xfId="292" xr:uid="{FAD92744-5199-426C-9225-DFFA2A55F864}"/>
     <cellStyle name="Moneda 2 3 9" xfId="70" xr:uid="{5FC70BAA-7994-49FF-B8A1-13765913B757}"/>
     <cellStyle name="Moneda 2 3 9 2" xfId="116" xr:uid="{74FD84EE-B106-4AC4-BEC4-2E83620C2F8A}"/>
     <cellStyle name="Moneda 2 3 9 3" xfId="162" xr:uid="{B56FB880-E67F-4704-860D-5D040EA47BD3}"/>
     <cellStyle name="Moneda 2 3 9 4" xfId="249" xr:uid="{18456A30-E58F-4715-97B7-C049517476AD}"/>
+    <cellStyle name="Moneda 2 3 9 5" xfId="297" xr:uid="{557B85F5-8373-4407-A9F9-C3EA24C8C7A1}"/>
     <cellStyle name="Moneda 2 4" xfId="22" xr:uid="{C856720B-E8A6-4AC5-AB83-CF98E3EF83EE}"/>
     <cellStyle name="Moneda 2 4 2" xfId="81" xr:uid="{B905E27A-E356-4F29-AEE3-13771753F9DA}"/>
     <cellStyle name="Moneda 2 4 3" xfId="127" xr:uid="{DACFF950-40D1-41D6-8EB6-B447D99CED5A}"/>
     <cellStyle name="Moneda 2 4 4" xfId="214" xr:uid="{9E337CD0-9A13-4633-90FE-83FCB36E59E5}"/>
+    <cellStyle name="Moneda 2 4 5" xfId="262" xr:uid="{756D9400-C2EE-4B19-AB46-64163E84F785}"/>
     <cellStyle name="Moneda 2 5" xfId="38" xr:uid="{543CB192-C6A7-4F18-96D2-D078B55A61CB}"/>
     <cellStyle name="Moneda 2 5 2" xfId="84" xr:uid="{486A89DC-ECBC-402C-A58A-FBAC4FFCF01C}"/>
     <cellStyle name="Moneda 2 5 3" xfId="130" xr:uid="{A43C2057-7CF1-475D-A586-BC553198FEBE}"/>
     <cellStyle name="Moneda 2 5 4" xfId="217" xr:uid="{9CCC8394-F96F-47AF-A39A-120DF642B610}"/>
+    <cellStyle name="Moneda 2 5 5" xfId="265" xr:uid="{11E2AF9D-3A55-45E3-9B9C-CEF6FAC25694}"/>
     <cellStyle name="Moneda 2 6" xfId="41" xr:uid="{14D1D7A7-6BF3-4644-A820-240992FDB63E}"/>
     <cellStyle name="Moneda 2 6 2" xfId="87" xr:uid="{93DBA7D8-4A16-4297-AED1-7E763BB07D3B}"/>
     <cellStyle name="Moneda 2 6 3" xfId="133" xr:uid="{AC18E7A7-AD52-4063-9EC4-5B12B12AC1E2}"/>
     <cellStyle name="Moneda 2 6 4" xfId="220" xr:uid="{7BB2960D-19E2-4607-A815-E350CD4D4E2E}"/>
+    <cellStyle name="Moneda 2 6 5" xfId="268" xr:uid="{99FE5A0D-8E09-4DE5-8F7E-172BD753D330}"/>
     <cellStyle name="Moneda 2 7" xfId="44" xr:uid="{FFF1D48E-6176-4CF7-81EF-EE5AC9546ED6}"/>
     <cellStyle name="Moneda 2 7 2" xfId="90" xr:uid="{662C375C-70C8-4901-893E-E33A91557316}"/>
     <cellStyle name="Moneda 2 7 3" xfId="136" xr:uid="{03CD9128-CD3A-4ACF-83FD-DD49DD62D230}"/>
     <cellStyle name="Moneda 2 7 4" xfId="223" xr:uid="{0982ADCE-1E5F-44E3-AFFF-9514712C3B4C}"/>
+    <cellStyle name="Moneda 2 7 5" xfId="271" xr:uid="{BBF80D97-DB48-4966-BE25-BCD55EF437BB}"/>
     <cellStyle name="Moneda 2 8" xfId="48" xr:uid="{505EEDDC-CA34-4C8E-894B-E00A33C56132}"/>
     <cellStyle name="Moneda 2 8 2" xfId="94" xr:uid="{0C48F0DF-9A9B-47F2-B5B5-8C5A4F507DB2}"/>
     <cellStyle name="Moneda 2 8 3" xfId="140" xr:uid="{2DDA0C3B-B4D2-4D0E-91AE-8417131A2ED7}"/>
     <cellStyle name="Moneda 2 8 4" xfId="227" xr:uid="{DB10AF3D-5235-4D42-B947-427251072FEA}"/>
+    <cellStyle name="Moneda 2 8 5" xfId="275" xr:uid="{60B948D5-B4AE-405B-A0FA-C9A8F9AAB957}"/>
     <cellStyle name="Moneda 2 9" xfId="53" xr:uid="{9DEFD098-5F68-4A9D-A770-6123E150DD6E}"/>
     <cellStyle name="Moneda 2 9 2" xfId="99" xr:uid="{4C4F8FDC-C495-441C-A948-3A3941756072}"/>
     <cellStyle name="Moneda 2 9 3" xfId="145" xr:uid="{A15D5E0D-4857-485B-B899-5C79ED2126D5}"/>
     <cellStyle name="Moneda 2 9 4" xfId="232" xr:uid="{2FB3D762-2DBC-41C3-8A4B-F42EAB96A89D}"/>
+    <cellStyle name="Moneda 2 9 5" xfId="280" xr:uid="{B9D66BE8-B78D-4203-B98E-4933871DB0CE}"/>
     <cellStyle name="Moneda 3" xfId="47" xr:uid="{85CAFDD7-BC80-42AB-AB19-AD3F8539702F}"/>
     <cellStyle name="Moneda 3 10" xfId="210" xr:uid="{47A1FA21-1B88-42B7-9293-A37799E2DB5B}"/>
+    <cellStyle name="Moneda 3 11" xfId="258" xr:uid="{6BC7C7A4-3049-4AAA-8D6A-1FF08649CC67}"/>
     <cellStyle name="Moneda 3 2" xfId="51" xr:uid="{96C4286F-DBE0-4288-BB74-90F8B138EA6D}"/>
     <cellStyle name="Moneda 3 2 2" xfId="97" xr:uid="{20E23E69-96B9-4897-A347-54D52E8BA6FB}"/>
     <cellStyle name="Moneda 3 2 3" xfId="143" xr:uid="{71BD2A54-4155-4016-BAFD-7CA7F2237F57}"/>
     <cellStyle name="Moneda 3 2 4" xfId="230" xr:uid="{E79D693B-91F0-4C13-87C9-AE6C3239D037}"/>
+    <cellStyle name="Moneda 3 2 5" xfId="278" xr:uid="{3696193C-A3E0-4286-8BAF-6FACBE41F256}"/>
     <cellStyle name="Moneda 3 3" xfId="56" xr:uid="{34925A72-50E9-4BB6-AB5E-29A42278EC06}"/>
     <cellStyle name="Moneda 3 3 2" xfId="102" xr:uid="{6A49C2AA-C587-4F11-A173-65C84D02B8F7}"/>
     <cellStyle name="Moneda 3 3 3" xfId="148" xr:uid="{302BEA78-715F-4324-ACD0-913C3FAB3E5F}"/>
     <cellStyle name="Moneda 3 3 4" xfId="235" xr:uid="{EA31B6D8-5FA9-41AC-B355-44EEF417FEB9}"/>
+    <cellStyle name="Moneda 3 3 5" xfId="283" xr:uid="{A5CE32CD-564E-440C-BAE0-63D3E577274E}"/>
     <cellStyle name="Moneda 3 4" xfId="62" xr:uid="{2CBB34AE-A901-454F-8B45-5C34D3D6C141}"/>
     <cellStyle name="Moneda 3 4 2" xfId="108" xr:uid="{B89AE0FB-3978-48B9-BB55-8875ECCD656E}"/>
     <cellStyle name="Moneda 3 4 3" xfId="154" xr:uid="{63E6F307-7839-490B-A5B9-66ED924F46EC}"/>
     <cellStyle name="Moneda 3 4 4" xfId="241" xr:uid="{B185CB40-E726-4791-8F3F-DAC9A0F48648}"/>
+    <cellStyle name="Moneda 3 4 5" xfId="289" xr:uid="{B9BF1107-5410-4E78-B117-8F7752C80ED8}"/>
     <cellStyle name="Moneda 3 5" xfId="67" xr:uid="{3FFD3DD0-5204-47D9-B534-A50AAA72ACB7}"/>
     <cellStyle name="Moneda 3 5 2" xfId="113" xr:uid="{20EED5AE-EC9D-4E21-859D-241A45CFABB1}"/>
     <cellStyle name="Moneda 3 5 3" xfId="159" xr:uid="{C2B9F339-D756-4C5D-8C08-99A8D24897C3}"/>
     <cellStyle name="Moneda 3 5 4" xfId="246" xr:uid="{6C021489-637C-4A39-99E4-5D3E6B3DD5E7}"/>
+    <cellStyle name="Moneda 3 5 5" xfId="294" xr:uid="{C46E3977-710A-48E0-96DB-326FA64F309A}"/>
     <cellStyle name="Moneda 3 6" xfId="72" xr:uid="{1123ABF6-735C-4B1A-9A9D-13E29730795D}"/>
     <cellStyle name="Moneda 3 6 2" xfId="118" xr:uid="{FC7BC7D2-0411-41D8-AA8D-F1A5D239DB53}"/>
     <cellStyle name="Moneda 3 6 3" xfId="164" xr:uid="{981CB1AA-33DA-4075-8E2C-8C3DF7FB9680}"/>
     <cellStyle name="Moneda 3 6 4" xfId="251" xr:uid="{D054D014-DA1F-4C61-9ADB-EE6129C7176A}"/>
+    <cellStyle name="Moneda 3 6 5" xfId="299" xr:uid="{118F50C4-5FE4-4124-8FE5-A74A0441B6C4}"/>
     <cellStyle name="Moneda 3 7" xfId="93" xr:uid="{143FA41C-45A1-4D0D-BCEB-2A6CD584F1A4}"/>
     <cellStyle name="Moneda 3 7 2" xfId="139" xr:uid="{9666F50D-330E-4835-BC7E-5A08B5870F28}"/>
     <cellStyle name="Moneda 3 7 3" xfId="226" xr:uid="{AEE6FEBA-FC88-460F-A1E4-CFC753A2AD21}"/>
+    <cellStyle name="Moneda 3 7 4" xfId="274" xr:uid="{989D063F-734C-42F6-91A4-12C9992A8444}"/>
     <cellStyle name="Moneda 3 8" xfId="77" xr:uid="{9D38D546-6677-4929-8E55-423271F0B76D}"/>
     <cellStyle name="Moneda 3 9" xfId="123" xr:uid="{71D30BF2-29FB-4DB6-B941-317AF9935F77}"/>
     <cellStyle name="Moneda 4" xfId="52" xr:uid="{37C3E87F-62D1-4247-9FCD-BF46D4177B38}"/>
+    <cellStyle name="Moneda 4 10" xfId="259" xr:uid="{311046E6-A922-4B45-A93C-82F300601548}"/>
     <cellStyle name="Moneda 4 2" xfId="57" xr:uid="{0D33716A-1B52-49C5-B03E-298B115A6242}"/>
     <cellStyle name="Moneda 4 2 2" xfId="103" xr:uid="{AACBA8BA-7D9F-4375-8223-C5DC3A39545A}"/>
     <cellStyle name="Moneda 4 2 3" xfId="149" xr:uid="{001258B4-E819-4E14-A4BC-69EC9A476FE6}"/>
     <cellStyle name="Moneda 4 2 4" xfId="236" xr:uid="{D36259C9-FD7D-400D-BCD1-26EC9D76B543}"/>
+    <cellStyle name="Moneda 4 2 5" xfId="284" xr:uid="{0FA7BD94-F0A2-416C-B6C0-7DC8147AE08F}"/>
     <cellStyle name="Moneda 4 3" xfId="63" xr:uid="{ED1C5CE2-B4BC-4A3D-AB59-9C0356444D01}"/>
     <cellStyle name="Moneda 4 3 2" xfId="109" xr:uid="{1CD0CC82-5263-4DEE-B94E-D77A2438921E}"/>
     <cellStyle name="Moneda 4 3 3" xfId="155" xr:uid="{5DD14E02-C160-4EEF-8CB5-E2E7D2B0945B}"/>
     <cellStyle name="Moneda 4 3 4" xfId="242" xr:uid="{D4B83A40-21EC-497B-9D2A-C8198487483A}"/>
+    <cellStyle name="Moneda 4 3 5" xfId="290" xr:uid="{2ECB4995-9C43-4ABA-99F8-67B163A24DF0}"/>
     <cellStyle name="Moneda 4 4" xfId="68" xr:uid="{A8A598A9-970D-47DC-B1E1-29E7D47DD090}"/>
     <cellStyle name="Moneda 4 4 2" xfId="114" xr:uid="{59279AA4-CD79-48BE-BA6F-A548E9E73AA7}"/>
     <cellStyle name="Moneda 4 4 3" xfId="160" xr:uid="{809D950E-8DD7-4C72-A60E-6AEC953EFB87}"/>
     <cellStyle name="Moneda 4 4 4" xfId="247" xr:uid="{7E083487-A7F5-4EDF-9737-4F0A76B48A43}"/>
+    <cellStyle name="Moneda 4 4 5" xfId="295" xr:uid="{6CD6C3CD-12E5-4BF9-9916-2AFFEAB6D009}"/>
     <cellStyle name="Moneda 4 5" xfId="73" xr:uid="{69AE1A5E-3A9B-4A7C-B962-B3043E993D8D}"/>
     <cellStyle name="Moneda 4 5 2" xfId="119" xr:uid="{41931F4B-6B43-4774-8F41-F8AACDBD14B2}"/>
     <cellStyle name="Moneda 4 5 3" xfId="165" xr:uid="{50D6C0B2-B998-4C77-AEDD-420AE00EDE82}"/>
     <cellStyle name="Moneda 4 5 4" xfId="252" xr:uid="{F2BF692C-6CE4-47D1-847C-7C8D4010FB28}"/>
+    <cellStyle name="Moneda 4 5 5" xfId="300" xr:uid="{3F1B598D-56C4-4098-9205-DD9611CED73B}"/>
     <cellStyle name="Moneda 4 6" xfId="98" xr:uid="{4F9D7CCE-4CC0-4C6C-9305-EA75C4F3875B}"/>
     <cellStyle name="Moneda 4 6 2" xfId="144" xr:uid="{39DE7B02-8CEB-402C-9AA1-EABC50DB2540}"/>
     <cellStyle name="Moneda 4 6 3" xfId="231" xr:uid="{AF02880C-F531-4C7D-AD09-5D7917357588}"/>
+    <cellStyle name="Moneda 4 6 4" xfId="279" xr:uid="{02FBC436-F645-465E-8F75-707BB06D02AA}"/>
     <cellStyle name="Moneda 4 7" xfId="78" xr:uid="{35E27D55-94D0-4DEB-AA9D-FDA546D20F9E}"/>
     <cellStyle name="Moneda 4 8" xfId="124" xr:uid="{D4251BD3-7034-44C2-AADD-AB8F76DC2AB0}"/>
     <cellStyle name="Moneda 4 9" xfId="211" xr:uid="{56745075-97AD-4F75-A521-4FC3CA6F3143}"/>
@@ -1329,7 +1423,9 @@
     <cellStyle name="Moneda 5 2" xfId="104" xr:uid="{AAA1E068-29D5-4C3E-BCED-A365C80CD4D7}"/>
     <cellStyle name="Moneda 5 3" xfId="150" xr:uid="{E7798976-6AE6-4957-B10E-F095B839ADD4}"/>
     <cellStyle name="Moneda 5 4" xfId="237" xr:uid="{BB71DFD8-A349-4772-BDC8-941CB4398B27}"/>
+    <cellStyle name="Moneda 5 5" xfId="285" xr:uid="{771CEC20-E009-4C58-BC25-3B35DC9173F9}"/>
     <cellStyle name="Moneda 6" xfId="253" xr:uid="{A995F97A-4D71-43DC-9949-BFE8D21A8A32}"/>
+    <cellStyle name="Moneda 6 2" xfId="301" xr:uid="{9D0714FA-6736-4DDF-9F4B-F221C4021677}"/>
     <cellStyle name="Neutral" xfId="173" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="10" xr:uid="{0B95864E-03D8-4F67-B990-2AF43328EB3C}"/>
@@ -1346,6 +1442,8 @@
     <cellStyle name="Normal 15 2" xfId="20" xr:uid="{55332A69-B081-4BAD-8A20-77725DD92B5C}"/>
     <cellStyle name="Normal 15 3" xfId="35" xr:uid="{CCD54986-C90C-4098-A1A6-8D44F35D6691}"/>
     <cellStyle name="Normal 16" xfId="254" xr:uid="{25D55C6B-2597-45A4-85E5-AD68CDB53B3A}"/>
+    <cellStyle name="Normal 16 2" xfId="302" xr:uid="{6F6D7CDF-F565-41AE-BB55-FCED5269665F}"/>
+    <cellStyle name="Normal 17" xfId="303" xr:uid="{FA37BBD5-B52E-4D72-8E31-05C4DA7A2670}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{0C12119C-D43E-49BD-BFF9-9B05911E5BF0}"/>
     <cellStyle name="Normal 2 2" xfId="2" xr:uid="{A7FB9C6F-E634-4B2E-86BE-BBD572D5AFB7}"/>
     <cellStyle name="Normal 2 3" xfId="16" xr:uid="{76702E4E-6488-468F-BE6C-98D1A76F4C63}"/>
@@ -1387,7 +1485,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46106.545731828701" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46113.481429861109" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1420,7 +1518,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7538"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7612"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1436,32 +1534,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1160"/>
+    <n v="1349"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="1098"/>
+    <n v="1092"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1286"/>
+    <n v="1101"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1392"/>
+    <n v="1254"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1380"/>
+    <n v="1478"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="1222"/>
+    <n v="1338"/>
   </r>
   <r>
     <x v="0"/>
@@ -1471,7 +1569,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="7538"/>
+    <n v="7612"/>
   </r>
   <r>
     <x v="1"/>
@@ -1677,7 +1775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="990" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="149" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2170,14 +2268,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1160</v>
+        <v>1349</v>
       </c>
       <c r="D3" s="31">
-        <v>1160</v>
+        <v>1349</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>193.33333333333334</v>
+        <v>224.83333333333334</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2190,14 +2288,14 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="D4" s="31">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="32" t="s">
@@ -2214,14 +2312,14 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1286</v>
+        <v>1101</v>
       </c>
       <c r="D5" s="31">
-        <v>1286</v>
+        <v>1101</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>214.33333333333334</v>
+        <v>183.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -2234,14 +2332,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1392</v>
+        <v>1254</v>
       </c>
       <c r="D6" s="31">
-        <v>1392</v>
+        <v>1254</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2254,14 +2352,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="D7" s="31">
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>230</v>
+        <v>246.33333333333334</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2274,14 +2372,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>1222</v>
+        <v>1338</v>
       </c>
       <c r="D8" s="31">
-        <v>1222</v>
+        <v>1338</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>203.66666666666666</v>
+        <v>223</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2303,11 +2401,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>7538</v>
+        <v>7612</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>7538</v>
+        <v>7612</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2327,7 +2425,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>251.26666666666665</v>
+        <v>253.73333333333335</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2411,25 +2509,25 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1160</v>
+        <v>1349</v>
       </c>
       <c r="Q12" s="35">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="R12" s="35">
-        <v>1286</v>
+        <v>1101</v>
       </c>
       <c r="S12" s="35">
-        <v>1392</v>
+        <v>1254</v>
       </c>
       <c r="T12" s="35">
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="U12" s="35">
-        <v>1222</v>
+        <v>1338</v>
       </c>
       <c r="V12" s="35">
-        <v>7538</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2616,25 +2714,25 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1160</v>
+        <v>1349</v>
       </c>
       <c r="Q17" s="35">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="R17" s="35">
-        <v>1286</v>
+        <v>1101</v>
       </c>
       <c r="S17" s="35">
-        <v>1392</v>
+        <v>1254</v>
       </c>
       <c r="T17" s="35">
-        <v>1380</v>
+        <v>1478</v>
       </c>
       <c r="U17" s="35">
-        <v>1222</v>
+        <v>1338</v>
       </c>
       <c r="V17" s="35">
-        <v>7538</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2751,7 +2849,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46105.854166666664</v>
+        <v>46112.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3439,6 +3537,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3673,7 +3782,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3682,18 +3791,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3712,21 +3821,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F2E453A-A053-43DD-989D-FEBFFC27E551}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540BFB52-CF1C-459F-9A6C-ECEAE260F414}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="149" r:id="rId2"/>
+    <pivotCache cacheId="17" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1485,7 +1485,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46113.481429861109" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46127.481692824076" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1518,7 +1518,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7612"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7402"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1534,7 +1534,7 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1349"/>
+    <n v="1375"/>
   </r>
   <r>
     <x v="0"/>
@@ -1549,17 +1549,17 @@
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1254"/>
+    <n v="1178"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1478"/>
+    <n v="1346"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="1338"/>
+    <n v="1310"/>
   </r>
   <r>
     <x v="0"/>
@@ -1569,7 +1569,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="7612"/>
+    <n v="7402"/>
   </r>
   <r>
     <x v="1"/>
@@ -1775,7 +1775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="149" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2268,14 +2268,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="D3" s="31">
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>224.83333333333334</v>
+        <v>229.16666666666666</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2332,14 +2332,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1254</v>
+        <v>1178</v>
       </c>
       <c r="D6" s="31">
-        <v>1254</v>
+        <v>1178</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>209</v>
+        <v>196.33333333333334</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2352,14 +2352,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1478</v>
+        <v>1346</v>
       </c>
       <c r="D7" s="31">
-        <v>1478</v>
+        <v>1346</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>246.33333333333334</v>
+        <v>224.33333333333334</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2372,14 +2372,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>1338</v>
+        <v>1310</v>
       </c>
       <c r="D8" s="31">
-        <v>1338</v>
+        <v>1310</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>223</v>
+        <v>218.33333333333334</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2401,11 +2401,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>7612</v>
+        <v>7402</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>7612</v>
+        <v>7402</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>253.73333333333335</v>
+        <v>246.73333333333335</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2509,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="Q12" s="35">
         <v>1092</v>
@@ -2518,16 +2518,16 @@
         <v>1101</v>
       </c>
       <c r="S12" s="35">
-        <v>1254</v>
+        <v>1178</v>
       </c>
       <c r="T12" s="35">
-        <v>1478</v>
+        <v>1346</v>
       </c>
       <c r="U12" s="35">
-        <v>1338</v>
+        <v>1310</v>
       </c>
       <c r="V12" s="35">
-        <v>7612</v>
+        <v>7402</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2714,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1349</v>
+        <v>1375</v>
       </c>
       <c r="Q17" s="35">
         <v>1092</v>
@@ -2723,16 +2723,16 @@
         <v>1101</v>
       </c>
       <c r="S17" s="35">
-        <v>1254</v>
+        <v>1178</v>
       </c>
       <c r="T17" s="35">
-        <v>1478</v>
+        <v>1346</v>
       </c>
       <c r="U17" s="35">
-        <v>1338</v>
+        <v>1310</v>
       </c>
       <c r="V17" s="35">
-        <v>7612</v>
+        <v>7402</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -3548,6 +3548,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3782,15 +3791,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
@@ -3803,6 +3803,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3819,12 +3827,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540BFB52-CF1C-459F-9A6C-ECEAE260F414}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E1D879-188C-41DC-84F1-50E29F7BEA75}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId2"/>
+    <pivotCache cacheId="1749" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -118,7 +118,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1155,14 +1155,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="304">
@@ -1485,7 +1483,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46127.481692824076" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46147.519752893517" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1518,7 +1516,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7402"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6798"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1534,32 +1532,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1375"/>
+    <n v="1230"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="1092"/>
+    <n v="1042"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1101"/>
+    <n v="1191"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1178"/>
+    <n v="1191"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1346"/>
+    <n v="1200"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="1310"/>
+    <n v="944"/>
   </r>
   <r>
     <x v="0"/>
@@ -1569,7 +1567,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="7402"/>
+    <n v="6798"/>
   </r>
   <r>
     <x v="1"/>
@@ -1775,7 +1773,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="1749" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2191,7 +2189,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC90F7AF-2A69-4C5E-9FF5-F9DB01805A13}">
   <dimension ref="A1:AF53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="7.85546875" customWidth="1"/>
@@ -2199,7 +2197,8 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -2207,7 +2206,7 @@
     <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>19</v>
       </c>
@@ -2225,7 +2224,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2236,30 +2235,30 @@
         <v>2</v>
       </c>
       <c r="D2" s="8">
-        <v>46084</v>
+        <v>46147</v>
       </c>
       <c r="E2" s="8">
         <f>+D2+1</f>
-        <v>46085</v>
+        <v>46148</v>
       </c>
       <c r="F2" s="8">
         <f t="shared" ref="F2:G2" si="0">+E2+1</f>
-        <v>46086</v>
+        <v>46149</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" si="0"/>
-        <v>46087</v>
+        <v>46150</v>
       </c>
       <c r="H2" s="8">
         <f>+G2+3</f>
-        <v>46090</v>
+        <v>46153</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2268,18 +2267,18 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1375</v>
-      </c>
-      <c r="D3" s="31">
-        <v>1375</v>
+        <v>1230</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1230</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>229.16666666666666</v>
+        <v>205</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -2288,22 +2287,22 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>1092</v>
-      </c>
-      <c r="D4" s="31">
-        <v>1092</v>
+        <v>1042</v>
+      </c>
+      <c r="D4" s="34">
+        <v>1042</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>182</v>
+        <v>173.66666666666666</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="32"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="P4" s="31"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
@@ -2312,18 +2311,18 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1101</v>
-      </c>
-      <c r="D5" s="31">
-        <v>1101</v>
+        <v>1191</v>
+      </c>
+      <c r="D5" s="34">
+        <v>1191</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>183.5</v>
+        <v>198.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
@@ -2332,18 +2331,18 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1178</v>
-      </c>
-      <c r="D6" s="31">
-        <v>1178</v>
+        <v>1191</v>
+      </c>
+      <c r="D6" s="34">
+        <v>1191</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>196.33333333333334</v>
+        <v>198.5</v>
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>1</v>
       </c>
@@ -2352,18 +2351,18 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1346</v>
-      </c>
-      <c r="D7" s="31">
-        <v>1346</v>
+        <v>1200</v>
+      </c>
+      <c r="D7" s="34">
+        <v>1200</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>224.33333333333334</v>
+        <v>200</v>
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
@@ -2372,18 +2371,18 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>1310</v>
-      </c>
-      <c r="D8" s="31">
-        <v>1310</v>
+        <v>944</v>
+      </c>
+      <c r="D8" s="34">
+        <v>944</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>218.33333333333334</v>
+        <v>157.33333333333334</v>
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:22" hidden="1">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
@@ -2392,7 +2391,7 @@
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
@@ -2401,11 +2400,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>7402</v>
+        <v>6798</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>7402</v>
+        <v>6798</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2425,7 +2424,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>246.73333333333335</v>
+        <v>226.6</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2435,7 +2434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -2471,7 +2470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -2483,23 +2482,23 @@
       </c>
       <c r="D12" s="8">
         <f>+H2+1</f>
-        <v>46091</v>
+        <v>46154</v>
       </c>
       <c r="E12" s="8">
         <f>+D12+1</f>
-        <v>46092</v>
+        <v>46155</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" ref="F12:G12" si="4">+E12+1</f>
-        <v>46093</v>
+        <v>46156</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="4"/>
-        <v>46094</v>
+        <v>46157</v>
       </c>
       <c r="H12" s="8">
         <f>+G12+3</f>
-        <v>46097</v>
+        <v>46160</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>3</v>
@@ -2509,28 +2508,28 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="Q12" s="35">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="R12" s="35">
-        <v>1101</v>
+        <v>1191</v>
       </c>
       <c r="S12" s="35">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="T12" s="35">
-        <v>1346</v>
+        <v>1200</v>
       </c>
       <c r="U12" s="35">
-        <v>1310</v>
+        <v>944</v>
       </c>
       <c r="V12" s="35">
-        <v>7402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -2571,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -2653,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -2694,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
@@ -2714,28 +2713,28 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="Q17" s="35">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="R17" s="35">
-        <v>1101</v>
+        <v>1191</v>
       </c>
       <c r="S17" s="35">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="T17" s="35">
-        <v>1346</v>
+        <v>1200</v>
       </c>
       <c r="U17" s="35">
-        <v>1310</v>
+        <v>944</v>
       </c>
       <c r="V17" s="35">
-        <v>7402</v>
-      </c>
-    </row>
-    <row r="18" spans="1:32">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>11</v>
       </c>
@@ -2752,7 +2751,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:32" hidden="1">
+    <row r="19" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -2761,7 +2760,7 @@
       <c r="I19" s="26"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
@@ -2798,9 +2797,9 @@
       </c>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -2809,12 +2808,12 @@
       <c r="H21" s="21"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="O21" s="32" t="s">
+      <c r="O21" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="32"/>
-    </row>
-    <row r="22" spans="1:32">
+      <c r="P21" s="31"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>12</v>
       </c>
@@ -2826,23 +2825,23 @@
       </c>
       <c r="D22" s="8">
         <f>+H12+1</f>
-        <v>46098</v>
+        <v>46161</v>
       </c>
       <c r="E22" s="8">
         <f>+D22+1</f>
-        <v>46099</v>
+        <v>46162</v>
       </c>
       <c r="F22" s="8">
         <f t="shared" ref="F22:G22" si="8">+E22+1</f>
-        <v>46100</v>
+        <v>46163</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="8"/>
-        <v>46101</v>
+        <v>46164</v>
       </c>
       <c r="H22" s="8">
         <f>+G22+3</f>
-        <v>46104</v>
+        <v>46167</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>3</v>
@@ -2852,7 +2851,7 @@
         <v>46112.854166666664</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>12</v>
       </c>
@@ -2869,7 +2868,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>12</v>
       </c>
@@ -2886,7 +2885,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>12</v>
       </c>
@@ -2903,7 +2902,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>12</v>
       </c>
@@ -2920,7 +2919,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>12</v>
       </c>
@@ -2937,7 +2936,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>12</v>
       </c>
@@ -2954,7 +2953,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:32" hidden="1">
+    <row r="29" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>12</v>
       </c>
@@ -2963,7 +2962,7 @@
       <c r="I29" s="26"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>12</v>
       </c>
@@ -3000,9 +2999,9 @@
       </c>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="1:32">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3013,7 +3012,7 @@
       <c r="J31" s="3"/>
       <c r="AF31" s="27"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>13</v>
       </c>
@@ -3025,23 +3024,23 @@
       </c>
       <c r="D32" s="8">
         <f>+H22+1</f>
-        <v>46105</v>
+        <v>46168</v>
       </c>
       <c r="E32" s="8">
         <f>+D32+1</f>
-        <v>46106</v>
+        <v>46169</v>
       </c>
       <c r="F32" s="8">
         <f t="shared" ref="F32:G32" si="12">+E32+1</f>
-        <v>46107</v>
+        <v>46170</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="12"/>
-        <v>46108</v>
+        <v>46171</v>
       </c>
       <c r="H32" s="8">
         <f>+G32+3</f>
-        <v>46111</v>
+        <v>46174</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>3</v>
@@ -3049,7 +3048,7 @@
       <c r="J32" s="1"/>
       <c r="AF32" s="27"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>13</v>
       </c>
@@ -3071,7 +3070,7 @@
       <c r="J33" s="3"/>
       <c r="AF33" s="27"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>13</v>
       </c>
@@ -3093,7 +3092,7 @@
       <c r="J34" s="3"/>
       <c r="AF34" s="27"/>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>13</v>
       </c>
@@ -3115,7 +3114,7 @@
       <c r="J35" s="3"/>
       <c r="AF35" s="27"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>13</v>
       </c>
@@ -3137,7 +3136,7 @@
       <c r="J36" s="3"/>
       <c r="AF36" s="27"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>13</v>
       </c>
@@ -3159,7 +3158,7 @@
       <c r="J37" s="3"/>
       <c r="AF37" s="27"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>13</v>
       </c>
@@ -3181,7 +3180,7 @@
       <c r="J38" s="3"/>
       <c r="AF38" s="27"/>
     </row>
-    <row r="39" spans="1:32" hidden="1">
+    <row r="39" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>13</v>
       </c>
@@ -3196,7 +3195,7 @@
       <c r="J39" s="3"/>
       <c r="AF39" s="27"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>13</v>
       </c>
@@ -3234,9 +3233,9 @@
       <c r="J40" s="20"/>
       <c r="AF40" s="27"/>
     </row>
-    <row r="41" spans="1:32">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A41" s="33"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3247,7 +3246,7 @@
       <c r="J41" s="3"/>
       <c r="AF41" s="27"/>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>14</v>
       </c>
@@ -3259,23 +3258,23 @@
       </c>
       <c r="D42" s="8">
         <f>+H32+1</f>
-        <v>46112</v>
+        <v>46175</v>
       </c>
       <c r="E42" s="8">
         <f>+D42+1</f>
-        <v>46113</v>
+        <v>46176</v>
       </c>
       <c r="F42" s="8">
         <f t="shared" ref="F42:G42" si="16">+E42+1</f>
-        <v>46114</v>
+        <v>46177</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="16"/>
-        <v>46115</v>
+        <v>46178</v>
       </c>
       <c r="H42" s="8">
         <f>+G42+3</f>
-        <v>46118</v>
+        <v>46181</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>3</v>
@@ -3283,7 +3282,7 @@
       <c r="J42" s="1"/>
       <c r="AF42" s="27"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>14</v>
       </c>
@@ -3306,7 +3305,7 @@
       <c r="J43" s="3"/>
       <c r="AF43" s="27"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>14</v>
       </c>
@@ -3329,7 +3328,7 @@
       <c r="J44" s="3"/>
       <c r="AF44" s="27"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>14</v>
       </c>
@@ -3352,7 +3351,7 @@
       <c r="J45" s="3"/>
       <c r="AF45" s="27"/>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>14</v>
       </c>
@@ -3375,7 +3374,7 @@
       <c r="J46" s="3"/>
       <c r="AF46" s="27"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>14</v>
       </c>
@@ -3398,7 +3397,7 @@
       <c r="J47" s="3"/>
       <c r="AF47" s="27"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>14</v>
       </c>
@@ -3421,7 +3420,7 @@
       <c r="J48" s="3"/>
       <c r="AF48" s="27"/>
     </row>
-    <row r="49" spans="1:32" hidden="1">
+    <row r="49" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>14</v>
       </c>
@@ -3436,7 +3435,7 @@
       <c r="J49" s="3"/>
       <c r="AF49" s="27"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>14</v>
       </c>
@@ -3474,9 +3473,9 @@
       <c r="J50" s="20"/>
       <c r="AF50" s="27"/>
     </row>
-    <row r="51" spans="1:32">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
       <c r="C51" s="2"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
@@ -3487,9 +3486,9 @@
       <c r="J51" s="3"/>
       <c r="AF51" s="27"/>
     </row>
-    <row r="52" spans="1:32">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21">
         <v>0</v>
@@ -3509,9 +3508,9 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="1:32">
-      <c r="A53" s="33"/>
-      <c r="B53" s="33"/>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3548,15 +3547,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3791,6 +3781,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
@@ -3803,14 +3802,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3827,4 +3818,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -3557,8 +3557,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e7f576afb137e09b84b3a9dd4651f92f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="81da8bc2beca58c86a5d31f30ec09267" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
     <xsd:import namespace="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <xsd:element name="properties">
@@ -3616,7 +3616,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0e055066-1d0b-4836-b0e5-54071a0012ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0e055066-1d0b-4836-b0e5-54071a0012ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -3654,7 +3654,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="396b9688-3d64-4f4f-b40d-59fd809f50b1" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3673,7 +3673,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -3701,8 +3701,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -3811,20 +3811,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36A93179-9D9C-4D14-A08B-C1A220B5EC1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40DF0DFE-F3D1-4294-8326-0317E0AC0904}"/>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{540BFB52-CF1C-459F-9A6C-ECEAE260F414}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96B22DE9-845C-4012-9719-3BCEAAC603ED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
   <sheets>
     <sheet name="Estatus diario" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId2"/>
+    <pivotCache cacheId="139" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1485,7 +1485,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46127.481692824076" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46148.494425810182" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1775,7 +1775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46112.854166666664</v>
+        <v>46147.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3548,17 +3548,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e7f576afb137e09b84b3a9dd4651f92f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="81da8bc2beca58c86a5d31f30ec09267" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
     <xsd:import namespace="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <xsd:element name="properties">
@@ -3616,7 +3607,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0e055066-1d0b-4836-b0e5-54071a0012ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0e055066-1d0b-4836-b0e5-54071a0012ab" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -3654,7 +3645,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="396b9688-3d64-4f4f-b40d-59fd809f50b1" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3673,7 +3664,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -3701,8 +3692,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -3791,6 +3782,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
@@ -3803,13 +3803,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB9C6E1-9ED5-4F9E-A921-9601F6BFCC2B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40DF0DFE-F3D1-4294-8326-0317E0AC0904}"/>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96B22DE9-845C-4012-9719-3BCEAAC603ED}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D37F5BCD-5942-498E-BE59-0F1DF6A5CC1F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="139" r:id="rId2"/>
+    <pivotCache cacheId="790" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1155,14 +1155,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="304">
@@ -1485,7 +1483,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46148.494425810182" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46148.707666087961" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1518,7 +1516,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="7402"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6798"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1534,32 +1532,32 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1375"/>
+    <n v="1230"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="1092"/>
+    <n v="1042"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1101"/>
+    <n v="1191"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1178"/>
+    <n v="1191"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1346"/>
+    <n v="1200"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="1310"/>
+    <n v="944"/>
   </r>
   <r>
     <x v="0"/>
@@ -1569,7 +1567,7 @@
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="7402"/>
+    <n v="6798"/>
   </r>
   <r>
     <x v="1"/>
@@ -1775,7 +1773,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="139" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="790" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2199,7 +2197,8 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -2268,14 +2267,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1375</v>
-      </c>
-      <c r="D3" s="31">
-        <v>1375</v>
+        <v>1230</v>
+      </c>
+      <c r="D3" s="34">
+        <v>1230</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>229.16666666666666</v>
+        <v>205</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2288,20 +2287,20 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>1092</v>
-      </c>
-      <c r="D4" s="31">
-        <v>1092</v>
+        <v>1042</v>
+      </c>
+      <c r="D4" s="34">
+        <v>1042</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>182</v>
+        <v>173.66666666666666</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="32"/>
+      <c r="P4" s="31"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="13" t="s">
@@ -2312,14 +2311,14 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1101</v>
-      </c>
-      <c r="D5" s="31">
-        <v>1101</v>
+        <v>1191</v>
+      </c>
+      <c r="D5" s="34">
+        <v>1191</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>183.5</v>
+        <v>198.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -2332,14 +2331,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1178</v>
-      </c>
-      <c r="D6" s="31">
-        <v>1178</v>
+        <v>1191</v>
+      </c>
+      <c r="D6" s="34">
+        <v>1191</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>196.33333333333334</v>
+        <v>198.5</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2352,14 +2351,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1346</v>
-      </c>
-      <c r="D7" s="31">
-        <v>1346</v>
+        <v>1200</v>
+      </c>
+      <c r="D7" s="34">
+        <v>1200</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>224.33333333333334</v>
+        <v>200</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2372,14 +2371,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>1310</v>
-      </c>
-      <c r="D8" s="31">
-        <v>1310</v>
+        <v>944</v>
+      </c>
+      <c r="D8" s="34">
+        <v>944</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>218.33333333333334</v>
+        <v>157.33333333333334</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2401,11 +2400,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>7402</v>
+        <v>6798</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>7402</v>
+        <v>6798</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2425,7 +2424,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>246.73333333333335</v>
+        <v>226.6</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2509,25 +2508,25 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="Q12" s="35">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="R12" s="35">
-        <v>1101</v>
+        <v>1191</v>
       </c>
       <c r="S12" s="35">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="T12" s="35">
-        <v>1346</v>
+        <v>1200</v>
       </c>
       <c r="U12" s="35">
-        <v>1310</v>
+        <v>944</v>
       </c>
       <c r="V12" s="35">
-        <v>7402</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2714,25 +2713,25 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1375</v>
+        <v>1230</v>
       </c>
       <c r="Q17" s="35">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="R17" s="35">
-        <v>1101</v>
+        <v>1191</v>
       </c>
       <c r="S17" s="35">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="T17" s="35">
-        <v>1346</v>
+        <v>1200</v>
       </c>
       <c r="U17" s="35">
-        <v>1310</v>
+        <v>944</v>
       </c>
       <c r="V17" s="35">
-        <v>7402</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2799,8 +2798,8 @@
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -2809,10 +2808,10 @@
       <c r="H21" s="21"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="O21" s="32" t="s">
+      <c r="O21" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="32"/>
+      <c r="P21" s="31"/>
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="5" t="s">
@@ -2849,7 +2848,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46147.854166666664</v>
+        <v>46146.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3001,8 +3000,8 @@
       <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3235,8 +3234,8 @@
       <c r="AF40" s="27"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3475,8 +3474,8 @@
       <c r="AF50" s="27"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
       <c r="C51" s="2"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
@@ -3488,8 +3487,8 @@
       <c r="AF51" s="27"/>
     </row>
     <row r="52" spans="1:32">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21">
         <v>0</v>
@@ -3510,8 +3509,8 @@
       <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:32">
-      <c r="A53" s="33"/>
-      <c r="B53" s="33"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3803,7 +3802,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB9C6E1-9ED5-4F9E-A921-9601F6BFCC2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB9C6E1-9ED5-4F9E-A921-9601F6BFCC2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="382" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D37F5BCD-5942-498E-BE59-0F1DF6A5CC1F}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00A7A31-F7E6-41C9-B715-1D2F69B55449}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
   <sheets>
     <sheet name="Estatus diario" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="790" r:id="rId2"/>
+    <pivotCache cacheId="33" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="24">
   <si>
     <t>SEM</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Hora de corte</t>
+  </si>
+  <si>
+    <t>C4</t>
   </si>
 </sst>
 </file>
@@ -1155,12 +1158,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="304">
@@ -1483,7 +1486,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46148.707666087961" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46155.771338194441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1499,15 +1502,16 @@
       </sharedItems>
     </cacheField>
     <cacheField name="S1" numFmtId="0">
-      <sharedItems containsBlank="1" count="13">
+      <sharedItems containsBlank="1" count="14">
         <s v="A1"/>
         <s v="A2"/>
         <s v="B1"/>
         <s v="B2"/>
         <s v="C1"/>
         <s v="C2"/>
+        <s v="C4"/>
+        <s v="TL"/>
         <m/>
-        <s v="TL"/>
         <s v="S2"/>
         <s v="S3"/>
         <s v="S4"/>
@@ -1516,7 +1520,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6798"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6959"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1532,51 +1536,51 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1230"/>
+    <n v="1255"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="1042"/>
+    <n v="866"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1191"/>
+    <n v="1083"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1191"/>
+    <n v="1071"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1200"/>
+    <n v="1020"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="944"/>
+    <n v="848"/>
   </r>
   <r>
     <x v="0"/>
     <x v="6"/>
-    <m/>
+    <n v="816"/>
   </r>
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="6798"/>
+    <n v="6959"/>
   </r>
   <r>
     <x v="1"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
     <x v="2"/>
-    <x v="8"/>
+    <x v="9"/>
     <s v="TL"/>
   </r>
   <r>
@@ -1611,7 +1615,7 @@
   </r>
   <r>
     <x v="2"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
@@ -1621,12 +1625,12 @@
   </r>
   <r>
     <x v="1"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
     <x v="3"/>
-    <x v="9"/>
+    <x v="10"/>
     <s v="TL"/>
   </r>
   <r>
@@ -1661,7 +1665,7 @@
   </r>
   <r>
     <x v="3"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
@@ -1671,12 +1675,12 @@
   </r>
   <r>
     <x v="1"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
     <x v="4"/>
-    <x v="10"/>
+    <x v="11"/>
     <s v="TL"/>
   </r>
   <r>
@@ -1711,7 +1715,7 @@
   </r>
   <r>
     <x v="4"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
@@ -1721,12 +1725,12 @@
   </r>
   <r>
     <x v="1"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
     <x v="5"/>
-    <x v="11"/>
+    <x v="12"/>
     <s v="TL"/>
   </r>
   <r>
@@ -1761,7 +1765,7 @@
   </r>
   <r>
     <x v="5"/>
-    <x v="6"/>
+    <x v="8"/>
     <m/>
   </r>
   <r>
@@ -1773,8 +1777,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="790" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O10:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O10:W17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="7">
@@ -1788,20 +1792,21 @@
       </items>
     </pivotField>
     <pivotField axis="axisCol" showAll="0">
-      <items count="14">
+      <items count="15">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
-        <item m="1" x="12"/>
-        <item h="1" x="8"/>
+        <item h="1" m="1" x="13"/>
         <item h="1" x="9"/>
         <item h="1" x="10"/>
         <item h="1" x="11"/>
+        <item h="1" x="12"/>
         <item h="1" x="7"/>
-        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1833,7 +1838,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="7">
+  <colItems count="8">
     <i>
       <x/>
     </i>
@@ -1851,6 +1856,9 @@
     </i>
     <i>
       <x v="5"/>
+    </i>
+    <i>
+      <x v="13"/>
     </i>
     <i t="grand">
       <x/>
@@ -2197,16 +2205,17 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="25" t="s">
         <v>19</v>
       </c>
@@ -2224,7 +2233,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2267,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2267,18 +2276,18 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1230</v>
-      </c>
-      <c r="D3" s="34">
-        <v>1230</v>
+        <v>1255</v>
+      </c>
+      <c r="D3" s="31">
+        <v>1255</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>205</v>
+        <v>209.16666666666666</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -2286,23 +2295,23 @@
         <v>5</v>
       </c>
       <c r="C4" s="11">
-        <f t="shared" ref="C4:C8" si="1">+SUM(D4:H4)</f>
-        <v>1042</v>
-      </c>
-      <c r="D4" s="34">
-        <v>1042</v>
+        <f t="shared" ref="C4:C9" si="1">+SUM(D4:H4)</f>
+        <v>866</v>
+      </c>
+      <c r="D4" s="31">
+        <v>866</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>173.66666666666666</v>
+        <v>144.33333333333334</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="P4" s="31"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="P4" s="32"/>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
@@ -2311,18 +2320,18 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1191</v>
-      </c>
-      <c r="D5" s="34">
-        <v>1191</v>
+        <v>1083</v>
+      </c>
+      <c r="D5" s="31">
+        <v>1083</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>198.5</v>
+        <v>180.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
@@ -2331,18 +2340,18 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1191</v>
-      </c>
-      <c r="D6" s="34">
-        <v>1191</v>
+        <v>1071</v>
+      </c>
+      <c r="D6" s="31">
+        <v>1071</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>198.5</v>
+        <v>178.5</v>
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="13" t="s">
         <v>1</v>
       </c>
@@ -2351,18 +2360,18 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="D7" s="34">
-        <v>1200</v>
+        <v>1020</v>
+      </c>
+      <c r="D7" s="31">
+        <v>1020</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
@@ -2371,27 +2380,35 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>944</v>
-      </c>
-      <c r="D8" s="34">
-        <v>944</v>
+        <v>848</v>
+      </c>
+      <c r="D8" s="31">
+        <v>848</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>157.33333333333334</v>
+        <v>141.33333333333334</v>
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:22" hidden="1">
+    <row r="9" spans="1:23">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="11"/>
+      <c r="B9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="11">
+        <f t="shared" si="1"/>
+        <v>816</v>
+      </c>
+      <c r="D9" s="31">
+        <v>816</v>
+      </c>
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
@@ -2400,11 +2417,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>6798</v>
+        <v>6959</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>6798</v>
+        <v>6959</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2424,7 +2441,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>226.6</v>
+        <v>231.96666666666664</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2434,7 +2451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="5"/>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
@@ -2467,10 +2484,13 @@
         <v>9</v>
       </c>
       <c r="V11" t="s">
+        <v>23</v>
+      </c>
+      <c r="W11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -2508,28 +2528,31 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="Q12" s="35">
-        <v>1042</v>
+        <v>866</v>
       </c>
       <c r="R12" s="35">
-        <v>1191</v>
+        <v>1083</v>
       </c>
       <c r="S12" s="35">
-        <v>1191</v>
+        <v>1071</v>
       </c>
       <c r="T12" s="35">
-        <v>1200</v>
+        <v>1020</v>
       </c>
       <c r="U12" s="35">
-        <v>944</v>
+        <v>848</v>
       </c>
       <c r="V12" s="35">
-        <v>6798</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>816</v>
+      </c>
+      <c r="W12" s="35">
+        <v>6959</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -2566,11 +2589,12 @@
       <c r="U13" s="35">
         <v>0</v>
       </c>
-      <c r="V13" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="V13" s="35"/>
+      <c r="W13" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="13" t="s">
         <v>11</v>
       </c>
@@ -2607,11 +2631,12 @@
       <c r="U14" s="35">
         <v>0</v>
       </c>
-      <c r="V14" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="V14" s="35"/>
+      <c r="W14" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -2648,11 +2673,12 @@
       <c r="U15" s="35">
         <v>0</v>
       </c>
-      <c r="V15" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="V15" s="35"/>
+      <c r="W15" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="13" t="s">
         <v>11</v>
       </c>
@@ -2689,7 +2715,8 @@
       <c r="U16" s="35">
         <v>0</v>
       </c>
-      <c r="V16" s="35">
+      <c r="V16" s="35"/>
+      <c r="W16" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2713,25 +2740,28 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="Q17" s="35">
-        <v>1042</v>
+        <v>866</v>
       </c>
       <c r="R17" s="35">
-        <v>1191</v>
+        <v>1083</v>
       </c>
       <c r="S17" s="35">
-        <v>1191</v>
+        <v>1071</v>
       </c>
       <c r="T17" s="35">
-        <v>1200</v>
+        <v>1020</v>
       </c>
       <c r="U17" s="35">
-        <v>944</v>
+        <v>848</v>
       </c>
       <c r="V17" s="35">
-        <v>6798</v>
+        <v>816</v>
+      </c>
+      <c r="W17" s="35">
+        <v>6959</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2751,7 +2781,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:32" hidden="1">
+    <row r="19" spans="1:32">
       <c r="A19" s="13" t="s">
         <v>11</v>
       </c>
@@ -2798,8 +2828,8 @@
       <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -2808,10 +2838,10 @@
       <c r="H21" s="21"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="31"/>
+      <c r="P21" s="32"/>
     </row>
     <row r="22" spans="1:32">
       <c r="A22" s="5" t="s">
@@ -2953,7 +2983,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:32" hidden="1">
+    <row r="29" spans="1:32">
       <c r="A29" s="13" t="s">
         <v>12</v>
       </c>
@@ -3000,8 +3030,8 @@
       <c r="J30" s="20"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -3180,7 +3210,7 @@
       <c r="J38" s="3"/>
       <c r="AF38" s="27"/>
     </row>
-    <row r="39" spans="1:32" hidden="1">
+    <row r="39" spans="1:32">
       <c r="A39" s="13" t="s">
         <v>13</v>
       </c>
@@ -3234,8 +3264,8 @@
       <c r="AF40" s="27"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3420,7 +3450,7 @@
       <c r="J48" s="3"/>
       <c r="AF48" s="27"/>
     </row>
-    <row r="49" spans="1:32" hidden="1">
+    <row r="49" spans="1:32">
       <c r="A49" s="13" t="s">
         <v>14</v>
       </c>
@@ -3474,8 +3504,8 @@
       <c r="AF50" s="27"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="2"/>
       <c r="D51" s="24"/>
       <c r="E51" s="24"/>
@@ -3487,8 +3517,8 @@
       <c r="AF51" s="27"/>
     </row>
     <row r="52" spans="1:32">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21">
         <v>0</v>
@@ -3509,8 +3539,8 @@
       <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:32">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3536,17 +3566,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3781,6 +3800,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3791,17 +3821,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB9C6E1-9ED5-4F9E-A921-9601F6BFCC2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3820,6 +3839,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
   <ds:schemaRefs>

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E00A7A31-F7E6-41C9-B715-1D2F69B55449}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97BD725-1B7A-4BC6-95B6-142A76792FC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="33" r:id="rId2"/>
+    <pivotCache cacheId="23" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1486,7 +1486,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46155.771338194441" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46177.42890324074" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1520,7 +1520,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6959"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="5998"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1536,42 +1536,42 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1255"/>
+    <n v="907"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="866"/>
+    <n v="862"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1083"/>
+    <n v="969"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1071"/>
+    <n v="872"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1020"/>
+    <n v="966"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="848"/>
+    <n v="786"/>
   </r>
   <r>
     <x v="0"/>
     <x v="6"/>
-    <n v="816"/>
+    <n v="636"/>
   </r>
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="6959"/>
+    <n v="5998"/>
   </r>
   <r>
     <x v="1"/>
@@ -1777,7 +1777,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:W17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2205,9 +2205,7 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -2276,14 +2274,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1255</v>
+        <v>907</v>
       </c>
       <c r="D3" s="31">
-        <v>1255</v>
+        <v>907</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>209.16666666666666</v>
+        <v>151.16666666666666</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2296,14 +2294,14 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C9" si="1">+SUM(D4:H4)</f>
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="D4" s="31">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>144.33333333333334</v>
+        <v>143.66666666666666</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="32" t="s">
@@ -2320,14 +2318,14 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1083</v>
+        <v>969</v>
       </c>
       <c r="D5" s="31">
-        <v>1083</v>
+        <v>969</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>180.5</v>
+        <v>161.5</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -2340,14 +2338,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1071</v>
+        <v>872</v>
       </c>
       <c r="D6" s="31">
-        <v>1071</v>
+        <v>872</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>178.5</v>
+        <v>145.33333333333334</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2360,14 +2358,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>966</v>
       </c>
       <c r="D7" s="31">
-        <v>1020</v>
+        <v>966</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2380,14 +2378,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="D8" s="31">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>141.33333333333334</v>
+        <v>131</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2400,10 +2398,10 @@
       </c>
       <c r="C9" s="11">
         <f t="shared" si="1"/>
-        <v>816</v>
+        <v>636</v>
       </c>
       <c r="D9" s="31">
-        <v>816</v>
+        <v>636</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
@@ -2417,11 +2415,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>6959</v>
+        <v>5998</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>6959</v>
+        <v>5998</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2441,7 +2439,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>231.96666666666664</v>
+        <v>199.93333333333334</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2528,28 +2526,28 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1255</v>
+        <v>907</v>
       </c>
       <c r="Q12" s="35">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="R12" s="35">
-        <v>1083</v>
+        <v>969</v>
       </c>
       <c r="S12" s="35">
-        <v>1071</v>
+        <v>872</v>
       </c>
       <c r="T12" s="35">
-        <v>1020</v>
+        <v>966</v>
       </c>
       <c r="U12" s="35">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="V12" s="35">
-        <v>816</v>
+        <v>636</v>
       </c>
       <c r="W12" s="35">
-        <v>6959</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2740,28 +2738,28 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1255</v>
+        <v>907</v>
       </c>
       <c r="Q17" s="35">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="R17" s="35">
-        <v>1083</v>
+        <v>969</v>
       </c>
       <c r="S17" s="35">
-        <v>1071</v>
+        <v>872</v>
       </c>
       <c r="T17" s="35">
-        <v>1020</v>
+        <v>966</v>
       </c>
       <c r="U17" s="35">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="V17" s="35">
-        <v>816</v>
+        <v>636</v>
       </c>
       <c r="W17" s="35">
-        <v>6959</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2878,7 +2876,7 @@
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46146.854166666664</v>
+        <v>46176.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3801,6 +3799,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -3809,15 +3816,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3840,6 +3838,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3848,12 +3854,4 @@
     <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97BD725-1B7A-4BC6-95B6-142A76792FC5}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF10FCB0-2A55-4AEA-80FA-03647C972CAD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="23" r:id="rId2"/>
+    <pivotCache cacheId="18" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1486,7 +1486,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46177.42890324074" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46209.515215740743" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1520,7 +1520,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="5998"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="8556"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1536,42 +1536,42 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="907"/>
+    <n v="1250"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="862"/>
+    <n v="1160"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="969"/>
+    <n v="1456"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="872"/>
+    <n v="1280"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="966"/>
+    <n v="1320"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="786"/>
+    <n v="1254"/>
   </r>
   <r>
     <x v="0"/>
     <x v="6"/>
-    <n v="636"/>
+    <n v="836"/>
   </r>
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="5998"/>
+    <n v="8556"/>
   </r>
   <r>
     <x v="1"/>
@@ -1777,7 +1777,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:W17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2205,7 +2205,8 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -2274,14 +2275,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>907</v>
+        <v>1250</v>
       </c>
       <c r="D3" s="31">
-        <v>907</v>
+        <v>1250</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>151.16666666666666</v>
+        <v>208.33333333333334</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2294,14 +2295,14 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C9" si="1">+SUM(D4:H4)</f>
-        <v>862</v>
+        <v>1160</v>
       </c>
       <c r="D4" s="31">
-        <v>862</v>
+        <v>1160</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>143.66666666666666</v>
+        <v>193.33333333333334</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="32" t="s">
@@ -2318,14 +2319,14 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>969</v>
+        <v>1456</v>
       </c>
       <c r="D5" s="31">
-        <v>969</v>
+        <v>1456</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>161.5</v>
+        <v>242.66666666666666</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -2338,14 +2339,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>872</v>
+        <v>1280</v>
       </c>
       <c r="D6" s="31">
-        <v>872</v>
+        <v>1280</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>145.33333333333334</v>
+        <v>213.33333333333334</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2358,14 +2359,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>966</v>
+        <v>1320</v>
       </c>
       <c r="D7" s="31">
-        <v>966</v>
+        <v>1320</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2378,14 +2379,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>786</v>
+        <v>1254</v>
       </c>
       <c r="D8" s="31">
-        <v>786</v>
+        <v>1254</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2398,10 +2399,10 @@
       </c>
       <c r="C9" s="11">
         <f t="shared" si="1"/>
-        <v>636</v>
+        <v>836</v>
       </c>
       <c r="D9" s="31">
-        <v>636</v>
+        <v>836</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
@@ -2415,11 +2416,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>5998</v>
+        <v>8556</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>5998</v>
+        <v>8556</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2439,7 +2440,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>199.93333333333334</v>
+        <v>285.2</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2526,28 +2527,28 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>907</v>
+        <v>1250</v>
       </c>
       <c r="Q12" s="35">
-        <v>862</v>
+        <v>1160</v>
       </c>
       <c r="R12" s="35">
-        <v>969</v>
+        <v>1456</v>
       </c>
       <c r="S12" s="35">
-        <v>872</v>
+        <v>1280</v>
       </c>
       <c r="T12" s="35">
-        <v>966</v>
+        <v>1320</v>
       </c>
       <c r="U12" s="35">
-        <v>786</v>
+        <v>1254</v>
       </c>
       <c r="V12" s="35">
-        <v>636</v>
+        <v>836</v>
       </c>
       <c r="W12" s="35">
-        <v>5998</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2738,28 +2739,28 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>907</v>
+        <v>1250</v>
       </c>
       <c r="Q17" s="35">
-        <v>862</v>
+        <v>1160</v>
       </c>
       <c r="R17" s="35">
-        <v>969</v>
+        <v>1456</v>
       </c>
       <c r="S17" s="35">
-        <v>872</v>
+        <v>1280</v>
       </c>
       <c r="T17" s="35">
-        <v>966</v>
+        <v>1320</v>
       </c>
       <c r="U17" s="35">
-        <v>786</v>
+        <v>1254</v>
       </c>
       <c r="V17" s="35">
-        <v>636</v>
+        <v>836</v>
       </c>
       <c r="W17" s="35">
-        <v>5998</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="18" spans="1:32">

--- a/SUDOKU.xlsx
+++ b/SUDOKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF10FCB0-2A55-4AEA-80FA-03647C972CAD}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:1_{0AD06FF4-A909-423F-B378-69C0033412ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB1AB86B-6B86-4C99-BE4B-9750E05ADBE8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF95C2B5-218E-4516-887F-CDE11964293A}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId2"/>
+    <pivotCache cacheId="279" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1486,7 +1486,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46209.515215740743" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Santiago Calvo Prieto" refreshedDate="46244.479573842589" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{93C581A5-61B5-40FF-AC76-618DD97B7B96}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:C50" sheet="Estatus diario"/>
   </cacheSource>
@@ -1520,7 +1520,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="HS" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="8556"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="5811"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1536,42 +1536,42 @@
   <r>
     <x v="0"/>
     <x v="0"/>
-    <n v="1250"/>
+    <n v="964"/>
   </r>
   <r>
     <x v="0"/>
     <x v="1"/>
-    <n v="1160"/>
+    <n v="770"/>
   </r>
   <r>
     <x v="0"/>
     <x v="2"/>
-    <n v="1456"/>
+    <n v="926"/>
   </r>
   <r>
     <x v="0"/>
     <x v="3"/>
-    <n v="1280"/>
+    <n v="906"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <n v="1320"/>
+    <n v="1002"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <n v="1254"/>
+    <n v="713"/>
   </r>
   <r>
     <x v="0"/>
     <x v="6"/>
-    <n v="836"/>
+    <n v="530"/>
   </r>
   <r>
     <x v="0"/>
     <x v="7"/>
-    <n v="8556"/>
+    <n v="5811"/>
   </r>
   <r>
     <x v="1"/>
@@ -1777,7 +1777,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96476416-5E19-428A-9C28-862565FD05AB}" name="TablaDinámica2" cacheId="279" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O10:W17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -2205,8 +2205,9 @@
     <col min="14" max="14" width="5.5703125" customWidth="1"/>
     <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="3" bestFit="1" customWidth="1"/>
@@ -2243,23 +2244,23 @@
         <v>2</v>
       </c>
       <c r="D2" s="8">
-        <v>46084</v>
+        <v>46238</v>
       </c>
       <c r="E2" s="8">
         <f>+D2+1</f>
-        <v>46085</v>
+        <v>46239</v>
       </c>
       <c r="F2" s="8">
         <f t="shared" ref="F2:G2" si="0">+E2+1</f>
-        <v>46086</v>
+        <v>46240</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" si="0"/>
-        <v>46087</v>
+        <v>46241</v>
       </c>
       <c r="H2" s="8">
         <f>+G2+3</f>
-        <v>46090</v>
+        <v>46244</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>3</v>
@@ -2275,14 +2276,14 @@
       </c>
       <c r="C3" s="11">
         <f>+SUM(D3:H3)</f>
-        <v>1250</v>
+        <v>964</v>
       </c>
       <c r="D3" s="31">
-        <v>1250</v>
+        <v>964</v>
       </c>
       <c r="I3" s="26">
         <f>IFERROR(C3/6/COUNT(D3:H3),0)</f>
-        <v>208.33333333333334</v>
+        <v>160.66666666666666</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -2295,14 +2296,14 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" ref="C4:C9" si="1">+SUM(D4:H4)</f>
-        <v>1160</v>
+        <v>770</v>
       </c>
       <c r="D4" s="31">
-        <v>1160</v>
+        <v>770</v>
       </c>
       <c r="I4" s="26">
         <f t="shared" ref="I4:I10" si="2">IFERROR(C4/6/COUNT(D4:H4),0)</f>
-        <v>193.33333333333334</v>
+        <v>128.33333333333334</v>
       </c>
       <c r="J4" s="3"/>
       <c r="O4" s="32" t="s">
@@ -2319,14 +2320,14 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>1456</v>
+        <v>926</v>
       </c>
       <c r="D5" s="31">
-        <v>1456</v>
+        <v>926</v>
       </c>
       <c r="I5" s="26">
         <f t="shared" si="2"/>
-        <v>242.66666666666666</v>
+        <v>154.33333333333334</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -2339,14 +2340,14 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>1280</v>
+        <v>906</v>
       </c>
       <c r="D6" s="31">
-        <v>1280</v>
+        <v>906</v>
       </c>
       <c r="I6" s="26">
         <f t="shared" si="2"/>
-        <v>213.33333333333334</v>
+        <v>151</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -2359,14 +2360,14 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>1320</v>
+        <v>1002</v>
       </c>
       <c r="D7" s="31">
-        <v>1320</v>
+        <v>1002</v>
       </c>
       <c r="I7" s="26">
         <f t="shared" si="2"/>
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2379,14 +2380,14 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>1254</v>
+        <v>713</v>
       </c>
       <c r="D8" s="31">
-        <v>1254</v>
+        <v>713</v>
       </c>
       <c r="I8" s="26">
         <f t="shared" si="2"/>
-        <v>209</v>
+        <v>118.83333333333333</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2399,10 +2400,10 @@
       </c>
       <c r="C9" s="11">
         <f t="shared" si="1"/>
-        <v>836</v>
+        <v>530</v>
       </c>
       <c r="D9" s="31">
-        <v>836</v>
+        <v>530</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="3"/>
@@ -2416,11 +2417,11 @@
       </c>
       <c r="C10" s="18">
         <f>SUM(C3:C9)</f>
-        <v>8556</v>
+        <v>5811</v>
       </c>
       <c r="D10" s="19">
         <f>SUM(D3:D9)</f>
-        <v>8556</v>
+        <v>5811</v>
       </c>
       <c r="E10" s="19">
         <f t="shared" ref="E10:H10" si="3">SUM(E3:E9)</f>
@@ -2440,7 +2441,7 @@
       </c>
       <c r="I10" s="26">
         <f t="shared" si="2"/>
-        <v>285.2</v>
+        <v>193.7</v>
       </c>
       <c r="J10" s="20"/>
       <c r="O10" s="30" t="s">
@@ -2501,23 +2502,23 @@
       </c>
       <c r="D12" s="8">
         <f>+H2+1</f>
-        <v>46091</v>
+        <v>46245</v>
       </c>
       <c r="E12" s="8">
         <f>+D12+1</f>
-        <v>46092</v>
+        <v>46246</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" ref="F12:G12" si="4">+E12+1</f>
-        <v>46093</v>
+        <v>46247</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="4"/>
-        <v>46094</v>
+        <v>46248</v>
       </c>
       <c r="H12" s="8">
         <f>+G12+3</f>
-        <v>46097</v>
+        <v>46251</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>3</v>
@@ -2527,28 +2528,28 @@
         <v>1</v>
       </c>
       <c r="P12" s="35">
-        <v>1250</v>
+        <v>964</v>
       </c>
       <c r="Q12" s="35">
-        <v>1160</v>
+        <v>770</v>
       </c>
       <c r="R12" s="35">
-        <v>1456</v>
+        <v>926</v>
       </c>
       <c r="S12" s="35">
-        <v>1280</v>
+        <v>906</v>
       </c>
       <c r="T12" s="35">
-        <v>1320</v>
+        <v>1002</v>
       </c>
       <c r="U12" s="35">
-        <v>1254</v>
+        <v>713</v>
       </c>
       <c r="V12" s="35">
-        <v>836</v>
+        <v>530</v>
       </c>
       <c r="W12" s="35">
-        <v>8556</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2739,28 +2740,28 @@
         <v>16</v>
       </c>
       <c r="P17" s="35">
-        <v>1250</v>
+        <v>964</v>
       </c>
       <c r="Q17" s="35">
-        <v>1160</v>
+        <v>770</v>
       </c>
       <c r="R17" s="35">
-        <v>1456</v>
+        <v>926</v>
       </c>
       <c r="S17" s="35">
-        <v>1280</v>
+        <v>906</v>
       </c>
       <c r="T17" s="35">
-        <v>1320</v>
+        <v>1002</v>
       </c>
       <c r="U17" s="35">
-        <v>1254</v>
+        <v>713</v>
       </c>
       <c r="V17" s="35">
-        <v>836</v>
+        <v>530</v>
       </c>
       <c r="W17" s="35">
-        <v>8556</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="18" spans="1:32">
@@ -2854,30 +2855,30 @@
       </c>
       <c r="D22" s="8">
         <f>+H12+1</f>
-        <v>46098</v>
+        <v>46252</v>
       </c>
       <c r="E22" s="8">
         <f>+D22+1</f>
-        <v>46099</v>
+        <v>46253</v>
       </c>
       <c r="F22" s="8">
         <f t="shared" ref="F22:G22" si="8">+E22+1</f>
-        <v>46100</v>
+        <v>46254</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="8"/>
-        <v>46101</v>
+        <v>46255</v>
       </c>
       <c r="H22" s="8">
         <f>+G22+3</f>
-        <v>46104</v>
+        <v>46258</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="28">
-        <v>46176.854166666664</v>
+        <v>46241.854166666664</v>
       </c>
     </row>
     <row r="23" spans="1:32">
@@ -3053,23 +3054,23 @@
       </c>
       <c r="D32" s="8">
         <f>+H22+1</f>
-        <v>46105</v>
+        <v>46259</v>
       </c>
       <c r="E32" s="8">
         <f>+D32+1</f>
-        <v>46106</v>
+        <v>46260</v>
       </c>
       <c r="F32" s="8">
         <f t="shared" ref="F32:G32" si="12">+E32+1</f>
-        <v>46107</v>
+        <v>46261</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="12"/>
-        <v>46108</v>
+        <v>46262</v>
       </c>
       <c r="H32" s="8">
         <f>+G32+3</f>
-        <v>46111</v>
+        <v>46265</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>3</v>
@@ -3287,23 +3288,23 @@
       </c>
       <c r="D42" s="8">
         <f>+H32+1</f>
-        <v>46112</v>
+        <v>46266</v>
       </c>
       <c r="E42" s="8">
         <f>+D42+1</f>
-        <v>46113</v>
+        <v>46267</v>
       </c>
       <c r="F42" s="8">
         <f t="shared" ref="F42:G42" si="16">+E42+1</f>
-        <v>46114</v>
+        <v>46268</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="16"/>
-        <v>46115</v>
+        <v>46269</v>
       </c>
       <c r="H42" s="8">
         <f>+G42+3</f>
-        <v>46118</v>
+        <v>46272</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>3</v>
@@ -3565,6 +3566,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -3799,27 +3820,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB9C6E1-9ED5-4F9E-A921-9601F6BFCC2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3836,23 +3856,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BCA648-DFB0-4933-AD78-DBDD8CAF7C52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{007506E0-0CDE-4051-B6C4-9C0A8A8B90A4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>